--- a/artfynd/A 41034-2025 artfynd.xlsx
+++ b/artfynd/A 41034-2025 artfynd.xlsx
@@ -3688,32 +3688,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128819672</v>
+        <v>128834415</v>
       </c>
       <c r="B30" t="n">
-        <v>98619</v>
+        <v>80221</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3723,13 +3723,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>753733</v>
+        <v>754084</v>
       </c>
       <c r="R30" t="n">
-        <v>7294060</v>
+        <v>7293943</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3759,11 +3759,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Mycket Riklig förekomst</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3778,44 +3773,44 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128819673</v>
+        <v>128834411</v>
       </c>
       <c r="B31" t="n">
-        <v>98619</v>
+        <v>80221</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3825,13 +3820,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>753787</v>
+        <v>754071</v>
       </c>
       <c r="R31" t="n">
-        <v>7294025</v>
+        <v>7293962</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3861,11 +3856,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Mycket riktig förekomst</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3880,44 +3870,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128834473</v>
+        <v>128834420</v>
       </c>
       <c r="B32" t="n">
-        <v>98619</v>
+        <v>80221</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3927,10 +3917,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>754284</v>
+        <v>754338</v>
       </c>
       <c r="R32" t="n">
-        <v>7293849</v>
+        <v>7293821</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3989,7 +3979,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128834490</v>
+        <v>128819672</v>
       </c>
       <c r="B33" t="n">
         <v>98619</v>
@@ -4024,13 +4014,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>754042</v>
+        <v>753733</v>
       </c>
       <c r="R33" t="n">
-        <v>7294151</v>
+        <v>7294060</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4064,7 +4054,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Riklig förekomst ca 10m diam</t>
+          <t>Mycket Riklig förekomst</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4079,44 +4069,44 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128834415</v>
+        <v>128834473</v>
       </c>
       <c r="B34" t="n">
-        <v>80221</v>
+        <v>98619</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4126,10 +4116,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>754084</v>
+        <v>754284</v>
       </c>
       <c r="R34" t="n">
-        <v>7293943</v>
+        <v>7293849</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4188,32 +4178,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128834411</v>
+        <v>128819673</v>
       </c>
       <c r="B35" t="n">
-        <v>80221</v>
+        <v>98619</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4223,13 +4213,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>754071</v>
+        <v>753787</v>
       </c>
       <c r="R35" t="n">
-        <v>7293962</v>
+        <v>7294025</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4259,6 +4249,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Mycket riktig förekomst</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4273,44 +4268,44 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128834420</v>
+        <v>128834490</v>
       </c>
       <c r="B36" t="n">
-        <v>80221</v>
+        <v>98619</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4320,10 +4315,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>754338</v>
+        <v>754042</v>
       </c>
       <c r="R36" t="n">
-        <v>7293821</v>
+        <v>7294151</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4356,6 +4351,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Riklig förekomst ca 10m diam</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4382,32 +4382,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128834417</v>
+        <v>128834462</v>
       </c>
       <c r="B37" t="n">
-        <v>80221</v>
+        <v>98619</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4417,10 +4417,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>754171</v>
+        <v>754024</v>
       </c>
       <c r="R37" t="n">
-        <v>7293926</v>
+        <v>7293998</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4479,32 +4479,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128834462</v>
+        <v>128834434</v>
       </c>
       <c r="B38" t="n">
-        <v>98619</v>
+        <v>95469</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>2387</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>754024</v>
+        <v>753879</v>
       </c>
       <c r="R38" t="n">
-        <v>7293998</v>
+        <v>7293890</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4576,7 +4576,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128834405</v>
+        <v>128834417</v>
       </c>
       <c r="B39" t="n">
         <v>80221</v>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>753772</v>
+        <v>754171</v>
       </c>
       <c r="R39" t="n">
-        <v>7293986</v>
+        <v>7293926</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4673,10 +4673,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128834390</v>
+        <v>128819696</v>
       </c>
       <c r="B40" t="n">
-        <v>80125</v>
+        <v>80256</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4684,21 +4684,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6456</v>
+        <v>6463</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4708,13 +4708,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>754064</v>
+        <v>754302</v>
       </c>
       <c r="R40" t="n">
-        <v>7294121</v>
+        <v>7293804</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4758,44 +4758,44 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128834378</v>
+        <v>128834405</v>
       </c>
       <c r="B41" t="n">
-        <v>80250</v>
+        <v>80221</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4805,10 +4805,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>753636</v>
+        <v>753772</v>
       </c>
       <c r="R41" t="n">
-        <v>7294023</v>
+        <v>7293986</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4867,10 +4867,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128834434</v>
+        <v>128834390</v>
       </c>
       <c r="B42" t="n">
-        <v>95469</v>
+        <v>80125</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4878,21 +4878,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2387</v>
+        <v>6456</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>753879</v>
+        <v>754064</v>
       </c>
       <c r="R42" t="n">
-        <v>7293890</v>
+        <v>7294121</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5061,10 +5061,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128819696</v>
+        <v>128834378</v>
       </c>
       <c r="B44" t="n">
-        <v>80256</v>
+        <v>80250</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5072,21 +5072,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5096,13 +5096,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>754302</v>
+        <v>753636</v>
       </c>
       <c r="R44" t="n">
-        <v>7293804</v>
+        <v>7294023</v>
       </c>
       <c r="S44" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5146,44 +5146,44 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128819675</v>
+        <v>128834410</v>
       </c>
       <c r="B45" t="n">
-        <v>98619</v>
+        <v>80221</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5193,13 +5193,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>753812</v>
+        <v>754046</v>
       </c>
       <c r="R45" t="n">
-        <v>7293999</v>
+        <v>7293956</v>
       </c>
       <c r="S45" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5229,11 +5229,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5248,12 +5243,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5357,32 +5352,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128834454</v>
+        <v>128834386</v>
       </c>
       <c r="B47" t="n">
-        <v>98619</v>
+        <v>57713</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5392,10 +5387,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>753898</v>
+        <v>753889</v>
       </c>
       <c r="R47" t="n">
-        <v>7293898</v>
+        <v>7294195</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5432,7 +5427,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>3mtr diam</t>
+          <t>Hack vid trädbas</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5459,32 +5454,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128834386</v>
+        <v>128834454</v>
       </c>
       <c r="B48" t="n">
-        <v>57713</v>
+        <v>98619</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5494,10 +5489,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>753889</v>
+        <v>753898</v>
       </c>
       <c r="R48" t="n">
-        <v>7294195</v>
+        <v>7293898</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5534,7 +5529,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Hack vid trädbas</t>
+          <t>3mtr diam</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5561,32 +5556,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128834410</v>
+        <v>128819675</v>
       </c>
       <c r="B49" t="n">
-        <v>80221</v>
+        <v>98619</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5596,13 +5591,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>754046</v>
+        <v>753812</v>
       </c>
       <c r="R49" t="n">
-        <v>7293956</v>
+        <v>7293999</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5632,6 +5627,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5646,44 +5646,44 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128819690</v>
+        <v>128834406</v>
       </c>
       <c r="B50" t="n">
-        <v>98619</v>
+        <v>80221</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5693,13 +5693,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>754224</v>
+        <v>753974</v>
       </c>
       <c r="R50" t="n">
-        <v>7293966</v>
+        <v>7294029</v>
       </c>
       <c r="S50" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5743,44 +5743,44 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128819693</v>
+        <v>128834430</v>
       </c>
       <c r="B51" t="n">
-        <v>98619</v>
+        <v>80221</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5790,13 +5790,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>754024</v>
+        <v>754027</v>
       </c>
       <c r="R51" t="n">
-        <v>7294106</v>
+        <v>7294150</v>
       </c>
       <c r="S51" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5826,11 +5826,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>På ett större område mer än 30 individer</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5845,44 +5840,44 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128834406</v>
+        <v>128819690</v>
       </c>
       <c r="B52" t="n">
-        <v>80221</v>
+        <v>98619</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5892,13 +5887,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>753974</v>
+        <v>754224</v>
       </c>
       <c r="R52" t="n">
-        <v>7294029</v>
+        <v>7293966</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5942,19 +5937,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128834484</v>
+        <v>128819693</v>
       </c>
       <c r="B53" t="n">
         <v>98619</v>
@@ -5989,13 +5984,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>754289</v>
+        <v>754024</v>
       </c>
       <c r="R53" t="n">
-        <v>7293999</v>
+        <v>7294106</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6029,7 +6024,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Riklig förekomst  ca 6m diam</t>
+          <t>På ett större område mer än 30 individer</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6044,44 +6039,44 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128834430</v>
+        <v>128834484</v>
       </c>
       <c r="B54" t="n">
-        <v>80221</v>
+        <v>98619</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6091,10 +6086,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>754027</v>
+        <v>754289</v>
       </c>
       <c r="R54" t="n">
-        <v>7294150</v>
+        <v>7293999</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6127,6 +6122,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Riklig förekomst  ca 6m diam</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6255,10 +6255,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128819648</v>
+        <v>128834376</v>
       </c>
       <c r="B56" t="n">
-        <v>80221</v>
+        <v>91494</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6266,21 +6266,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>754142</v>
+        <v>754253</v>
       </c>
       <c r="R56" t="n">
-        <v>7293999</v>
+        <v>7293898</v>
       </c>
       <c r="S56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6340,44 +6340,44 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128819680</v>
+        <v>128834433</v>
       </c>
       <c r="B57" t="n">
-        <v>98619</v>
+        <v>95469</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>2387</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6387,13 +6387,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>754079</v>
+        <v>753867</v>
       </c>
       <c r="R57" t="n">
-        <v>7294043</v>
+        <v>7293877</v>
       </c>
       <c r="S57" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6423,11 +6423,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Rik förekomst</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6442,44 +6437,44 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128834433</v>
+        <v>128834491</v>
       </c>
       <c r="B58" t="n">
-        <v>95469</v>
+        <v>56898</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2387</v>
+        <v>102612</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6489,10 +6484,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>753867</v>
+        <v>753881</v>
       </c>
       <c r="R58" t="n">
-        <v>7293877</v>
+        <v>7293891</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6551,10 +6546,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128834376</v>
+        <v>128819648</v>
       </c>
       <c r="B59" t="n">
-        <v>91494</v>
+        <v>80221</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6562,21 +6557,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6586,13 +6581,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>754253</v>
+        <v>754142</v>
       </c>
       <c r="R59" t="n">
-        <v>7293898</v>
+        <v>7293999</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6636,44 +6631,44 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128834446</v>
+        <v>128834404</v>
       </c>
       <c r="B60" t="n">
-        <v>98619</v>
+        <v>80221</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6683,10 +6678,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>753638</v>
+        <v>753693</v>
       </c>
       <c r="R60" t="n">
-        <v>7293994</v>
+        <v>7293978</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6719,11 +6714,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Mycket rikligt bestånd</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6750,7 +6740,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128834449</v>
+        <v>128834446</v>
       </c>
       <c r="B61" t="n">
         <v>98619</v>
@@ -6785,10 +6775,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>753732</v>
+        <v>753638</v>
       </c>
       <c r="R61" t="n">
-        <v>7293989</v>
+        <v>7293994</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6852,32 +6842,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128834491</v>
+        <v>128834449</v>
       </c>
       <c r="B62" t="n">
-        <v>56898</v>
+        <v>98619</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6887,10 +6877,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>753881</v>
+        <v>753732</v>
       </c>
       <c r="R62" t="n">
-        <v>7293891</v>
+        <v>7293989</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6923,6 +6913,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Mycket rikligt bestånd</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6949,32 +6944,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128834404</v>
+        <v>128819680</v>
       </c>
       <c r="B63" t="n">
-        <v>80221</v>
+        <v>98619</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6984,13 +6979,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>753693</v>
+        <v>754079</v>
       </c>
       <c r="R63" t="n">
-        <v>7293978</v>
+        <v>7294043</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7020,6 +7015,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Rik förekomst</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7034,44 +7034,44 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128819677</v>
+        <v>128834407</v>
       </c>
       <c r="B64" t="n">
-        <v>98619</v>
+        <v>80221</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7081,13 +7081,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>753875</v>
+        <v>753989</v>
       </c>
       <c r="R64" t="n">
-        <v>7294001</v>
+        <v>7294010</v>
       </c>
       <c r="S64" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7131,19 +7131,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128834407</v>
+        <v>128834416</v>
       </c>
       <c r="B65" t="n">
         <v>80221</v>
@@ -7178,10 +7178,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>753989</v>
+        <v>754148</v>
       </c>
       <c r="R65" t="n">
-        <v>7294010</v>
+        <v>7293935</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7240,32 +7240,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128834457</v>
+        <v>128834380</v>
       </c>
       <c r="B66" t="n">
-        <v>98619</v>
+        <v>80250</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7275,10 +7275,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>753947</v>
+        <v>754091</v>
       </c>
       <c r="R66" t="n">
-        <v>7293964</v>
+        <v>7293941</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7311,11 +7311,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>5mtr diam</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7342,7 +7337,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128834463</v>
+        <v>128834457</v>
       </c>
       <c r="B67" t="n">
         <v>98619</v>
@@ -7377,7 +7372,7 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>754071</v>
+        <v>753947</v>
       </c>
       <c r="R67" t="n">
         <v>7293964</v>
@@ -7413,6 +7408,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>5mtr diam</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7439,32 +7439,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128834416</v>
+        <v>128834463</v>
       </c>
       <c r="B68" t="n">
-        <v>80221</v>
+        <v>98619</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7474,10 +7474,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>754148</v>
+        <v>754071</v>
       </c>
       <c r="R68" t="n">
-        <v>7293935</v>
+        <v>7293964</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7638,7 +7638,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128834461</v>
+        <v>128819677</v>
       </c>
       <c r="B70" t="n">
         <v>98619</v>
@@ -7673,13 +7673,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>753981</v>
+        <v>753875</v>
       </c>
       <c r="R70" t="n">
-        <v>7294022</v>
+        <v>7294001</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7723,44 +7723,44 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128834380</v>
+        <v>128834461</v>
       </c>
       <c r="B71" t="n">
-        <v>80250</v>
+        <v>98619</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7770,10 +7770,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>754091</v>
+        <v>753981</v>
       </c>
       <c r="R71" t="n">
-        <v>7293941</v>
+        <v>7294022</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7934,32 +7934,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128819652</v>
+        <v>128834476</v>
       </c>
       <c r="B73" t="n">
-        <v>80221</v>
+        <v>98619</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7969,13 +7969,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>754297</v>
+        <v>754345</v>
       </c>
       <c r="R73" t="n">
-        <v>7293780</v>
+        <v>7293808</v>
       </c>
       <c r="S73" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8005,6 +8005,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>3m diam</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8019,19 +8024,19 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128834476</v>
+        <v>128834443</v>
       </c>
       <c r="B74" t="n">
         <v>98619</v>
@@ -8066,10 +8071,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>754345</v>
+        <v>754042</v>
       </c>
       <c r="R74" t="n">
-        <v>7293808</v>
+        <v>7294129</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8106,7 +8111,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>3m diam</t>
+          <t>Måttlig förekomst 6m diam</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8133,7 +8138,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128834443</v>
+        <v>128834456</v>
       </c>
       <c r="B75" t="n">
         <v>98619</v>
@@ -8168,10 +8173,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>754042</v>
+        <v>753917</v>
       </c>
       <c r="R75" t="n">
-        <v>7294129</v>
+        <v>7293936</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8204,11 +8209,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Måttlig förekomst 6m diam</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8235,32 +8235,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128834456</v>
+        <v>128834409</v>
       </c>
       <c r="B76" t="n">
-        <v>98619</v>
+        <v>80221</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8270,10 +8270,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>753917</v>
+        <v>754042</v>
       </c>
       <c r="R76" t="n">
-        <v>7293936</v>
+        <v>7293966</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8332,7 +8332,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128834409</v>
+        <v>128834401</v>
       </c>
       <c r="B77" t="n">
         <v>80221</v>
@@ -8367,10 +8367,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>754042</v>
+        <v>753629</v>
       </c>
       <c r="R77" t="n">
-        <v>7293966</v>
+        <v>7294009</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8429,7 +8429,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128834401</v>
+        <v>128819652</v>
       </c>
       <c r="B78" t="n">
         <v>80221</v>
@@ -8464,13 +8464,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>753629</v>
+        <v>754297</v>
       </c>
       <c r="R78" t="n">
-        <v>7294009</v>
+        <v>7293780</v>
       </c>
       <c r="S78" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8514,12 +8514,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -8623,32 +8623,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128834497</v>
+        <v>128819685</v>
       </c>
       <c r="B80" t="n">
-        <v>80256</v>
+        <v>98619</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8658,13 +8658,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>754176</v>
+        <v>754139</v>
       </c>
       <c r="R80" t="n">
-        <v>7293924</v>
+        <v>7294003</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8708,44 +8708,44 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128834492</v>
+        <v>128834488</v>
       </c>
       <c r="B81" t="n">
-        <v>56898</v>
+        <v>98619</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8755,10 +8755,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>753985</v>
+        <v>754049</v>
       </c>
       <c r="R81" t="n">
-        <v>7294023</v>
+        <v>7294111</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -8817,7 +8817,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128834488</v>
+        <v>128834466</v>
       </c>
       <c r="B82" t="n">
         <v>98619</v>
@@ -8852,10 +8852,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>754049</v>
+        <v>754165</v>
       </c>
       <c r="R82" t="n">
-        <v>7294111</v>
+        <v>7293935</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -8888,6 +8888,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>2m diam</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8914,32 +8919,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128834466</v>
+        <v>128834497</v>
       </c>
       <c r="B83" t="n">
-        <v>98619</v>
+        <v>80256</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8949,10 +8954,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>754165</v>
+        <v>754176</v>
       </c>
       <c r="R83" t="n">
-        <v>7293935</v>
+        <v>7293924</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -8985,11 +8990,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>2m diam</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9016,32 +9016,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128834381</v>
+        <v>128819655</v>
       </c>
       <c r="B84" t="n">
-        <v>80250</v>
+        <v>80221</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9051,13 +9051,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>754177</v>
+        <v>754314</v>
       </c>
       <c r="R84" t="n">
-        <v>7293925</v>
+        <v>7293792</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9101,19 +9101,19 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128819655</v>
+        <v>128819664</v>
       </c>
       <c r="B85" t="n">
         <v>80221</v>
@@ -9148,10 +9148,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>754314</v>
+        <v>754142</v>
       </c>
       <c r="R85" t="n">
-        <v>7293792</v>
+        <v>7294080</v>
       </c>
       <c r="S85" t="n">
         <v>3</v>
@@ -9210,32 +9210,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128819664</v>
+        <v>128834381</v>
       </c>
       <c r="B86" t="n">
-        <v>80221</v>
+        <v>80250</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9245,13 +9245,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>754142</v>
+        <v>754177</v>
       </c>
       <c r="R86" t="n">
-        <v>7294080</v>
+        <v>7293925</v>
       </c>
       <c r="S86" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9295,44 +9295,44 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128819685</v>
+        <v>128834492</v>
       </c>
       <c r="B87" t="n">
-        <v>98619</v>
+        <v>56898</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9342,13 +9342,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>754139</v>
+        <v>753985</v>
       </c>
       <c r="R87" t="n">
-        <v>7294003</v>
+        <v>7294023</v>
       </c>
       <c r="S87" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9392,12 +9392,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -9501,32 +9501,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128819681</v>
+        <v>128834427</v>
       </c>
       <c r="B89" t="n">
-        <v>98619</v>
+        <v>80221</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9536,13 +9536,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>754100</v>
+        <v>754149</v>
       </c>
       <c r="R89" t="n">
-        <v>7294064</v>
+        <v>7294074</v>
       </c>
       <c r="S89" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9572,11 +9572,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Mycket Riklig förekomst</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9591,44 +9586,44 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128834427</v>
+        <v>128834432</v>
       </c>
       <c r="B90" t="n">
-        <v>80221</v>
+        <v>80125</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9638,10 +9633,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>754149</v>
+        <v>754056</v>
       </c>
       <c r="R90" t="n">
-        <v>7294074</v>
+        <v>7293965</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -9700,7 +9695,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128834459</v>
+        <v>128819681</v>
       </c>
       <c r="B91" t="n">
         <v>98619</v>
@@ -9735,13 +9730,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>753972</v>
+        <v>754100</v>
       </c>
       <c r="R91" t="n">
-        <v>7294032</v>
+        <v>7294064</v>
       </c>
       <c r="S91" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9771,6 +9766,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Mycket Riklig förekomst</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9785,44 +9785,44 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128834432</v>
+        <v>128834459</v>
       </c>
       <c r="B92" t="n">
-        <v>80125</v>
+        <v>98619</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9832,10 +9832,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>754056</v>
+        <v>753972</v>
       </c>
       <c r="R92" t="n">
-        <v>7293965</v>
+        <v>7294032</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -9991,32 +9991,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128819654</v>
+        <v>128834435</v>
       </c>
       <c r="B94" t="n">
-        <v>80221</v>
+        <v>95469</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6458</v>
+        <v>2387</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10026,13 +10026,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>754303</v>
+        <v>753941</v>
       </c>
       <c r="R94" t="n">
-        <v>7293804</v>
+        <v>7294196</v>
       </c>
       <c r="S94" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10076,44 +10076,44 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128819686</v>
+        <v>128819654</v>
       </c>
       <c r="B95" t="n">
-        <v>98619</v>
+        <v>80221</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10123,10 +10123,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>754145</v>
+        <v>754303</v>
       </c>
       <c r="R95" t="n">
-        <v>7293994</v>
+        <v>7293804</v>
       </c>
       <c r="S95" t="n">
         <v>3</v>
@@ -10379,32 +10379,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128834435</v>
+        <v>128819686</v>
       </c>
       <c r="B98" t="n">
-        <v>95469</v>
+        <v>98619</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2387</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10414,13 +10414,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>753941</v>
+        <v>754145</v>
       </c>
       <c r="R98" t="n">
-        <v>7294196</v>
+        <v>7293994</v>
       </c>
       <c r="S98" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10464,12 +10464,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
@@ -10578,32 +10578,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128834451</v>
+        <v>128819644</v>
       </c>
       <c r="B100" t="n">
-        <v>98619</v>
+        <v>80221</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10613,13 +10613,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>753769</v>
+        <v>754003</v>
       </c>
       <c r="R100" t="n">
-        <v>7293962</v>
+        <v>7294039</v>
       </c>
       <c r="S100" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10663,12 +10663,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -10869,7 +10869,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128834448</v>
+        <v>128819679</v>
       </c>
       <c r="B103" t="n">
         <v>98619</v>
@@ -10904,13 +10904,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>753692</v>
+        <v>754015</v>
       </c>
       <c r="R103" t="n">
-        <v>7293978</v>
+        <v>7294040</v>
       </c>
       <c r="S103" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -10940,6 +10940,11 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10954,19 +10959,19 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128819679</v>
+        <v>128834451</v>
       </c>
       <c r="B104" t="n">
         <v>98619</v>
@@ -11001,13 +11006,13 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>754015</v>
+        <v>753769</v>
       </c>
       <c r="R104" t="n">
-        <v>7294040</v>
+        <v>7293962</v>
       </c>
       <c r="S104" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11037,11 +11042,6 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11056,44 +11056,44 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128819644</v>
+        <v>128834448</v>
       </c>
       <c r="B105" t="n">
-        <v>80221</v>
+        <v>98619</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11103,13 +11103,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>754003</v>
+        <v>753692</v>
       </c>
       <c r="R105" t="n">
-        <v>7294039</v>
+        <v>7293978</v>
       </c>
       <c r="S105" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11153,44 +11153,44 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128834450</v>
+        <v>128834436</v>
       </c>
       <c r="B106" t="n">
-        <v>98619</v>
+        <v>95469</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220787</v>
+        <v>2387</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11200,10 +11200,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>753753</v>
+        <v>753913</v>
       </c>
       <c r="R106" t="n">
-        <v>7293995</v>
+        <v>7294181</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -11262,32 +11262,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128834436</v>
+        <v>128834450</v>
       </c>
       <c r="B107" t="n">
-        <v>95469</v>
+        <v>98619</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>2387</v>
+        <v>220787</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11297,10 +11297,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>753913</v>
+        <v>753753</v>
       </c>
       <c r="R107" t="n">
-        <v>7294181</v>
+        <v>7293995</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -11359,7 +11359,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128834465</v>
+        <v>128819670</v>
       </c>
       <c r="B108" t="n">
         <v>98619</v>
@@ -11394,13 +11394,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>754148</v>
+        <v>753799</v>
       </c>
       <c r="R108" t="n">
-        <v>7293932</v>
+        <v>7294127</v>
       </c>
       <c r="S108" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11430,6 +11430,11 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Mycket riktig förekomst</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11444,19 +11449,19 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128834445</v>
+        <v>128819684</v>
       </c>
       <c r="B109" t="n">
         <v>98619</v>
@@ -11491,13 +11496,13 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>753685</v>
+        <v>754145</v>
       </c>
       <c r="R109" t="n">
-        <v>7294059</v>
+        <v>7294023</v>
       </c>
       <c r="S109" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -11527,11 +11532,6 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>3mtr diam</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11546,19 +11546,19 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128834468</v>
+        <v>128834465</v>
       </c>
       <c r="B110" t="n">
         <v>98619</v>
@@ -11593,10 +11593,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>754196</v>
+        <v>754148</v>
       </c>
       <c r="R110" t="n">
-        <v>7293923</v>
+        <v>7293932</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -11655,7 +11655,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128819670</v>
+        <v>128834445</v>
       </c>
       <c r="B111" t="n">
         <v>98619</v>
@@ -11690,13 +11690,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>753799</v>
+        <v>753685</v>
       </c>
       <c r="R111" t="n">
-        <v>7294127</v>
+        <v>7294059</v>
       </c>
       <c r="S111" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Mycket riktig förekomst</t>
+          <t>3mtr diam</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11745,19 +11745,19 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128819684</v>
+        <v>128834468</v>
       </c>
       <c r="B112" t="n">
         <v>98619</v>
@@ -11792,13 +11792,13 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>754145</v>
+        <v>754196</v>
       </c>
       <c r="R112" t="n">
-        <v>7294023</v>
+        <v>7293923</v>
       </c>
       <c r="S112" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -11842,44 +11842,44 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128819689</v>
+        <v>128834408</v>
       </c>
       <c r="B113" t="n">
-        <v>98619</v>
+        <v>80221</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11889,13 +11889,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>754240</v>
+        <v>754013</v>
       </c>
       <c r="R113" t="n">
-        <v>7293924</v>
+        <v>7293996</v>
       </c>
       <c r="S113" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -11925,11 +11925,6 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Större förekomst</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11944,19 +11939,19 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128819668</v>
+        <v>128834419</v>
       </c>
       <c r="B114" t="n">
         <v>80221</v>
@@ -11991,13 +11986,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>753980</v>
+        <v>754329</v>
       </c>
       <c r="R114" t="n">
-        <v>7294135</v>
+        <v>7293829</v>
       </c>
       <c r="S114" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12041,19 +12036,19 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128819647</v>
+        <v>128819668</v>
       </c>
       <c r="B115" t="n">
         <v>80221</v>
@@ -12088,10 +12083,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>754139</v>
+        <v>753980</v>
       </c>
       <c r="R115" t="n">
-        <v>7294012</v>
+        <v>7294135</v>
       </c>
       <c r="S115" t="n">
         <v>3</v>
@@ -12150,7 +12145,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128834408</v>
+        <v>128819647</v>
       </c>
       <c r="B116" t="n">
         <v>80221</v>
@@ -12185,13 +12180,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>754013</v>
+        <v>754139</v>
       </c>
       <c r="R116" t="n">
-        <v>7293996</v>
+        <v>7294012</v>
       </c>
       <c r="S116" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12235,44 +12230,44 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128834419</v>
+        <v>128819689</v>
       </c>
       <c r="B117" t="n">
-        <v>80221</v>
+        <v>98619</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12282,13 +12277,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>754329</v>
+        <v>754240</v>
       </c>
       <c r="R117" t="n">
-        <v>7293829</v>
+        <v>7293924</v>
       </c>
       <c r="S117" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12318,6 +12313,11 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Större förekomst</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12332,57 +12332,60 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128834400</v>
+        <v>128834499</v>
       </c>
       <c r="B118" t="n">
-        <v>80221</v>
+        <v>91866</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6458</v>
+        <v>1505</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Stormansberget, Nb</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>753636</v>
+        <v>754035</v>
       </c>
       <c r="R118" t="n">
-        <v>7294018</v>
+        <v>7294132</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -12423,6 +12426,7 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
+      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -12441,32 +12445,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128834477</v>
+        <v>128834400</v>
       </c>
       <c r="B119" t="n">
-        <v>98619</v>
+        <v>80221</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12476,10 +12480,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>754356</v>
+        <v>753636</v>
       </c>
       <c r="R119" t="n">
-        <v>7293813</v>
+        <v>7294018</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -12512,11 +12516,6 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Ca 2m diam</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12543,48 +12542,45 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128834499</v>
+        <v>128834429</v>
       </c>
       <c r="B120" t="n">
-        <v>91866</v>
+        <v>80221</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1505</v>
+        <v>6458</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Stormansberget, Nb</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>754035</v>
+        <v>754063</v>
       </c>
       <c r="R120" t="n">
-        <v>7294132</v>
+        <v>7294120</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -12625,7 +12621,6 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -12644,7 +12639,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128834469</v>
+        <v>128834477</v>
       </c>
       <c r="B121" t="n">
         <v>98619</v>
@@ -12679,10 +12674,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>754222</v>
+        <v>754356</v>
       </c>
       <c r="R121" t="n">
-        <v>7293912</v>
+        <v>7293813</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -12719,7 +12714,7 @@
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>10m diam mycket riklig förekomst</t>
+          <t>Ca 2m diam</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12746,32 +12741,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128834429</v>
+        <v>128834469</v>
       </c>
       <c r="B122" t="n">
-        <v>80221</v>
+        <v>98619</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12781,10 +12776,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>754063</v>
+        <v>754222</v>
       </c>
       <c r="R122" t="n">
-        <v>7294120</v>
+        <v>7293912</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -12817,6 +12812,11 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>10m diam mycket riklig förekomst</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12940,32 +12940,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128819671</v>
+        <v>128834375</v>
       </c>
       <c r="B124" t="n">
-        <v>98619</v>
+        <v>79148</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12975,13 +12975,13 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>753685</v>
+        <v>754092</v>
       </c>
       <c r="R124" t="n">
-        <v>7294093</v>
+        <v>7293962</v>
       </c>
       <c r="S124" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13025,44 +13025,44 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128819650</v>
+        <v>128819697</v>
       </c>
       <c r="B125" t="n">
-        <v>80221</v>
+        <v>96738</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6458</v>
+        <v>2869</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13072,10 +13072,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>754166</v>
+        <v>754263</v>
       </c>
       <c r="R125" t="n">
-        <v>7293978</v>
+        <v>7293846</v>
       </c>
       <c r="S125" t="n">
         <v>3</v>
@@ -13134,10 +13134,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128819653</v>
+        <v>128834373</v>
       </c>
       <c r="B126" t="n">
-        <v>80221</v>
+        <v>91669</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13145,21 +13145,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6458</v>
+        <v>1588</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13169,13 +13169,13 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>754304</v>
+        <v>754056</v>
       </c>
       <c r="R126" t="n">
-        <v>7293805</v>
+        <v>7294109</v>
       </c>
       <c r="S126" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13219,22 +13219,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128819694</v>
+        <v>128819650</v>
       </c>
       <c r="B127" t="n">
-        <v>56898</v>
+        <v>80221</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13242,21 +13242,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13266,10 +13266,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>754139</v>
+        <v>754166</v>
       </c>
       <c r="R127" t="n">
-        <v>7294034</v>
+        <v>7293978</v>
       </c>
       <c r="S127" t="n">
         <v>3</v>
@@ -13328,32 +13328,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128819697</v>
+        <v>128834418</v>
       </c>
       <c r="B128" t="n">
-        <v>96738</v>
+        <v>80221</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>2869</v>
+        <v>6458</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13363,13 +13363,13 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>754263</v>
+        <v>754325</v>
       </c>
       <c r="R128" t="n">
-        <v>7293846</v>
+        <v>7293826</v>
       </c>
       <c r="S128" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13413,44 +13413,44 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128819683</v>
+        <v>128819653</v>
       </c>
       <c r="B129" t="n">
-        <v>98619</v>
+        <v>80221</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13460,10 +13460,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>754142</v>
+        <v>754304</v>
       </c>
       <c r="R129" t="n">
-        <v>7294040</v>
+        <v>7293805</v>
       </c>
       <c r="S129" t="n">
         <v>3</v>
@@ -13522,32 +13522,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128834453</v>
+        <v>128819694</v>
       </c>
       <c r="B130" t="n">
-        <v>98619</v>
+        <v>56898</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13557,13 +13557,13 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>753894</v>
+        <v>754139</v>
       </c>
       <c r="R130" t="n">
-        <v>7293894</v>
+        <v>7294034</v>
       </c>
       <c r="S130" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -13593,11 +13593,6 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>5mtr mycket rikligt bestånd</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13612,44 +13607,44 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128834375</v>
+        <v>128819671</v>
       </c>
       <c r="B131" t="n">
-        <v>79148</v>
+        <v>98619</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13659,13 +13654,13 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>754092</v>
+        <v>753685</v>
       </c>
       <c r="R131" t="n">
-        <v>7293962</v>
+        <v>7294093</v>
       </c>
       <c r="S131" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -13709,19 +13704,19 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128834452</v>
+        <v>128834453</v>
       </c>
       <c r="B132" t="n">
         <v>98619</v>
@@ -13756,10 +13751,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>753833</v>
+        <v>753894</v>
       </c>
       <c r="R132" t="n">
-        <v>7293877</v>
+        <v>7293894</v>
       </c>
       <c r="S132" t="n">
         <v>5</v>
@@ -13792,6 +13787,11 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>5mtr mycket rikligt bestånd</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -13818,32 +13818,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128834418</v>
+        <v>128834452</v>
       </c>
       <c r="B133" t="n">
-        <v>80221</v>
+        <v>98619</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13853,10 +13853,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>754325</v>
+        <v>753833</v>
       </c>
       <c r="R133" t="n">
-        <v>7293826</v>
+        <v>7293877</v>
       </c>
       <c r="S133" t="n">
         <v>5</v>
@@ -14012,32 +14012,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128834373</v>
+        <v>128819683</v>
       </c>
       <c r="B135" t="n">
-        <v>91669</v>
+        <v>98619</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1588</v>
+        <v>220787</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14047,13 +14047,13 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>754056</v>
+        <v>754142</v>
       </c>
       <c r="R135" t="n">
-        <v>7294109</v>
+        <v>7294040</v>
       </c>
       <c r="S135" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -14097,22 +14097,22 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128819651</v>
+        <v>128834372</v>
       </c>
       <c r="B136" t="n">
-        <v>80221</v>
+        <v>88763</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14120,21 +14120,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6458</v>
+        <v>4412</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14144,13 +14144,13 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>754220</v>
+        <v>754265</v>
       </c>
       <c r="R136" t="n">
-        <v>7293908</v>
+        <v>7293869</v>
       </c>
       <c r="S136" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -14194,19 +14194,19 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128819669</v>
+        <v>128819651</v>
       </c>
       <c r="B137" t="n">
         <v>80221</v>
@@ -14241,10 +14241,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>753872</v>
+        <v>754220</v>
       </c>
       <c r="R137" t="n">
-        <v>7294169</v>
+        <v>7293908</v>
       </c>
       <c r="S137" t="n">
         <v>3</v>
@@ -14303,7 +14303,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128819645</v>
+        <v>128819669</v>
       </c>
       <c r="B138" t="n">
         <v>80221</v>
@@ -14338,10 +14338,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>754081</v>
+        <v>753872</v>
       </c>
       <c r="R138" t="n">
-        <v>7294036</v>
+        <v>7294169</v>
       </c>
       <c r="S138" t="n">
         <v>3</v>
@@ -14400,7 +14400,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128819640</v>
+        <v>128819645</v>
       </c>
       <c r="B139" t="n">
         <v>80221</v>
@@ -14435,10 +14435,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>754021</v>
+        <v>754081</v>
       </c>
       <c r="R139" t="n">
-        <v>7294099</v>
+        <v>7294036</v>
       </c>
       <c r="S139" t="n">
         <v>3</v>
@@ -14479,7 +14479,6 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -14498,7 +14497,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128834402</v>
+        <v>128819640</v>
       </c>
       <c r="B140" t="n">
         <v>80221</v>
@@ -14533,13 +14532,13 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>753663</v>
+        <v>754021</v>
       </c>
       <c r="R140" t="n">
-        <v>7293971</v>
+        <v>7294099</v>
       </c>
       <c r="S140" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -14577,50 +14576,51 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128834498</v>
+        <v>128834402</v>
       </c>
       <c r="B141" t="n">
-        <v>80256</v>
+        <v>80221</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14630,10 +14630,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>754129</v>
+        <v>753663</v>
       </c>
       <c r="R141" t="n">
-        <v>7294101</v>
+        <v>7293971</v>
       </c>
       <c r="S141" t="n">
         <v>5</v>
@@ -14692,32 +14692,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128834372</v>
+        <v>128834498</v>
       </c>
       <c r="B142" t="n">
-        <v>88763</v>
+        <v>80256</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>4412</v>
+        <v>6463</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14727,10 +14727,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>754265</v>
+        <v>754129</v>
       </c>
       <c r="R142" t="n">
-        <v>7293869</v>
+        <v>7294101</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -14789,32 +14789,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128819667</v>
+        <v>128834379</v>
       </c>
       <c r="B143" t="n">
-        <v>80221</v>
+        <v>80250</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14824,13 +14824,13 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>754002</v>
+        <v>753674</v>
       </c>
       <c r="R143" t="n">
-        <v>7294106</v>
+        <v>7293973</v>
       </c>
       <c r="S143" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -14874,19 +14874,19 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128819643</v>
+        <v>128834412</v>
       </c>
       <c r="B144" t="n">
         <v>80221</v>
@@ -14921,13 +14921,13 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>753951</v>
+        <v>754096</v>
       </c>
       <c r="R144" t="n">
-        <v>7293999</v>
+        <v>7293963</v>
       </c>
       <c r="S144" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -14971,22 +14971,22 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128819636</v>
+        <v>128819667</v>
       </c>
       <c r="B145" t="n">
-        <v>57876</v>
+        <v>80221</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14994,21 +14994,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15018,10 +15018,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>754361</v>
+        <v>754002</v>
       </c>
       <c r="R145" t="n">
-        <v>7293841</v>
+        <v>7294106</v>
       </c>
       <c r="S145" t="n">
         <v>3</v>
@@ -15054,11 +15054,6 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>6 individer</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15085,32 +15080,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128819682</v>
+        <v>128819643</v>
       </c>
       <c r="B146" t="n">
-        <v>98619</v>
+        <v>80221</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15120,10 +15115,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>754120</v>
+        <v>753951</v>
       </c>
       <c r="R146" t="n">
-        <v>7294078</v>
+        <v>7293999</v>
       </c>
       <c r="S146" t="n">
         <v>3</v>
@@ -15156,11 +15151,6 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>Riktig förekomst</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15187,32 +15177,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128834379</v>
+        <v>128819636</v>
       </c>
       <c r="B147" t="n">
-        <v>80250</v>
+        <v>57876</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15222,13 +15212,13 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>753674</v>
+        <v>754361</v>
       </c>
       <c r="R147" t="n">
-        <v>7293973</v>
+        <v>7293841</v>
       </c>
       <c r="S147" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -15258,6 +15248,11 @@
       <c r="AA147" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>6 individer</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15272,44 +15267,44 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128834412</v>
+        <v>128834489</v>
       </c>
       <c r="B148" t="n">
-        <v>80221</v>
+        <v>98619</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15319,10 +15314,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>754096</v>
+        <v>754044</v>
       </c>
       <c r="R148" t="n">
-        <v>7293963</v>
+        <v>7294116</v>
       </c>
       <c r="S148" t="n">
         <v>5</v>
@@ -15381,7 +15376,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128834489</v>
+        <v>128834487</v>
       </c>
       <c r="B149" t="n">
         <v>98619</v>
@@ -15416,10 +15411,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>754044</v>
+        <v>754147</v>
       </c>
       <c r="R149" t="n">
-        <v>7294116</v>
+        <v>7294086</v>
       </c>
       <c r="S149" t="n">
         <v>5</v>
@@ -15478,7 +15473,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128834487</v>
+        <v>128819682</v>
       </c>
       <c r="B150" t="n">
         <v>98619</v>
@@ -15513,13 +15508,13 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>754147</v>
+        <v>754120</v>
       </c>
       <c r="R150" t="n">
-        <v>7294086</v>
+        <v>7294078</v>
       </c>
       <c r="S150" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -15549,6 +15544,11 @@
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>Riktig förekomst</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -15563,12 +15563,12 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
@@ -15672,32 +15672,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128834472</v>
+        <v>128834389</v>
       </c>
       <c r="B152" t="n">
-        <v>98619</v>
+        <v>80125</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15707,10 +15707,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>754273</v>
+        <v>754026</v>
       </c>
       <c r="R152" t="n">
-        <v>7293868</v>
+        <v>7293997</v>
       </c>
       <c r="S152" t="n">
         <v>5</v>
@@ -15743,11 +15743,6 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>Ca 8 m diam</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -15774,7 +15769,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128834475</v>
+        <v>128834472</v>
       </c>
       <c r="B153" t="n">
         <v>98619</v>
@@ -15809,10 +15804,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>754330</v>
+        <v>754273</v>
       </c>
       <c r="R153" t="n">
-        <v>7293823</v>
+        <v>7293868</v>
       </c>
       <c r="S153" t="n">
         <v>5</v>
@@ -15849,7 +15844,7 @@
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>4mtr diam</t>
+          <t>Ca 8 m diam</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -15876,32 +15871,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128834389</v>
+        <v>128834475</v>
       </c>
       <c r="B154" t="n">
-        <v>80125</v>
+        <v>98619</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -15911,10 +15906,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>754026</v>
+        <v>754330</v>
       </c>
       <c r="R154" t="n">
-        <v>7293997</v>
+        <v>7293823</v>
       </c>
       <c r="S154" t="n">
         <v>5</v>
@@ -15947,6 +15942,11 @@
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>4mtr diam</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -15973,32 +15973,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128819688</v>
+        <v>128834391</v>
       </c>
       <c r="B155" t="n">
-        <v>98619</v>
+        <v>97490</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16008,13 +16008,13 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>754342</v>
+        <v>754184</v>
       </c>
       <c r="R155" t="n">
-        <v>7293868</v>
+        <v>7294045</v>
       </c>
       <c r="S155" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -16058,44 +16058,44 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128819646</v>
+        <v>128834470</v>
       </c>
       <c r="B156" t="n">
-        <v>80221</v>
+        <v>98619</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16105,13 +16105,13 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>754143</v>
+        <v>754249</v>
       </c>
       <c r="R156" t="n">
-        <v>7294037</v>
+        <v>7293901</v>
       </c>
       <c r="S156" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -16155,44 +16155,44 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128834391</v>
+        <v>128819692</v>
       </c>
       <c r="B157" t="n">
-        <v>97490</v>
+        <v>98619</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16202,13 +16202,13 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>754184</v>
+        <v>754049</v>
       </c>
       <c r="R157" t="n">
-        <v>7294045</v>
+        <v>7294082</v>
       </c>
       <c r="S157" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -16238,6 +16238,11 @@
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>Stor förekomst</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16252,19 +16257,19 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128834470</v>
+        <v>128819691</v>
       </c>
       <c r="B158" t="n">
         <v>98619</v>
@@ -16299,13 +16304,13 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>754249</v>
+        <v>754222</v>
       </c>
       <c r="R158" t="n">
-        <v>7293901</v>
+        <v>7293998</v>
       </c>
       <c r="S158" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -16335,6 +16340,11 @@
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>Större område</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -16349,44 +16359,44 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128834413</v>
+        <v>128834485</v>
       </c>
       <c r="B159" t="n">
-        <v>80221</v>
+        <v>98619</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16396,10 +16406,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>754091</v>
+        <v>754182</v>
       </c>
       <c r="R159" t="n">
-        <v>7293941</v>
+        <v>7294034</v>
       </c>
       <c r="S159" t="n">
         <v>5</v>
@@ -16432,6 +16442,11 @@
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -16458,7 +16473,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128834485</v>
+        <v>128819688</v>
       </c>
       <c r="B160" t="n">
         <v>98619</v>
@@ -16493,13 +16508,13 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>754182</v>
+        <v>754342</v>
       </c>
       <c r="R160" t="n">
-        <v>7294034</v>
+        <v>7293868</v>
       </c>
       <c r="S160" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -16529,11 +16544,6 @@
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC160" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -16548,44 +16558,44 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128819692</v>
+        <v>128834413</v>
       </c>
       <c r="B161" t="n">
-        <v>98619</v>
+        <v>80221</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16595,13 +16605,13 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>754049</v>
+        <v>754091</v>
       </c>
       <c r="R161" t="n">
-        <v>7294082</v>
+        <v>7293941</v>
       </c>
       <c r="S161" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -16631,11 +16641,6 @@
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC161" t="inlineStr">
-        <is>
-          <t>Stor förekomst</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -16650,44 +16655,44 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128819691</v>
+        <v>128819646</v>
       </c>
       <c r="B162" t="n">
-        <v>98619</v>
+        <v>80221</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -16697,10 +16702,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>754222</v>
+        <v>754143</v>
       </c>
       <c r="R162" t="n">
-        <v>7293998</v>
+        <v>7294037</v>
       </c>
       <c r="S162" t="n">
         <v>3</v>
@@ -16733,11 +16738,6 @@
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC162" t="inlineStr">
-        <is>
-          <t>Större område</t>
         </is>
       </c>
       <c r="AD162" t="b">

--- a/artfynd/A 41034-2025 artfynd.xlsx
+++ b/artfynd/A 41034-2025 artfynd.xlsx
@@ -3688,32 +3688,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128834415</v>
+        <v>128819672</v>
       </c>
       <c r="B30" t="n">
-        <v>80221</v>
+        <v>98625</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3723,13 +3723,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>754084</v>
+        <v>753733</v>
       </c>
       <c r="R30" t="n">
-        <v>7293943</v>
+        <v>7294060</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3759,6 +3759,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Mycket Riklig förekomst</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3773,44 +3778,44 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128834411</v>
+        <v>128834473</v>
       </c>
       <c r="B31" t="n">
-        <v>80221</v>
+        <v>98625</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3820,10 +3825,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>754071</v>
+        <v>754284</v>
       </c>
       <c r="R31" t="n">
-        <v>7293962</v>
+        <v>7293849</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3882,10 +3887,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128834420</v>
+        <v>128834415</v>
       </c>
       <c r="B32" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3917,10 +3922,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>754338</v>
+        <v>754084</v>
       </c>
       <c r="R32" t="n">
-        <v>7293821</v>
+        <v>7293943</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3979,32 +3984,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128819672</v>
+        <v>128834411</v>
       </c>
       <c r="B33" t="n">
-        <v>98619</v>
+        <v>80225</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4014,13 +4019,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>753733</v>
+        <v>754071</v>
       </c>
       <c r="R33" t="n">
-        <v>7294060</v>
+        <v>7293962</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4050,11 +4055,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Mycket Riklig förekomst</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4069,44 +4069,44 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128834473</v>
+        <v>128834420</v>
       </c>
       <c r="B34" t="n">
-        <v>98619</v>
+        <v>80225</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4116,10 +4116,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>754284</v>
+        <v>754338</v>
       </c>
       <c r="R34" t="n">
-        <v>7293849</v>
+        <v>7293821</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4181,7 +4181,7 @@
         <v>128819673</v>
       </c>
       <c r="B35" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         <v>128834490</v>
       </c>
       <c r="B36" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>128834462</v>
       </c>
       <c r="B37" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>128834434</v>
       </c>
       <c r="B38" t="n">
-        <v>95469</v>
+        <v>95475</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
         <v>128834417</v>
       </c>
       <c r="B39" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         <v>128819696</v>
       </c>
       <c r="B40" t="n">
-        <v>80256</v>
+        <v>80260</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>128834405</v>
       </c>
       <c r="B41" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>128834390</v>
       </c>
       <c r="B42" t="n">
-        <v>80125</v>
+        <v>80129</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>128819663</v>
       </c>
       <c r="B43" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         <v>128834378</v>
       </c>
       <c r="B44" t="n">
-        <v>80250</v>
+        <v>80254</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         <v>128834410</v>
       </c>
       <c r="B45" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>128819642</v>
       </c>
       <c r="B46" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5457,7 +5457,7 @@
         <v>128834454</v>
       </c>
       <c r="B48" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>128819675</v>
       </c>
       <c r="B49" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5661,7 +5661,7 @@
         <v>128834406</v>
       </c>
       <c r="B50" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         <v>128834430</v>
       </c>
       <c r="B51" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         <v>128819690</v>
       </c>
       <c r="B52" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>128819693</v>
       </c>
       <c r="B53" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>128834484</v>
       </c>
       <c r="B54" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6153,32 +6153,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128819639</v>
+        <v>128834433</v>
       </c>
       <c r="B55" t="n">
-        <v>91790</v>
+        <v>95475</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>658</v>
+        <v>2387</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6188,13 +6188,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>754249</v>
+        <v>753867</v>
       </c>
       <c r="R55" t="n">
-        <v>7293891</v>
+        <v>7293877</v>
       </c>
       <c r="S55" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6224,11 +6224,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>10 fruktkroppar</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6243,22 +6238,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128834376</v>
+        <v>128819639</v>
       </c>
       <c r="B56" t="n">
-        <v>91494</v>
+        <v>91795</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6266,21 +6261,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6290,13 +6285,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>754253</v>
+        <v>754249</v>
       </c>
       <c r="R56" t="n">
-        <v>7293898</v>
+        <v>7293891</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6326,6 +6321,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>10 fruktkroppar</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6340,44 +6340,44 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128834433</v>
+        <v>128834376</v>
       </c>
       <c r="B57" t="n">
-        <v>95469</v>
+        <v>91499</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2387</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6387,10 +6387,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>753867</v>
+        <v>754253</v>
       </c>
       <c r="R57" t="n">
-        <v>7293877</v>
+        <v>7293898</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6449,10 +6449,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128834491</v>
+        <v>128819648</v>
       </c>
       <c r="B58" t="n">
-        <v>56898</v>
+        <v>80225</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6460,21 +6460,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6484,13 +6484,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>753881</v>
+        <v>754142</v>
       </c>
       <c r="R58" t="n">
-        <v>7293891</v>
+        <v>7293999</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6534,22 +6534,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128819648</v>
+        <v>128834404</v>
       </c>
       <c r="B59" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6581,13 +6581,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>754142</v>
+        <v>753693</v>
       </c>
       <c r="R59" t="n">
-        <v>7293999</v>
+        <v>7293978</v>
       </c>
       <c r="S59" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6631,22 +6631,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128834404</v>
+        <v>128834491</v>
       </c>
       <c r="B60" t="n">
-        <v>80221</v>
+        <v>56898</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6654,21 +6654,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>753693</v>
+        <v>753881</v>
       </c>
       <c r="R60" t="n">
-        <v>7293978</v>
+        <v>7293891</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6743,7 +6743,7 @@
         <v>128834446</v>
       </c>
       <c r="B61" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
         <v>128834449</v>
       </c>
       <c r="B62" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         <v>128819680</v>
       </c>
       <c r="B63" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         <v>128834407</v>
       </c>
       <c r="B64" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         <v>128834416</v>
       </c>
       <c r="B65" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>128834380</v>
       </c>
       <c r="B66" t="n">
-        <v>80250</v>
+        <v>80254</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7340,7 +7340,7 @@
         <v>128834457</v>
       </c>
       <c r="B67" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         <v>128834463</v>
       </c>
       <c r="B68" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>128834458</v>
       </c>
       <c r="B69" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7641,7 +7641,7 @@
         <v>128819677</v>
       </c>
       <c r="B70" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         <v>128834461</v>
       </c>
       <c r="B71" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>128819676</v>
       </c>
       <c r="B72" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
         <v>128834476</v>
       </c>
       <c r="B73" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         <v>128834443</v>
       </c>
       <c r="B74" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
         <v>128834456</v>
       </c>
       <c r="B75" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
         <v>128834409</v>
       </c>
       <c r="B76" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>128834401</v>
       </c>
       <c r="B77" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8432,7 +8432,7 @@
         <v>128819652</v>
       </c>
       <c r="B78" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>128834431</v>
       </c>
       <c r="B79" t="n">
-        <v>80257</v>
+        <v>80261</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8623,32 +8623,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128819685</v>
+        <v>128834497</v>
       </c>
       <c r="B80" t="n">
-        <v>98619</v>
+        <v>80260</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8658,13 +8658,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>754139</v>
+        <v>754176</v>
       </c>
       <c r="R80" t="n">
-        <v>7294003</v>
+        <v>7293924</v>
       </c>
       <c r="S80" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8708,44 +8708,44 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128834488</v>
+        <v>128819655</v>
       </c>
       <c r="B81" t="n">
-        <v>98619</v>
+        <v>80225</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8755,13 +8755,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>754049</v>
+        <v>754314</v>
       </c>
       <c r="R81" t="n">
-        <v>7294111</v>
+        <v>7293792</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8805,44 +8805,44 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128834466</v>
+        <v>128819664</v>
       </c>
       <c r="B82" t="n">
-        <v>98619</v>
+        <v>80225</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8852,13 +8852,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>754165</v>
+        <v>754142</v>
       </c>
       <c r="R82" t="n">
-        <v>7293935</v>
+        <v>7294080</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8888,11 +8888,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>2m diam</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8907,22 +8902,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128834497</v>
+        <v>128834381</v>
       </c>
       <c r="B83" t="n">
-        <v>80256</v>
+        <v>80254</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8930,21 +8925,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8954,10 +8949,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>754176</v>
+        <v>754177</v>
       </c>
       <c r="R83" t="n">
-        <v>7293924</v>
+        <v>7293925</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9016,10 +9011,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128819655</v>
+        <v>128819637</v>
       </c>
       <c r="B84" t="n">
-        <v>80221</v>
+        <v>57713</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9027,21 +9022,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9051,10 +9046,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>754314</v>
+        <v>753970</v>
       </c>
       <c r="R84" t="n">
-        <v>7293792</v>
+        <v>7294021</v>
       </c>
       <c r="S84" t="n">
         <v>3</v>
@@ -9113,10 +9108,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128819664</v>
+        <v>128834492</v>
       </c>
       <c r="B85" t="n">
-        <v>80221</v>
+        <v>56898</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9124,21 +9119,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9148,13 +9143,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>754142</v>
+        <v>753985</v>
       </c>
       <c r="R85" t="n">
-        <v>7294080</v>
+        <v>7294023</v>
       </c>
       <c r="S85" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9198,44 +9193,44 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128834381</v>
+        <v>128819685</v>
       </c>
       <c r="B86" t="n">
-        <v>80250</v>
+        <v>98625</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9245,13 +9240,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>754177</v>
+        <v>754139</v>
       </c>
       <c r="R86" t="n">
-        <v>7293925</v>
+        <v>7294003</v>
       </c>
       <c r="S86" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9295,44 +9290,44 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128834492</v>
+        <v>128834488</v>
       </c>
       <c r="B87" t="n">
-        <v>56898</v>
+        <v>98625</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9342,10 +9337,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>753985</v>
+        <v>754049</v>
       </c>
       <c r="R87" t="n">
-        <v>7294023</v>
+        <v>7294111</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9404,32 +9399,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128819637</v>
+        <v>128834466</v>
       </c>
       <c r="B88" t="n">
-        <v>57713</v>
+        <v>98625</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9439,13 +9434,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>753970</v>
+        <v>754165</v>
       </c>
       <c r="R88" t="n">
-        <v>7294021</v>
+        <v>7293935</v>
       </c>
       <c r="S88" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9475,6 +9470,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>2m diam</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9489,12 +9489,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -9504,7 +9504,7 @@
         <v>128834427</v>
       </c>
       <c r="B89" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9601,7 +9601,7 @@
         <v>128834432</v>
       </c>
       <c r="B90" t="n">
-        <v>80125</v>
+        <v>80129</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9698,7 +9698,7 @@
         <v>128819681</v>
       </c>
       <c r="B91" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9800,7 +9800,7 @@
         <v>128834459</v>
       </c>
       <c r="B92" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         <v>128834471</v>
       </c>
       <c r="B93" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9991,32 +9991,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128834435</v>
+        <v>128819654</v>
       </c>
       <c r="B94" t="n">
-        <v>95469</v>
+        <v>80225</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2387</v>
+        <v>6458</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10026,13 +10026,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>753941</v>
+        <v>754303</v>
       </c>
       <c r="R94" t="n">
-        <v>7294196</v>
+        <v>7293804</v>
       </c>
       <c r="S94" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10076,22 +10076,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128819654</v>
+        <v>128819649</v>
       </c>
       <c r="B95" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10123,10 +10123,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>754303</v>
+        <v>754149</v>
       </c>
       <c r="R95" t="n">
-        <v>7293804</v>
+        <v>7293983</v>
       </c>
       <c r="S95" t="n">
         <v>3</v>
@@ -10185,32 +10185,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128819649</v>
+        <v>128834435</v>
       </c>
       <c r="B96" t="n">
-        <v>80221</v>
+        <v>95475</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>2387</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10220,13 +10220,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>754149</v>
+        <v>753941</v>
       </c>
       <c r="R96" t="n">
-        <v>7293983</v>
+        <v>7294196</v>
       </c>
       <c r="S96" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10270,12 +10270,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
@@ -10285,7 +10285,7 @@
         <v>128834482</v>
       </c>
       <c r="B97" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10382,7 +10382,7 @@
         <v>128819686</v>
       </c>
       <c r="B98" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10479,7 +10479,7 @@
         <v>128834455</v>
       </c>
       <c r="B99" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10578,32 +10578,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128819644</v>
+        <v>128819679</v>
       </c>
       <c r="B100" t="n">
-        <v>80221</v>
+        <v>98625</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10613,10 +10613,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>754003</v>
+        <v>754015</v>
       </c>
       <c r="R100" t="n">
-        <v>7294039</v>
+        <v>7294040</v>
       </c>
       <c r="S100" t="n">
         <v>3</v>
@@ -10649,6 +10649,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10675,32 +10680,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128834399</v>
+        <v>128834451</v>
       </c>
       <c r="B101" t="n">
-        <v>80221</v>
+        <v>98625</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10710,10 +10715,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>753717</v>
+        <v>753769</v>
       </c>
       <c r="R101" t="n">
-        <v>7294108</v>
+        <v>7293962</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -10772,32 +10777,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128834428</v>
+        <v>128834448</v>
       </c>
       <c r="B102" t="n">
-        <v>80221</v>
+        <v>98625</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10807,10 +10812,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>754137</v>
+        <v>753692</v>
       </c>
       <c r="R102" t="n">
-        <v>7294102</v>
+        <v>7293978</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -10869,32 +10874,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128819679</v>
+        <v>128819644</v>
       </c>
       <c r="B103" t="n">
-        <v>98619</v>
+        <v>80225</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10904,10 +10909,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>754015</v>
+        <v>754003</v>
       </c>
       <c r="R103" t="n">
-        <v>7294040</v>
+        <v>7294039</v>
       </c>
       <c r="S103" t="n">
         <v>3</v>
@@ -10940,11 +10945,6 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10971,32 +10971,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128834451</v>
+        <v>128834399</v>
       </c>
       <c r="B104" t="n">
-        <v>98619</v>
+        <v>80225</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11006,10 +11006,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>753769</v>
+        <v>753717</v>
       </c>
       <c r="R104" t="n">
-        <v>7293962</v>
+        <v>7294108</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -11068,32 +11068,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128834448</v>
+        <v>128834428</v>
       </c>
       <c r="B105" t="n">
-        <v>98619</v>
+        <v>80225</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11103,10 +11103,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>753692</v>
+        <v>754137</v>
       </c>
       <c r="R105" t="n">
-        <v>7293978</v>
+        <v>7294102</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -11168,7 +11168,7 @@
         <v>128834436</v>
       </c>
       <c r="B106" t="n">
-        <v>95469</v>
+        <v>95475</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11265,7 +11265,7 @@
         <v>128834450</v>
       </c>
       <c r="B107" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11362,7 +11362,7 @@
         <v>128819670</v>
       </c>
       <c r="B108" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11464,7 +11464,7 @@
         <v>128819684</v>
       </c>
       <c r="B109" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11561,7 +11561,7 @@
         <v>128834465</v>
       </c>
       <c r="B110" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
         <v>128834445</v>
       </c>
       <c r="B111" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11760,7 +11760,7 @@
         <v>128834468</v>
       </c>
       <c r="B112" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11854,32 +11854,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128834408</v>
+        <v>128819689</v>
       </c>
       <c r="B113" t="n">
-        <v>80221</v>
+        <v>98625</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11889,13 +11889,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>754013</v>
+        <v>754240</v>
       </c>
       <c r="R113" t="n">
-        <v>7293996</v>
+        <v>7293924</v>
       </c>
       <c r="S113" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -11925,6 +11925,11 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Större förekomst</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11939,22 +11944,22 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128834419</v>
+        <v>128834408</v>
       </c>
       <c r="B114" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11986,10 +11991,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>754329</v>
+        <v>754013</v>
       </c>
       <c r="R114" t="n">
-        <v>7293829</v>
+        <v>7293996</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -12048,10 +12053,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128819668</v>
+        <v>128834419</v>
       </c>
       <c r="B115" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12083,13 +12088,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>753980</v>
+        <v>754329</v>
       </c>
       <c r="R115" t="n">
-        <v>7294135</v>
+        <v>7293829</v>
       </c>
       <c r="S115" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12133,22 +12138,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128819647</v>
+        <v>128819668</v>
       </c>
       <c r="B116" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12180,10 +12185,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>754139</v>
+        <v>753980</v>
       </c>
       <c r="R116" t="n">
-        <v>7294012</v>
+        <v>7294135</v>
       </c>
       <c r="S116" t="n">
         <v>3</v>
@@ -12242,32 +12247,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128819689</v>
+        <v>128819647</v>
       </c>
       <c r="B117" t="n">
-        <v>98619</v>
+        <v>80225</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12277,10 +12282,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>754240</v>
+        <v>754139</v>
       </c>
       <c r="R117" t="n">
-        <v>7293924</v>
+        <v>7294012</v>
       </c>
       <c r="S117" t="n">
         <v>3</v>
@@ -12313,11 +12318,6 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Större förekomst</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12344,48 +12344,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128834499</v>
+        <v>128834400</v>
       </c>
       <c r="B118" t="n">
-        <v>91866</v>
+        <v>80225</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1505</v>
+        <v>6458</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Stormansberget, Nb</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>754035</v>
+        <v>753636</v>
       </c>
       <c r="R118" t="n">
-        <v>7294132</v>
+        <v>7294018</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -12426,7 +12423,6 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -12445,10 +12441,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128834400</v>
+        <v>128834429</v>
       </c>
       <c r="B119" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12480,10 +12476,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>753636</v>
+        <v>754063</v>
       </c>
       <c r="R119" t="n">
-        <v>7294018</v>
+        <v>7294120</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -12542,32 +12538,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128834429</v>
+        <v>128834477</v>
       </c>
       <c r="B120" t="n">
-        <v>80221</v>
+        <v>98625</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12577,10 +12573,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>754063</v>
+        <v>754356</v>
       </c>
       <c r="R120" t="n">
-        <v>7294120</v>
+        <v>7293813</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -12613,6 +12609,11 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Ca 2m diam</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12639,10 +12640,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128834477</v>
+        <v>128834469</v>
       </c>
       <c r="B121" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12674,10 +12675,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>754356</v>
+        <v>754222</v>
       </c>
       <c r="R121" t="n">
-        <v>7293813</v>
+        <v>7293912</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -12714,7 +12715,7 @@
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Ca 2m diam</t>
+          <t>10m diam mycket riklig förekomst</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12741,10 +12742,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128834469</v>
+        <v>128834444</v>
       </c>
       <c r="B122" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12776,10 +12777,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>754222</v>
+        <v>753729</v>
       </c>
       <c r="R122" t="n">
-        <v>7293912</v>
+        <v>7294103</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -12812,11 +12813,6 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>10m diam mycket riklig förekomst</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12843,10 +12839,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128834444</v>
+        <v>128834499</v>
       </c>
       <c r="B123" t="n">
-        <v>98619</v>
+        <v>91871</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12854,34 +12850,37 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>220787</v>
+        <v>1505</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Stormansberget, Nb</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>753729</v>
+        <v>754035</v>
       </c>
       <c r="R123" t="n">
-        <v>7294103</v>
+        <v>7294132</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -12922,6 +12921,7 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -12943,7 +12943,7 @@
         <v>128834375</v>
       </c>
       <c r="B124" t="n">
-        <v>79148</v>
+        <v>79152</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13037,32 +13037,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128819697</v>
+        <v>128834373</v>
       </c>
       <c r="B125" t="n">
-        <v>96738</v>
+        <v>91674</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>2869</v>
+        <v>1588</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13072,13 +13072,13 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>754263</v>
+        <v>754056</v>
       </c>
       <c r="R125" t="n">
-        <v>7293846</v>
+        <v>7294109</v>
       </c>
       <c r="S125" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -13122,44 +13122,44 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128834373</v>
+        <v>128819697</v>
       </c>
       <c r="B126" t="n">
-        <v>91669</v>
+        <v>96744</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1588</v>
+        <v>2869</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13169,13 +13169,13 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>754056</v>
+        <v>754263</v>
       </c>
       <c r="R126" t="n">
-        <v>7294109</v>
+        <v>7293846</v>
       </c>
       <c r="S126" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13219,12 +13219,12 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
@@ -13234,7 +13234,7 @@
         <v>128819650</v>
       </c>
       <c r="B127" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13331,7 +13331,7 @@
         <v>128834418</v>
       </c>
       <c r="B128" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13428,7 +13428,7 @@
         <v>128819653</v>
       </c>
       <c r="B129" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13622,7 +13622,7 @@
         <v>128819671</v>
       </c>
       <c r="B131" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13719,7 +13719,7 @@
         <v>128834453</v>
       </c>
       <c r="B132" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13821,7 +13821,7 @@
         <v>128834452</v>
       </c>
       <c r="B133" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13918,7 +13918,7 @@
         <v>128834474</v>
       </c>
       <c r="B134" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14015,7 +14015,7 @@
         <v>128819683</v>
       </c>
       <c r="B135" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14112,7 +14112,7 @@
         <v>128834372</v>
       </c>
       <c r="B136" t="n">
-        <v>88763</v>
+        <v>88767</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
         <v>128819651</v>
       </c>
       <c r="B137" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14306,7 +14306,7 @@
         <v>128819669</v>
       </c>
       <c r="B138" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14403,7 +14403,7 @@
         <v>128819645</v>
       </c>
       <c r="B139" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14500,7 +14500,7 @@
         <v>128819640</v>
       </c>
       <c r="B140" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14598,7 +14598,7 @@
         <v>128834402</v>
       </c>
       <c r="B141" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14695,7 +14695,7 @@
         <v>128834498</v>
       </c>
       <c r="B142" t="n">
-        <v>80256</v>
+        <v>80260</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14792,7 +14792,7 @@
         <v>128834379</v>
       </c>
       <c r="B143" t="n">
-        <v>80250</v>
+        <v>80254</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>128834412</v>
       </c>
       <c r="B144" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14986,7 +14986,7 @@
         <v>128819667</v>
       </c>
       <c r="B145" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15083,7 +15083,7 @@
         <v>128819643</v>
       </c>
       <c r="B146" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15279,10 +15279,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128834489</v>
+        <v>128834487</v>
       </c>
       <c r="B148" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15314,10 +15314,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>754044</v>
+        <v>754147</v>
       </c>
       <c r="R148" t="n">
-        <v>7294116</v>
+        <v>7294086</v>
       </c>
       <c r="S148" t="n">
         <v>5</v>
@@ -15376,10 +15376,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128834487</v>
+        <v>128819682</v>
       </c>
       <c r="B149" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15411,13 +15411,13 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>754147</v>
+        <v>754120</v>
       </c>
       <c r="R149" t="n">
-        <v>7294086</v>
+        <v>7294078</v>
       </c>
       <c r="S149" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -15447,6 +15447,11 @@
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>Riktig förekomst</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15461,22 +15466,22 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128819682</v>
+        <v>128834489</v>
       </c>
       <c r="B150" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15508,13 +15513,13 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>754120</v>
+        <v>754044</v>
       </c>
       <c r="R150" t="n">
-        <v>7294078</v>
+        <v>7294116</v>
       </c>
       <c r="S150" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -15544,11 +15549,6 @@
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>Riktig förekomst</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -15563,44 +15563,44 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128834422</v>
+        <v>128834472</v>
       </c>
       <c r="B151" t="n">
-        <v>80221</v>
+        <v>98625</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15610,10 +15610,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>754355</v>
+        <v>754273</v>
       </c>
       <c r="R151" t="n">
-        <v>7293811</v>
+        <v>7293868</v>
       </c>
       <c r="S151" t="n">
         <v>5</v>
@@ -15646,6 +15646,11 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>Ca 8 m diam</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -15672,32 +15677,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128834389</v>
+        <v>128834475</v>
       </c>
       <c r="B152" t="n">
-        <v>80125</v>
+        <v>98625</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15707,10 +15712,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>754026</v>
+        <v>754330</v>
       </c>
       <c r="R152" t="n">
-        <v>7293997</v>
+        <v>7293823</v>
       </c>
       <c r="S152" t="n">
         <v>5</v>
@@ -15743,6 +15748,11 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>4mtr diam</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -15769,32 +15779,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128834472</v>
+        <v>128834422</v>
       </c>
       <c r="B153" t="n">
-        <v>98619</v>
+        <v>80225</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -15804,10 +15814,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>754273</v>
+        <v>754355</v>
       </c>
       <c r="R153" t="n">
-        <v>7293868</v>
+        <v>7293811</v>
       </c>
       <c r="S153" t="n">
         <v>5</v>
@@ -15840,11 +15850,6 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>Ca 8 m diam</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -15871,32 +15876,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128834475</v>
+        <v>128834389</v>
       </c>
       <c r="B154" t="n">
-        <v>98619</v>
+        <v>80129</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -15906,10 +15911,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>754330</v>
+        <v>754026</v>
       </c>
       <c r="R154" t="n">
-        <v>7293823</v>
+        <v>7293997</v>
       </c>
       <c r="S154" t="n">
         <v>5</v>
@@ -15942,11 +15947,6 @@
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>4mtr diam</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -15976,7 +15976,7 @@
         <v>128834391</v>
       </c>
       <c r="B155" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16070,32 +16070,32 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128834470</v>
+        <v>128834413</v>
       </c>
       <c r="B156" t="n">
-        <v>98619</v>
+        <v>80225</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16105,10 +16105,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>754249</v>
+        <v>754091</v>
       </c>
       <c r="R156" t="n">
-        <v>7293901</v>
+        <v>7293941</v>
       </c>
       <c r="S156" t="n">
         <v>5</v>
@@ -16167,32 +16167,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128819692</v>
+        <v>128819646</v>
       </c>
       <c r="B157" t="n">
-        <v>98619</v>
+        <v>80225</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16202,10 +16202,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>754049</v>
+        <v>754143</v>
       </c>
       <c r="R157" t="n">
-        <v>7294082</v>
+        <v>7294037</v>
       </c>
       <c r="S157" t="n">
         <v>3</v>
@@ -16238,11 +16238,6 @@
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>Stor förekomst</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16269,10 +16264,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128819691</v>
+        <v>128834470</v>
       </c>
       <c r="B158" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16304,13 +16299,13 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>754222</v>
+        <v>754249</v>
       </c>
       <c r="R158" t="n">
-        <v>7293998</v>
+        <v>7293901</v>
       </c>
       <c r="S158" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -16340,11 +16335,6 @@
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>Större område</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -16359,22 +16349,22 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128834485</v>
+        <v>128819692</v>
       </c>
       <c r="B159" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16406,13 +16396,13 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>754182</v>
+        <v>754049</v>
       </c>
       <c r="R159" t="n">
-        <v>7294034</v>
+        <v>7294082</v>
       </c>
       <c r="S159" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -16446,7 +16436,7 @@
       </c>
       <c r="AC159" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Stor förekomst</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -16461,22 +16451,22 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128819688</v>
+        <v>128819691</v>
       </c>
       <c r="B160" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16508,10 +16498,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>754342</v>
+        <v>754222</v>
       </c>
       <c r="R160" t="n">
-        <v>7293868</v>
+        <v>7293998</v>
       </c>
       <c r="S160" t="n">
         <v>3</v>
@@ -16544,6 +16534,11 @@
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>Större område</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -16570,32 +16565,32 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128834413</v>
+        <v>128834485</v>
       </c>
       <c r="B161" t="n">
-        <v>80221</v>
+        <v>98625</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16605,10 +16600,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>754091</v>
+        <v>754182</v>
       </c>
       <c r="R161" t="n">
-        <v>7293941</v>
+        <v>7294034</v>
       </c>
       <c r="S161" t="n">
         <v>5</v>
@@ -16641,6 +16636,11 @@
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -16667,32 +16667,32 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128819646</v>
+        <v>128819688</v>
       </c>
       <c r="B162" t="n">
-        <v>80221</v>
+        <v>98625</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -16702,10 +16702,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>754143</v>
+        <v>754342</v>
       </c>
       <c r="R162" t="n">
-        <v>7294037</v>
+        <v>7293868</v>
       </c>
       <c r="S162" t="n">
         <v>3</v>
@@ -16767,7 +16767,7 @@
         <v>128834383</v>
       </c>
       <c r="B163" t="n">
-        <v>80250</v>
+        <v>80254</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16864,7 +16864,7 @@
         <v>128834425</v>
       </c>
       <c r="B164" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>

--- a/artfynd/A 41034-2025 artfynd.xlsx
+++ b/artfynd/A 41034-2025 artfynd.xlsx
@@ -3688,32 +3688,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128819672</v>
+        <v>128834415</v>
       </c>
       <c r="B30" t="n">
-        <v>98625</v>
+        <v>80225</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3723,13 +3723,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>753733</v>
+        <v>754084</v>
       </c>
       <c r="R30" t="n">
-        <v>7294060</v>
+        <v>7293943</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3759,11 +3759,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Mycket Riklig förekomst</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3778,44 +3773,44 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128834473</v>
+        <v>128834411</v>
       </c>
       <c r="B31" t="n">
-        <v>98625</v>
+        <v>80225</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3825,10 +3820,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>754284</v>
+        <v>754071</v>
       </c>
       <c r="R31" t="n">
-        <v>7293849</v>
+        <v>7293962</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3887,7 +3882,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128834415</v>
+        <v>128834420</v>
       </c>
       <c r="B32" t="n">
         <v>80225</v>
@@ -3922,10 +3917,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>754084</v>
+        <v>754338</v>
       </c>
       <c r="R32" t="n">
-        <v>7293943</v>
+        <v>7293821</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3984,32 +3979,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128834411</v>
+        <v>128819672</v>
       </c>
       <c r="B33" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4019,13 +4014,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>754071</v>
+        <v>753733</v>
       </c>
       <c r="R33" t="n">
-        <v>7293962</v>
+        <v>7294060</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4055,6 +4050,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Mycket Riklig förekomst</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4069,44 +4069,44 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128834420</v>
+        <v>128819673</v>
       </c>
       <c r="B34" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4116,13 +4116,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>754338</v>
+        <v>753787</v>
       </c>
       <c r="R34" t="n">
-        <v>7293821</v>
+        <v>7294025</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4152,6 +4152,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Mycket riktig förekomst</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4166,22 +4171,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128819673</v>
+        <v>128834490</v>
       </c>
       <c r="B35" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4213,13 +4218,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>753787</v>
+        <v>754042</v>
       </c>
       <c r="R35" t="n">
-        <v>7294025</v>
+        <v>7294151</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4253,7 +4258,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Mycket riktig förekomst</t>
+          <t>Riklig förekomst ca 10m diam</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4268,22 +4273,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128834490</v>
+        <v>128834473</v>
       </c>
       <c r="B36" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4315,10 +4320,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>754042</v>
+        <v>754284</v>
       </c>
       <c r="R36" t="n">
-        <v>7294151</v>
+        <v>7293849</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4351,11 +4356,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Riklig förekomst ca 10m diam</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4382,32 +4382,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128834462</v>
+        <v>128834434</v>
       </c>
       <c r="B37" t="n">
-        <v>98625</v>
+        <v>95482</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>2387</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4417,10 +4417,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>754024</v>
+        <v>753879</v>
       </c>
       <c r="R37" t="n">
-        <v>7293998</v>
+        <v>7293890</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4479,10 +4479,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128834434</v>
+        <v>128819696</v>
       </c>
       <c r="B38" t="n">
-        <v>95475</v>
+        <v>80260</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4490,21 +4490,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2387</v>
+        <v>6463</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4514,13 +4514,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>753879</v>
+        <v>754302</v>
       </c>
       <c r="R38" t="n">
-        <v>7293890</v>
+        <v>7293804</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4564,44 +4564,44 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128834417</v>
+        <v>128834378</v>
       </c>
       <c r="B39" t="n">
-        <v>80225</v>
+        <v>80254</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>754171</v>
+        <v>753636</v>
       </c>
       <c r="R39" t="n">
-        <v>7293926</v>
+        <v>7294023</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4673,32 +4673,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128819696</v>
+        <v>128834417</v>
       </c>
       <c r="B40" t="n">
-        <v>80260</v>
+        <v>80225</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4708,13 +4708,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>754302</v>
+        <v>754171</v>
       </c>
       <c r="R40" t="n">
-        <v>7293804</v>
+        <v>7293926</v>
       </c>
       <c r="S40" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4758,12 +4758,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5061,32 +5061,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128834378</v>
+        <v>128834462</v>
       </c>
       <c r="B44" t="n">
-        <v>80254</v>
+        <v>98632</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5096,10 +5096,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>753636</v>
+        <v>754024</v>
       </c>
       <c r="R44" t="n">
-        <v>7294023</v>
+        <v>7293998</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5158,32 +5158,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128834410</v>
+        <v>128834454</v>
       </c>
       <c r="B45" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5193,10 +5193,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>754046</v>
+        <v>753898</v>
       </c>
       <c r="R45" t="n">
-        <v>7293956</v>
+        <v>7293898</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5229,6 +5229,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>3mtr diam</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5255,7 +5260,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128819642</v>
+        <v>128834410</v>
       </c>
       <c r="B46" t="n">
         <v>80225</v>
@@ -5290,13 +5295,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>753744</v>
+        <v>754046</v>
       </c>
       <c r="R46" t="n">
-        <v>7294126</v>
+        <v>7293956</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5340,22 +5345,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128834386</v>
+        <v>128819642</v>
       </c>
       <c r="B47" t="n">
-        <v>57713</v>
+        <v>80225</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5363,21 +5368,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5387,13 +5392,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>753889</v>
+        <v>753744</v>
       </c>
       <c r="R47" t="n">
-        <v>7294195</v>
+        <v>7294126</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5423,11 +5428,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Hack vid trädbas</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5442,22 +5442,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128834454</v>
+        <v>128819675</v>
       </c>
       <c r="B48" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5489,13 +5489,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>753898</v>
+        <v>753812</v>
       </c>
       <c r="R48" t="n">
-        <v>7293898</v>
+        <v>7293999</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>3mtr diam</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5544,44 +5544,44 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128819675</v>
+        <v>128834386</v>
       </c>
       <c r="B49" t="n">
-        <v>98625</v>
+        <v>57713</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5591,13 +5591,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>753812</v>
+        <v>753889</v>
       </c>
       <c r="R49" t="n">
-        <v>7293999</v>
+        <v>7294195</v>
       </c>
       <c r="S49" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Hack vid trädbas</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5646,12 +5646,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -5855,7 +5855,7 @@
         <v>128819690</v>
       </c>
       <c r="B52" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>128819693</v>
       </c>
       <c r="B53" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>128834484</v>
       </c>
       <c r="B54" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6153,32 +6153,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128834433</v>
+        <v>128834376</v>
       </c>
       <c r="B55" t="n">
-        <v>95475</v>
+        <v>91504</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2387</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6188,10 +6188,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>753867</v>
+        <v>754253</v>
       </c>
       <c r="R55" t="n">
-        <v>7293877</v>
+        <v>7293898</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6253,7 +6253,7 @@
         <v>128819639</v>
       </c>
       <c r="B56" t="n">
-        <v>91795</v>
+        <v>91800</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6352,32 +6352,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128834376</v>
+        <v>128834433</v>
       </c>
       <c r="B57" t="n">
-        <v>91499</v>
+        <v>95482</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>2387</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6387,10 +6387,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>754253</v>
+        <v>753867</v>
       </c>
       <c r="R57" t="n">
-        <v>7293898</v>
+        <v>7293877</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6449,32 +6449,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128819648</v>
+        <v>128834446</v>
       </c>
       <c r="B58" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6484,13 +6484,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>754142</v>
+        <v>753638</v>
       </c>
       <c r="R58" t="n">
-        <v>7293999</v>
+        <v>7293994</v>
       </c>
       <c r="S58" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6520,6 +6520,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Mycket rikligt bestånd</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6534,44 +6539,44 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128834404</v>
+        <v>128819680</v>
       </c>
       <c r="B59" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6581,13 +6586,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>753693</v>
+        <v>754079</v>
       </c>
       <c r="R59" t="n">
-        <v>7293978</v>
+        <v>7294043</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6617,6 +6622,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Rik förekomst</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6631,44 +6641,44 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128834491</v>
+        <v>128834449</v>
       </c>
       <c r="B60" t="n">
-        <v>56898</v>
+        <v>98632</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6678,10 +6688,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>753881</v>
+        <v>753732</v>
       </c>
       <c r="R60" t="n">
-        <v>7293891</v>
+        <v>7293989</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6714,6 +6724,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Mycket rikligt bestånd</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6740,32 +6755,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128834446</v>
+        <v>128819648</v>
       </c>
       <c r="B61" t="n">
-        <v>98625</v>
+        <v>80225</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6775,13 +6790,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>753638</v>
+        <v>754142</v>
       </c>
       <c r="R61" t="n">
-        <v>7293994</v>
+        <v>7293999</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6811,11 +6826,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Mycket rikligt bestånd</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6830,44 +6840,44 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128834449</v>
+        <v>128834404</v>
       </c>
       <c r="B62" t="n">
-        <v>98625</v>
+        <v>80225</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6877,10 +6887,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>753732</v>
+        <v>753693</v>
       </c>
       <c r="R62" t="n">
-        <v>7293989</v>
+        <v>7293978</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6913,11 +6923,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Mycket rikligt bestånd</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6944,32 +6949,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128819680</v>
+        <v>128834491</v>
       </c>
       <c r="B63" t="n">
-        <v>98625</v>
+        <v>56898</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6979,13 +6984,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>754079</v>
+        <v>753881</v>
       </c>
       <c r="R63" t="n">
-        <v>7294043</v>
+        <v>7293891</v>
       </c>
       <c r="S63" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7015,11 +7020,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Rik förekomst</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7034,12 +7034,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7340,7 +7340,7 @@
         <v>128834457</v>
       </c>
       <c r="B67" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         <v>128834463</v>
       </c>
       <c r="B68" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>128834458</v>
       </c>
       <c r="B69" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7638,10 +7638,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128819677</v>
+        <v>128834461</v>
       </c>
       <c r="B70" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7673,13 +7673,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>753875</v>
+        <v>753981</v>
       </c>
       <c r="R70" t="n">
-        <v>7294001</v>
+        <v>7294022</v>
       </c>
       <c r="S70" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7723,22 +7723,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128834461</v>
+        <v>128819677</v>
       </c>
       <c r="B71" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7770,13 +7770,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>753981</v>
+        <v>753875</v>
       </c>
       <c r="R71" t="n">
-        <v>7294022</v>
+        <v>7294001</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7820,44 +7820,44 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128819676</v>
+        <v>128834431</v>
       </c>
       <c r="B72" t="n">
-        <v>98625</v>
+        <v>80261</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7867,13 +7867,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>753836</v>
+        <v>754087</v>
       </c>
       <c r="R72" t="n">
-        <v>7293977</v>
+        <v>7293941</v>
       </c>
       <c r="S72" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7903,11 +7903,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7922,44 +7917,44 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128834476</v>
+        <v>128834409</v>
       </c>
       <c r="B73" t="n">
-        <v>98625</v>
+        <v>80225</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7969,10 +7964,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>754345</v>
+        <v>754042</v>
       </c>
       <c r="R73" t="n">
-        <v>7293808</v>
+        <v>7293966</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8005,11 +8000,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>3m diam</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8036,32 +8026,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128834443</v>
+        <v>128834401</v>
       </c>
       <c r="B74" t="n">
-        <v>98625</v>
+        <v>80225</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8071,10 +8061,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>754042</v>
+        <v>753629</v>
       </c>
       <c r="R74" t="n">
-        <v>7294129</v>
+        <v>7294009</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8107,11 +8097,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Måttlig förekomst 6m diam</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8138,32 +8123,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128834456</v>
+        <v>128819652</v>
       </c>
       <c r="B75" t="n">
-        <v>98625</v>
+        <v>80225</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8173,13 +8158,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>753917</v>
+        <v>754297</v>
       </c>
       <c r="R75" t="n">
-        <v>7293936</v>
+        <v>7293780</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8223,44 +8208,44 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128834409</v>
+        <v>128819676</v>
       </c>
       <c r="B76" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8270,13 +8255,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>754042</v>
+        <v>753836</v>
       </c>
       <c r="R76" t="n">
-        <v>7293966</v>
+        <v>7293977</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8306,6 +8291,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8320,44 +8310,44 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128834401</v>
+        <v>128834476</v>
       </c>
       <c r="B77" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8367,10 +8357,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>753629</v>
+        <v>754345</v>
       </c>
       <c r="R77" t="n">
-        <v>7294009</v>
+        <v>7293808</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8403,6 +8393,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>3m diam</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8429,32 +8424,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128819652</v>
+        <v>128834443</v>
       </c>
       <c r="B78" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8464,13 +8459,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>754297</v>
+        <v>754042</v>
       </c>
       <c r="R78" t="n">
-        <v>7293780</v>
+        <v>7294129</v>
       </c>
       <c r="S78" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8500,6 +8495,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Måttlig förekomst 6m diam</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8514,44 +8514,44 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128834431</v>
+        <v>128834456</v>
       </c>
       <c r="B79" t="n">
-        <v>80261</v>
+        <v>98632</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8561,10 +8561,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>754087</v>
+        <v>753917</v>
       </c>
       <c r="R79" t="n">
-        <v>7293941</v>
+        <v>7293936</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9208,7 +9208,7 @@
         <v>128819685</v>
       </c>
       <c r="B86" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9305,7 +9305,7 @@
         <v>128834488</v>
       </c>
       <c r="B87" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9402,7 +9402,7 @@
         <v>128834466</v>
       </c>
       <c r="B88" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9698,7 +9698,7 @@
         <v>128819681</v>
       </c>
       <c r="B91" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9800,7 +9800,7 @@
         <v>128834459</v>
       </c>
       <c r="B92" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         <v>128834471</v>
       </c>
       <c r="B93" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9991,32 +9991,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128819654</v>
+        <v>128834435</v>
       </c>
       <c r="B94" t="n">
-        <v>80225</v>
+        <v>95482</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6458</v>
+        <v>2387</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10026,13 +10026,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>754303</v>
+        <v>753941</v>
       </c>
       <c r="R94" t="n">
-        <v>7293804</v>
+        <v>7294196</v>
       </c>
       <c r="S94" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10076,19 +10076,19 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128819649</v>
+        <v>128819654</v>
       </c>
       <c r="B95" t="n">
         <v>80225</v>
@@ -10123,10 +10123,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>754149</v>
+        <v>754303</v>
       </c>
       <c r="R95" t="n">
-        <v>7293983</v>
+        <v>7293804</v>
       </c>
       <c r="S95" t="n">
         <v>3</v>
@@ -10185,32 +10185,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128834435</v>
+        <v>128819649</v>
       </c>
       <c r="B96" t="n">
-        <v>95475</v>
+        <v>80225</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2387</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10220,13 +10220,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>753941</v>
+        <v>754149</v>
       </c>
       <c r="R96" t="n">
-        <v>7294196</v>
+        <v>7293983</v>
       </c>
       <c r="S96" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10270,22 +10270,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128834482</v>
+        <v>128819686</v>
       </c>
       <c r="B97" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10317,13 +10317,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>754298</v>
+        <v>754145</v>
       </c>
       <c r="R97" t="n">
-        <v>7293981</v>
+        <v>7293994</v>
       </c>
       <c r="S97" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10367,22 +10367,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128819686</v>
+        <v>128834482</v>
       </c>
       <c r="B98" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10414,13 +10414,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>754145</v>
+        <v>754298</v>
       </c>
       <c r="R98" t="n">
-        <v>7293994</v>
+        <v>7293981</v>
       </c>
       <c r="S98" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10464,12 +10464,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
@@ -10479,7 +10479,7 @@
         <v>128834455</v>
       </c>
       <c r="B99" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10578,32 +10578,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128819679</v>
+        <v>128819644</v>
       </c>
       <c r="B100" t="n">
-        <v>98625</v>
+        <v>80225</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10613,10 +10613,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>754015</v>
+        <v>754003</v>
       </c>
       <c r="R100" t="n">
-        <v>7294040</v>
+        <v>7294039</v>
       </c>
       <c r="S100" t="n">
         <v>3</v>
@@ -10649,11 +10649,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10680,32 +10675,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128834451</v>
+        <v>128834399</v>
       </c>
       <c r="B101" t="n">
-        <v>98625</v>
+        <v>80225</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10715,10 +10710,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>753769</v>
+        <v>753717</v>
       </c>
       <c r="R101" t="n">
-        <v>7293962</v>
+        <v>7294108</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -10777,32 +10772,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128834448</v>
+        <v>128834428</v>
       </c>
       <c r="B102" t="n">
-        <v>98625</v>
+        <v>80225</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10812,10 +10807,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>753692</v>
+        <v>754137</v>
       </c>
       <c r="R102" t="n">
-        <v>7293978</v>
+        <v>7294102</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -10874,32 +10869,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128819644</v>
+        <v>128819679</v>
       </c>
       <c r="B103" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10909,10 +10904,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>754003</v>
+        <v>754015</v>
       </c>
       <c r="R103" t="n">
-        <v>7294039</v>
+        <v>7294040</v>
       </c>
       <c r="S103" t="n">
         <v>3</v>
@@ -10945,6 +10940,11 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10971,32 +10971,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128834399</v>
+        <v>128834451</v>
       </c>
       <c r="B104" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11006,10 +11006,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>753717</v>
+        <v>753769</v>
       </c>
       <c r="R104" t="n">
-        <v>7294108</v>
+        <v>7293962</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -11068,32 +11068,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128834428</v>
+        <v>128834448</v>
       </c>
       <c r="B105" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11103,10 +11103,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>754137</v>
+        <v>753692</v>
       </c>
       <c r="R105" t="n">
-        <v>7294102</v>
+        <v>7293978</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -11168,7 +11168,7 @@
         <v>128834436</v>
       </c>
       <c r="B106" t="n">
-        <v>95475</v>
+        <v>95482</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11265,7 +11265,7 @@
         <v>128834450</v>
       </c>
       <c r="B107" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11362,7 +11362,7 @@
         <v>128819670</v>
       </c>
       <c r="B108" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11464,7 +11464,7 @@
         <v>128819684</v>
       </c>
       <c r="B109" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11558,10 +11558,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128834465</v>
+        <v>128834445</v>
       </c>
       <c r="B110" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11593,10 +11593,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>754148</v>
+        <v>753685</v>
       </c>
       <c r="R110" t="n">
-        <v>7293932</v>
+        <v>7294059</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -11629,6 +11629,11 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>3mtr diam</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11655,10 +11660,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128834445</v>
+        <v>128834465</v>
       </c>
       <c r="B111" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11690,10 +11695,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>753685</v>
+        <v>754148</v>
       </c>
       <c r="R111" t="n">
-        <v>7294059</v>
+        <v>7293932</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -11726,11 +11731,6 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>3mtr diam</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11760,7 +11760,7 @@
         <v>128834468</v>
       </c>
       <c r="B112" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11854,32 +11854,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128819689</v>
+        <v>128834408</v>
       </c>
       <c r="B113" t="n">
-        <v>98625</v>
+        <v>80225</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11889,13 +11889,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>754240</v>
+        <v>754013</v>
       </c>
       <c r="R113" t="n">
-        <v>7293924</v>
+        <v>7293996</v>
       </c>
       <c r="S113" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -11925,11 +11925,6 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Större förekomst</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11944,19 +11939,19 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128834408</v>
+        <v>128834419</v>
       </c>
       <c r="B114" t="n">
         <v>80225</v>
@@ -11991,10 +11986,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>754013</v>
+        <v>754329</v>
       </c>
       <c r="R114" t="n">
-        <v>7293996</v>
+        <v>7293829</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -12053,7 +12048,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128834419</v>
+        <v>128819668</v>
       </c>
       <c r="B115" t="n">
         <v>80225</v>
@@ -12088,13 +12083,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>754329</v>
+        <v>753980</v>
       </c>
       <c r="R115" t="n">
-        <v>7293829</v>
+        <v>7294135</v>
       </c>
       <c r="S115" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12138,19 +12133,19 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128819668</v>
+        <v>128819647</v>
       </c>
       <c r="B116" t="n">
         <v>80225</v>
@@ -12185,10 +12180,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>753980</v>
+        <v>754139</v>
       </c>
       <c r="R116" t="n">
-        <v>7294135</v>
+        <v>7294012</v>
       </c>
       <c r="S116" t="n">
         <v>3</v>
@@ -12247,32 +12242,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128819647</v>
+        <v>128819689</v>
       </c>
       <c r="B117" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12282,10 +12277,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>754139</v>
+        <v>754240</v>
       </c>
       <c r="R117" t="n">
-        <v>7294012</v>
+        <v>7293924</v>
       </c>
       <c r="S117" t="n">
         <v>3</v>
@@ -12318,6 +12313,11 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Större förekomst</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12344,32 +12344,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128834400</v>
+        <v>128834469</v>
       </c>
       <c r="B118" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12379,10 +12379,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>753636</v>
+        <v>754222</v>
       </c>
       <c r="R118" t="n">
-        <v>7294018</v>
+        <v>7293912</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -12415,6 +12415,11 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>10m diam mycket riklig förekomst</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12441,32 +12446,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128834429</v>
+        <v>128834444</v>
       </c>
       <c r="B119" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12476,10 +12481,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>754063</v>
+        <v>753729</v>
       </c>
       <c r="R119" t="n">
-        <v>7294120</v>
+        <v>7294103</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -12541,7 +12546,7 @@
         <v>128834477</v>
       </c>
       <c r="B120" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12640,10 +12645,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128834469</v>
+        <v>128834499</v>
       </c>
       <c r="B121" t="n">
-        <v>98625</v>
+        <v>91876</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12651,34 +12656,37 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>220787</v>
+        <v>1505</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Stormansberget, Nb</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>754222</v>
+        <v>754035</v>
       </c>
       <c r="R121" t="n">
-        <v>7293912</v>
+        <v>7294132</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -12713,17 +12721,13 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>10m diam mycket riklig förekomst</t>
-        </is>
-      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -12742,32 +12746,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128834444</v>
+        <v>128834400</v>
       </c>
       <c r="B122" t="n">
-        <v>98625</v>
+        <v>80225</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12777,10 +12781,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>753729</v>
+        <v>753636</v>
       </c>
       <c r="R122" t="n">
-        <v>7294103</v>
+        <v>7294018</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -12839,48 +12843,45 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128834499</v>
+        <v>128834429</v>
       </c>
       <c r="B123" t="n">
-        <v>91871</v>
+        <v>80225</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1505</v>
+        <v>6458</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Stormansberget, Nb</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>754035</v>
+        <v>754063</v>
       </c>
       <c r="R123" t="n">
-        <v>7294132</v>
+        <v>7294120</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -12921,7 +12922,6 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -12940,32 +12940,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128834375</v>
+        <v>128819671</v>
       </c>
       <c r="B124" t="n">
-        <v>79152</v>
+        <v>98632</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12975,13 +12975,13 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>754092</v>
+        <v>753685</v>
       </c>
       <c r="R124" t="n">
-        <v>7293962</v>
+        <v>7294093</v>
       </c>
       <c r="S124" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13025,44 +13025,44 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128834373</v>
+        <v>128834452</v>
       </c>
       <c r="B125" t="n">
-        <v>91674</v>
+        <v>98632</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1588</v>
+        <v>220787</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13072,10 +13072,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>754056</v>
+        <v>753833</v>
       </c>
       <c r="R125" t="n">
-        <v>7294109</v>
+        <v>7293877</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -13134,32 +13134,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128819697</v>
+        <v>128819683</v>
       </c>
       <c r="B126" t="n">
-        <v>96744</v>
+        <v>98632</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13169,10 +13169,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>754263</v>
+        <v>754142</v>
       </c>
       <c r="R126" t="n">
-        <v>7293846</v>
+        <v>7294040</v>
       </c>
       <c r="S126" t="n">
         <v>3</v>
@@ -13231,10 +13231,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128819650</v>
+        <v>128834375</v>
       </c>
       <c r="B127" t="n">
-        <v>80225</v>
+        <v>79152</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13242,21 +13242,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13266,13 +13266,13 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>754166</v>
+        <v>754092</v>
       </c>
       <c r="R127" t="n">
-        <v>7293978</v>
+        <v>7293962</v>
       </c>
       <c r="S127" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -13316,22 +13316,22 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128834418</v>
+        <v>128834373</v>
       </c>
       <c r="B128" t="n">
-        <v>80225</v>
+        <v>91679</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13339,21 +13339,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6458</v>
+        <v>1588</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13363,10 +13363,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>754325</v>
+        <v>754056</v>
       </c>
       <c r="R128" t="n">
-        <v>7293826</v>
+        <v>7294109</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -13425,32 +13425,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128819653</v>
+        <v>128819697</v>
       </c>
       <c r="B129" t="n">
-        <v>80225</v>
+        <v>96751</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6458</v>
+        <v>2869</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13460,10 +13460,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>754304</v>
+        <v>754263</v>
       </c>
       <c r="R129" t="n">
-        <v>7293805</v>
+        <v>7293846</v>
       </c>
       <c r="S129" t="n">
         <v>3</v>
@@ -13522,10 +13522,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128819694</v>
+        <v>128819650</v>
       </c>
       <c r="B130" t="n">
-        <v>56898</v>
+        <v>80225</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13533,21 +13533,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13557,10 +13557,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>754139</v>
+        <v>754166</v>
       </c>
       <c r="R130" t="n">
-        <v>7294034</v>
+        <v>7293978</v>
       </c>
       <c r="S130" t="n">
         <v>3</v>
@@ -13619,32 +13619,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128819671</v>
+        <v>128834418</v>
       </c>
       <c r="B131" t="n">
-        <v>98625</v>
+        <v>80225</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13654,13 +13654,13 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>753685</v>
+        <v>754325</v>
       </c>
       <c r="R131" t="n">
-        <v>7294093</v>
+        <v>7293826</v>
       </c>
       <c r="S131" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -13704,44 +13704,44 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128834453</v>
+        <v>128819653</v>
       </c>
       <c r="B132" t="n">
-        <v>98625</v>
+        <v>80225</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13751,13 +13751,13 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>753894</v>
+        <v>754304</v>
       </c>
       <c r="R132" t="n">
-        <v>7293894</v>
+        <v>7293805</v>
       </c>
       <c r="S132" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -13787,11 +13787,6 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>5mtr mycket rikligt bestånd</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -13806,22 +13801,22 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128834452</v>
+        <v>128834474</v>
       </c>
       <c r="B133" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13853,10 +13848,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>753833</v>
+        <v>754313</v>
       </c>
       <c r="R133" t="n">
-        <v>7293877</v>
+        <v>7293834</v>
       </c>
       <c r="S133" t="n">
         <v>5</v>
@@ -13915,32 +13910,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128834474</v>
+        <v>128819694</v>
       </c>
       <c r="B134" t="n">
-        <v>98625</v>
+        <v>56898</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13950,13 +13945,13 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>754313</v>
+        <v>754139</v>
       </c>
       <c r="R134" t="n">
-        <v>7293834</v>
+        <v>7294034</v>
       </c>
       <c r="S134" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14000,22 +13995,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128819683</v>
+        <v>128834453</v>
       </c>
       <c r="B135" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14047,13 +14042,13 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>754142</v>
+        <v>753894</v>
       </c>
       <c r="R135" t="n">
-        <v>7294040</v>
+        <v>7293894</v>
       </c>
       <c r="S135" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -14083,6 +14078,11 @@
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>5mtr mycket rikligt bestånd</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14097,44 +14097,44 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128834372</v>
+        <v>128834498</v>
       </c>
       <c r="B136" t="n">
-        <v>88767</v>
+        <v>80260</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>4412</v>
+        <v>6463</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14144,10 +14144,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>754265</v>
+        <v>754129</v>
       </c>
       <c r="R136" t="n">
-        <v>7293869</v>
+        <v>7294101</v>
       </c>
       <c r="S136" t="n">
         <v>5</v>
@@ -14692,32 +14692,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128834498</v>
+        <v>128834372</v>
       </c>
       <c r="B142" t="n">
-        <v>80260</v>
+        <v>88768</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6463</v>
+        <v>4412</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14727,10 +14727,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>754129</v>
+        <v>754265</v>
       </c>
       <c r="R142" t="n">
-        <v>7294101</v>
+        <v>7293869</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -15279,10 +15279,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128834487</v>
+        <v>128834489</v>
       </c>
       <c r="B148" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15314,10 +15314,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>754147</v>
+        <v>754044</v>
       </c>
       <c r="R148" t="n">
-        <v>7294086</v>
+        <v>7294116</v>
       </c>
       <c r="S148" t="n">
         <v>5</v>
@@ -15379,7 +15379,7 @@
         <v>128819682</v>
       </c>
       <c r="B149" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15478,10 +15478,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128834489</v>
+        <v>128834487</v>
       </c>
       <c r="B150" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15513,10 +15513,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>754044</v>
+        <v>754147</v>
       </c>
       <c r="R150" t="n">
-        <v>7294116</v>
+        <v>7294086</v>
       </c>
       <c r="S150" t="n">
         <v>5</v>
@@ -15578,7 +15578,7 @@
         <v>128834472</v>
       </c>
       <c r="B151" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15680,7 +15680,7 @@
         <v>128834475</v>
       </c>
       <c r="B152" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15973,32 +15973,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128834391</v>
+        <v>128834470</v>
       </c>
       <c r="B155" t="n">
-        <v>97496</v>
+        <v>98632</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16008,10 +16008,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>754184</v>
+        <v>754249</v>
       </c>
       <c r="R155" t="n">
-        <v>7294045</v>
+        <v>7293901</v>
       </c>
       <c r="S155" t="n">
         <v>5</v>
@@ -16264,10 +16264,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128834470</v>
+        <v>128819692</v>
       </c>
       <c r="B158" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16299,13 +16299,13 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>754249</v>
+        <v>754049</v>
       </c>
       <c r="R158" t="n">
-        <v>7293901</v>
+        <v>7294082</v>
       </c>
       <c r="S158" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -16335,6 +16335,11 @@
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>Stor förekomst</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -16349,22 +16354,22 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128819692</v>
+        <v>128819691</v>
       </c>
       <c r="B159" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16396,10 +16401,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>754049</v>
+        <v>754222</v>
       </c>
       <c r="R159" t="n">
-        <v>7294082</v>
+        <v>7293998</v>
       </c>
       <c r="S159" t="n">
         <v>3</v>
@@ -16436,7 +16441,7 @@
       </c>
       <c r="AC159" t="inlineStr">
         <is>
-          <t>Stor förekomst</t>
+          <t>Större område</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -16463,10 +16468,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128819691</v>
+        <v>128834485</v>
       </c>
       <c r="B160" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16498,13 +16503,13 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>754222</v>
+        <v>754182</v>
       </c>
       <c r="R160" t="n">
-        <v>7293998</v>
+        <v>7294034</v>
       </c>
       <c r="S160" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -16538,7 +16543,7 @@
       </c>
       <c r="AC160" t="inlineStr">
         <is>
-          <t>Större område</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -16553,22 +16558,22 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128834485</v>
+        <v>128819688</v>
       </c>
       <c r="B161" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16600,13 +16605,13 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>754182</v>
+        <v>754342</v>
       </c>
       <c r="R161" t="n">
-        <v>7294034</v>
+        <v>7293868</v>
       </c>
       <c r="S161" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -16636,11 +16641,6 @@
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC161" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -16655,44 +16655,44 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128819688</v>
+        <v>128834391</v>
       </c>
       <c r="B162" t="n">
-        <v>98625</v>
+        <v>97503</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -16702,13 +16702,13 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>754342</v>
+        <v>754184</v>
       </c>
       <c r="R162" t="n">
-        <v>7293868</v>
+        <v>7294045</v>
       </c>
       <c r="S162" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -16752,12 +16752,12 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>

--- a/artfynd/A 41034-2025 artfynd.xlsx
+++ b/artfynd/A 41034-2025 artfynd.xlsx
@@ -3688,7 +3688,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128834415</v>
+        <v>128834411</v>
       </c>
       <c r="B30" t="n">
         <v>80225</v>
@@ -3723,10 +3723,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>754084</v>
+        <v>754071</v>
       </c>
       <c r="R30" t="n">
-        <v>7293943</v>
+        <v>7293962</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3785,7 +3785,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128834411</v>
+        <v>128834420</v>
       </c>
       <c r="B31" t="n">
         <v>80225</v>
@@ -3820,10 +3820,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>754071</v>
+        <v>754338</v>
       </c>
       <c r="R31" t="n">
-        <v>7293962</v>
+        <v>7293821</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3882,7 +3882,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128834420</v>
+        <v>128834415</v>
       </c>
       <c r="B32" t="n">
         <v>80225</v>
@@ -3917,10 +3917,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>754338</v>
+        <v>754084</v>
       </c>
       <c r="R32" t="n">
-        <v>7293821</v>
+        <v>7293943</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4081,7 +4081,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128819673</v>
+        <v>128834473</v>
       </c>
       <c r="B34" t="n">
         <v>98632</v>
@@ -4116,13 +4116,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>753787</v>
+        <v>754284</v>
       </c>
       <c r="R34" t="n">
-        <v>7294025</v>
+        <v>7293849</v>
       </c>
       <c r="S34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4152,11 +4152,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Mycket riktig förekomst</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4171,19 +4166,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128834490</v>
+        <v>128819673</v>
       </c>
       <c r="B35" t="n">
         <v>98632</v>
@@ -4218,13 +4213,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>754042</v>
+        <v>753787</v>
       </c>
       <c r="R35" t="n">
-        <v>7294151</v>
+        <v>7294025</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4258,7 +4253,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Riklig förekomst ca 10m diam</t>
+          <t>Mycket riktig förekomst</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4273,19 +4268,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128834473</v>
+        <v>128834490</v>
       </c>
       <c r="B36" t="n">
         <v>98632</v>
@@ -4320,10 +4315,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>754284</v>
+        <v>754042</v>
       </c>
       <c r="R36" t="n">
-        <v>7293849</v>
+        <v>7294151</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4356,6 +4351,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Riklig förekomst ca 10m diam</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4479,32 +4479,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128819696</v>
+        <v>128834417</v>
       </c>
       <c r="B38" t="n">
-        <v>80260</v>
+        <v>80225</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4514,13 +4514,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>754302</v>
+        <v>754171</v>
       </c>
       <c r="R38" t="n">
-        <v>7293804</v>
+        <v>7293926</v>
       </c>
       <c r="S38" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4564,22 +4564,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128834378</v>
+        <v>128834390</v>
       </c>
       <c r="B39" t="n">
-        <v>80254</v>
+        <v>80129</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4587,21 +4587,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>753636</v>
+        <v>754064</v>
       </c>
       <c r="R39" t="n">
-        <v>7294023</v>
+        <v>7294121</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4673,7 +4673,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128834417</v>
+        <v>128819663</v>
       </c>
       <c r="B40" t="n">
         <v>80225</v>
@@ -4708,13 +4708,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>754171</v>
+        <v>754152</v>
       </c>
       <c r="R40" t="n">
-        <v>7293926</v>
+        <v>7294076</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4758,44 +4758,44 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128834405</v>
+        <v>128819696</v>
       </c>
       <c r="B41" t="n">
-        <v>80225</v>
+        <v>80260</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4805,13 +4805,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>753772</v>
+        <v>754302</v>
       </c>
       <c r="R41" t="n">
-        <v>7293986</v>
+        <v>7293804</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4855,44 +4855,44 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128834390</v>
+        <v>128834405</v>
       </c>
       <c r="B42" t="n">
-        <v>80129</v>
+        <v>80225</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>754064</v>
+        <v>753772</v>
       </c>
       <c r="R42" t="n">
-        <v>7294121</v>
+        <v>7293986</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4964,32 +4964,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128819663</v>
+        <v>128834378</v>
       </c>
       <c r="B43" t="n">
-        <v>80225</v>
+        <v>80254</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4999,13 +4999,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>754152</v>
+        <v>753636</v>
       </c>
       <c r="R43" t="n">
-        <v>7294076</v>
+        <v>7294023</v>
       </c>
       <c r="S43" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5049,12 +5049,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5158,32 +5158,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128834454</v>
+        <v>128834386</v>
       </c>
       <c r="B45" t="n">
-        <v>98632</v>
+        <v>57713</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5193,10 +5193,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>753898</v>
+        <v>753889</v>
       </c>
       <c r="R45" t="n">
-        <v>7293898</v>
+        <v>7294195</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>3mtr diam</t>
+          <t>Hack vid trädbas</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5454,7 +5454,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128819675</v>
+        <v>128834454</v>
       </c>
       <c r="B48" t="n">
         <v>98632</v>
@@ -5489,13 +5489,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>753812</v>
+        <v>753898</v>
       </c>
       <c r="R48" t="n">
-        <v>7293999</v>
+        <v>7293898</v>
       </c>
       <c r="S48" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>3mtr diam</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5544,44 +5544,44 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128834386</v>
+        <v>128819675</v>
       </c>
       <c r="B49" t="n">
-        <v>57713</v>
+        <v>98632</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5591,13 +5591,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>753889</v>
+        <v>753812</v>
       </c>
       <c r="R49" t="n">
-        <v>7294195</v>
+        <v>7293999</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Hack vid trädbas</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5646,12 +5646,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -6449,32 +6449,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128834446</v>
+        <v>128819648</v>
       </c>
       <c r="B58" t="n">
-        <v>98632</v>
+        <v>80225</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6484,13 +6484,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>753638</v>
+        <v>754142</v>
       </c>
       <c r="R58" t="n">
-        <v>7293994</v>
+        <v>7293999</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6520,11 +6520,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Mycket rikligt bestånd</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6539,44 +6534,44 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128819680</v>
+        <v>128834404</v>
       </c>
       <c r="B59" t="n">
-        <v>98632</v>
+        <v>80225</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6586,13 +6581,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>754079</v>
+        <v>753693</v>
       </c>
       <c r="R59" t="n">
-        <v>7294043</v>
+        <v>7293978</v>
       </c>
       <c r="S59" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6622,11 +6617,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Rik förekomst</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6641,19 +6631,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128834449</v>
+        <v>128834446</v>
       </c>
       <c r="B60" t="n">
         <v>98632</v>
@@ -6688,10 +6678,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>753732</v>
+        <v>753638</v>
       </c>
       <c r="R60" t="n">
-        <v>7293989</v>
+        <v>7293994</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6755,32 +6745,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128819648</v>
+        <v>128834449</v>
       </c>
       <c r="B61" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6790,13 +6780,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>754142</v>
+        <v>753732</v>
       </c>
       <c r="R61" t="n">
-        <v>7293999</v>
+        <v>7293989</v>
       </c>
       <c r="S61" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6826,6 +6816,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Mycket rikligt bestånd</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6840,44 +6835,44 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128834404</v>
+        <v>128819680</v>
       </c>
       <c r="B62" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6887,13 +6882,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>753693</v>
+        <v>754079</v>
       </c>
       <c r="R62" t="n">
-        <v>7293978</v>
+        <v>7294043</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6923,6 +6918,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Rik förekomst</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6937,12 +6937,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7046,32 +7046,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128834407</v>
+        <v>128834457</v>
       </c>
       <c r="B64" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7081,10 +7081,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>753989</v>
+        <v>753947</v>
       </c>
       <c r="R64" t="n">
-        <v>7294010</v>
+        <v>7293964</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7117,6 +7117,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>5mtr diam</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7143,32 +7148,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128834416</v>
+        <v>128834463</v>
       </c>
       <c r="B65" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7178,10 +7183,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>754148</v>
+        <v>754071</v>
       </c>
       <c r="R65" t="n">
-        <v>7293935</v>
+        <v>7293964</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7240,32 +7245,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128834380</v>
+        <v>128834458</v>
       </c>
       <c r="B66" t="n">
-        <v>80254</v>
+        <v>98632</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7275,10 +7280,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>754091</v>
+        <v>753959</v>
       </c>
       <c r="R66" t="n">
-        <v>7293941</v>
+        <v>7294022</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7311,6 +7316,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>3m diam</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7337,7 +7347,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128834457</v>
+        <v>128819677</v>
       </c>
       <c r="B67" t="n">
         <v>98632</v>
@@ -7372,13 +7382,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>753947</v>
+        <v>753875</v>
       </c>
       <c r="R67" t="n">
-        <v>7293964</v>
+        <v>7294001</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7408,11 +7418,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>5mtr diam</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7427,19 +7432,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128834463</v>
+        <v>128834461</v>
       </c>
       <c r="B68" t="n">
         <v>98632</v>
@@ -7474,10 +7479,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>754071</v>
+        <v>753981</v>
       </c>
       <c r="R68" t="n">
-        <v>7293964</v>
+        <v>7294022</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7536,32 +7541,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128834458</v>
+        <v>128834407</v>
       </c>
       <c r="B69" t="n">
-        <v>98632</v>
+        <v>80225</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7571,10 +7576,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>753959</v>
+        <v>753989</v>
       </c>
       <c r="R69" t="n">
-        <v>7294022</v>
+        <v>7294010</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7607,11 +7612,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>3m diam</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7638,32 +7638,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128834461</v>
+        <v>128834416</v>
       </c>
       <c r="B70" t="n">
-        <v>98632</v>
+        <v>80225</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7673,10 +7673,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>753981</v>
+        <v>754148</v>
       </c>
       <c r="R70" t="n">
-        <v>7294022</v>
+        <v>7293935</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7735,32 +7735,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128819677</v>
+        <v>128834380</v>
       </c>
       <c r="B71" t="n">
-        <v>98632</v>
+        <v>80254</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7770,13 +7770,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>753875</v>
+        <v>754091</v>
       </c>
       <c r="R71" t="n">
-        <v>7294001</v>
+        <v>7293941</v>
       </c>
       <c r="S71" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7820,44 +7820,44 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128834431</v>
+        <v>128834409</v>
       </c>
       <c r="B72" t="n">
-        <v>80261</v>
+        <v>80225</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7867,10 +7867,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>754087</v>
+        <v>754042</v>
       </c>
       <c r="R72" t="n">
-        <v>7293941</v>
+        <v>7293966</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7929,32 +7929,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128834409</v>
+        <v>128834431</v>
       </c>
       <c r="B73" t="n">
-        <v>80225</v>
+        <v>80261</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7964,10 +7964,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>754042</v>
+        <v>754087</v>
       </c>
       <c r="R73" t="n">
-        <v>7293966</v>
+        <v>7293941</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8623,32 +8623,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128834497</v>
+        <v>128819637</v>
       </c>
       <c r="B80" t="n">
-        <v>80260</v>
+        <v>57713</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8658,13 +8658,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>754176</v>
+        <v>753970</v>
       </c>
       <c r="R80" t="n">
-        <v>7293924</v>
+        <v>7294021</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8708,12 +8708,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -8914,10 +8914,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128834381</v>
+        <v>128834497</v>
       </c>
       <c r="B83" t="n">
-        <v>80254</v>
+        <v>80260</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8925,21 +8925,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8949,10 +8949,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>754177</v>
+        <v>754176</v>
       </c>
       <c r="R83" t="n">
-        <v>7293925</v>
+        <v>7293924</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9011,32 +9011,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128819637</v>
+        <v>128834381</v>
       </c>
       <c r="B84" t="n">
-        <v>57713</v>
+        <v>80254</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9046,13 +9046,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>753970</v>
+        <v>754177</v>
       </c>
       <c r="R84" t="n">
-        <v>7294021</v>
+        <v>7293925</v>
       </c>
       <c r="S84" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9096,12 +9096,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -10088,32 +10088,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128819654</v>
+        <v>128834482</v>
       </c>
       <c r="B95" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10123,13 +10123,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>754303</v>
+        <v>754298</v>
       </c>
       <c r="R95" t="n">
-        <v>7293804</v>
+        <v>7293981</v>
       </c>
       <c r="S95" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10173,44 +10173,44 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128819649</v>
+        <v>128819686</v>
       </c>
       <c r="B96" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10220,10 +10220,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>754149</v>
+        <v>754145</v>
       </c>
       <c r="R96" t="n">
-        <v>7293983</v>
+        <v>7293994</v>
       </c>
       <c r="S96" t="n">
         <v>3</v>
@@ -10282,7 +10282,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128819686</v>
+        <v>128834455</v>
       </c>
       <c r="B97" t="n">
         <v>98632</v>
@@ -10317,13 +10317,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>754145</v>
+        <v>753903</v>
       </c>
       <c r="R97" t="n">
-        <v>7293994</v>
+        <v>7293910</v>
       </c>
       <c r="S97" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10353,6 +10353,11 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>4mtr diam</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10367,44 +10372,44 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128834482</v>
+        <v>128819654</v>
       </c>
       <c r="B98" t="n">
-        <v>98632</v>
+        <v>80225</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10414,13 +10419,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>754298</v>
+        <v>754303</v>
       </c>
       <c r="R98" t="n">
-        <v>7293981</v>
+        <v>7293804</v>
       </c>
       <c r="S98" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10464,44 +10469,44 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128834455</v>
+        <v>128819649</v>
       </c>
       <c r="B99" t="n">
-        <v>98632</v>
+        <v>80225</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10511,13 +10516,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>753903</v>
+        <v>754149</v>
       </c>
       <c r="R99" t="n">
-        <v>7293910</v>
+        <v>7293983</v>
       </c>
       <c r="S99" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10547,11 +10552,6 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>4mtr diam</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10566,44 +10566,44 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128819644</v>
+        <v>128819679</v>
       </c>
       <c r="B100" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10613,10 +10613,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>754003</v>
+        <v>754015</v>
       </c>
       <c r="R100" t="n">
-        <v>7294039</v>
+        <v>7294040</v>
       </c>
       <c r="S100" t="n">
         <v>3</v>
@@ -10649,6 +10649,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10675,32 +10680,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128834399</v>
+        <v>128834451</v>
       </c>
       <c r="B101" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10710,10 +10715,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>753717</v>
+        <v>753769</v>
       </c>
       <c r="R101" t="n">
-        <v>7294108</v>
+        <v>7293962</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -10772,32 +10777,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128834428</v>
+        <v>128834448</v>
       </c>
       <c r="B102" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10807,10 +10812,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>754137</v>
+        <v>753692</v>
       </c>
       <c r="R102" t="n">
-        <v>7294102</v>
+        <v>7293978</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -10869,32 +10874,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128819679</v>
+        <v>128819644</v>
       </c>
       <c r="B103" t="n">
-        <v>98632</v>
+        <v>80225</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10904,10 +10909,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>754015</v>
+        <v>754003</v>
       </c>
       <c r="R103" t="n">
-        <v>7294040</v>
+        <v>7294039</v>
       </c>
       <c r="S103" t="n">
         <v>3</v>
@@ -10940,11 +10945,6 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10971,32 +10971,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128834451</v>
+        <v>128834399</v>
       </c>
       <c r="B104" t="n">
-        <v>98632</v>
+        <v>80225</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11006,10 +11006,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>753769</v>
+        <v>753717</v>
       </c>
       <c r="R104" t="n">
-        <v>7293962</v>
+        <v>7294108</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -11068,32 +11068,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128834448</v>
+        <v>128834428</v>
       </c>
       <c r="B105" t="n">
-        <v>98632</v>
+        <v>80225</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11103,10 +11103,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>753692</v>
+        <v>754137</v>
       </c>
       <c r="R105" t="n">
-        <v>7293978</v>
+        <v>7294102</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -11558,7 +11558,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128834445</v>
+        <v>128834465</v>
       </c>
       <c r="B110" t="n">
         <v>98632</v>
@@ -11593,10 +11593,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>753685</v>
+        <v>754148</v>
       </c>
       <c r="R110" t="n">
-        <v>7294059</v>
+        <v>7293932</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -11629,11 +11629,6 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>3mtr diam</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11660,7 +11655,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128834465</v>
+        <v>128834445</v>
       </c>
       <c r="B111" t="n">
         <v>98632</v>
@@ -11695,10 +11690,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>754148</v>
+        <v>753685</v>
       </c>
       <c r="R111" t="n">
-        <v>7293932</v>
+        <v>7294059</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -11731,6 +11726,11 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>3mtr diam</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11951,32 +11951,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128834419</v>
+        <v>128819689</v>
       </c>
       <c r="B114" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11986,13 +11986,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>754329</v>
+        <v>754240</v>
       </c>
       <c r="R114" t="n">
-        <v>7293829</v>
+        <v>7293924</v>
       </c>
       <c r="S114" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12022,6 +12022,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Större förekomst</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12036,19 +12041,19 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128819668</v>
+        <v>128834419</v>
       </c>
       <c r="B115" t="n">
         <v>80225</v>
@@ -12083,13 +12088,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>753980</v>
+        <v>754329</v>
       </c>
       <c r="R115" t="n">
-        <v>7294135</v>
+        <v>7293829</v>
       </c>
       <c r="S115" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12133,19 +12138,19 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128819647</v>
+        <v>128819668</v>
       </c>
       <c r="B116" t="n">
         <v>80225</v>
@@ -12180,10 +12185,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>754139</v>
+        <v>753980</v>
       </c>
       <c r="R116" t="n">
-        <v>7294012</v>
+        <v>7294135</v>
       </c>
       <c r="S116" t="n">
         <v>3</v>
@@ -12242,32 +12247,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128819689</v>
+        <v>128819647</v>
       </c>
       <c r="B117" t="n">
-        <v>98632</v>
+        <v>80225</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12277,10 +12282,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>754240</v>
+        <v>754139</v>
       </c>
       <c r="R117" t="n">
-        <v>7293924</v>
+        <v>7294012</v>
       </c>
       <c r="S117" t="n">
         <v>3</v>
@@ -12313,11 +12318,6 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Större förekomst</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12344,10 +12344,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128834469</v>
+        <v>128834499</v>
       </c>
       <c r="B118" t="n">
-        <v>98632</v>
+        <v>91876</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12355,34 +12355,37 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220787</v>
+        <v>1505</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Stormansberget, Nb</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>754222</v>
+        <v>754035</v>
       </c>
       <c r="R118" t="n">
-        <v>7293912</v>
+        <v>7294132</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -12417,17 +12420,13 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>10m diam mycket riklig förekomst</t>
-        </is>
-      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
       <c r="AE118" t="b">
         <v>0</v>
       </c>
+      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -12446,32 +12445,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128834444</v>
+        <v>128834400</v>
       </c>
       <c r="B119" t="n">
-        <v>98632</v>
+        <v>80225</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12481,10 +12480,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>753729</v>
+        <v>753636</v>
       </c>
       <c r="R119" t="n">
-        <v>7294103</v>
+        <v>7294018</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -12543,32 +12542,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128834477</v>
+        <v>128834429</v>
       </c>
       <c r="B120" t="n">
-        <v>98632</v>
+        <v>80225</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12578,10 +12577,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>754356</v>
+        <v>754063</v>
       </c>
       <c r="R120" t="n">
-        <v>7293813</v>
+        <v>7294120</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -12614,11 +12613,6 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Ca 2m diam</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12645,10 +12639,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128834499</v>
+        <v>128834477</v>
       </c>
       <c r="B121" t="n">
-        <v>91876</v>
+        <v>98632</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12656,37 +12650,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1505</v>
+        <v>220787</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Stormansberget, Nb</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>754035</v>
+        <v>754356</v>
       </c>
       <c r="R121" t="n">
-        <v>7294132</v>
+        <v>7293813</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -12721,13 +12712,17 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Ca 2m diam</t>
+        </is>
+      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -12746,32 +12741,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128834400</v>
+        <v>128834469</v>
       </c>
       <c r="B122" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12781,10 +12776,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>753636</v>
+        <v>754222</v>
       </c>
       <c r="R122" t="n">
-        <v>7294018</v>
+        <v>7293912</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -12817,6 +12812,11 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>10m diam mycket riklig förekomst</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12843,32 +12843,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128834429</v>
+        <v>128834444</v>
       </c>
       <c r="B123" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12878,10 +12878,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>754063</v>
+        <v>753729</v>
       </c>
       <c r="R123" t="n">
-        <v>7294120</v>
+        <v>7294103</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -12940,32 +12940,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128819671</v>
+        <v>128834373</v>
       </c>
       <c r="B124" t="n">
-        <v>98632</v>
+        <v>91679</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>220787</v>
+        <v>1588</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12975,13 +12975,13 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>753685</v>
+        <v>754056</v>
       </c>
       <c r="R124" t="n">
-        <v>7294093</v>
+        <v>7294109</v>
       </c>
       <c r="S124" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13025,44 +13025,44 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128834452</v>
+        <v>128819694</v>
       </c>
       <c r="B125" t="n">
-        <v>98632</v>
+        <v>56898</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13072,13 +13072,13 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>753833</v>
+        <v>754139</v>
       </c>
       <c r="R125" t="n">
-        <v>7293877</v>
+        <v>7294034</v>
       </c>
       <c r="S125" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -13122,19 +13122,19 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128819683</v>
+        <v>128834452</v>
       </c>
       <c r="B126" t="n">
         <v>98632</v>
@@ -13169,13 +13169,13 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>754142</v>
+        <v>753833</v>
       </c>
       <c r="R126" t="n">
-        <v>7294040</v>
+        <v>7293877</v>
       </c>
       <c r="S126" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13219,44 +13219,44 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128834375</v>
+        <v>128834474</v>
       </c>
       <c r="B127" t="n">
-        <v>79152</v>
+        <v>98632</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13266,10 +13266,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>754092</v>
+        <v>754313</v>
       </c>
       <c r="R127" t="n">
-        <v>7293962</v>
+        <v>7293834</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -13328,32 +13328,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128834373</v>
+        <v>128819683</v>
       </c>
       <c r="B128" t="n">
-        <v>91679</v>
+        <v>98632</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1588</v>
+        <v>220787</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13363,13 +13363,13 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>754056</v>
+        <v>754142</v>
       </c>
       <c r="R128" t="n">
-        <v>7294109</v>
+        <v>7294040</v>
       </c>
       <c r="S128" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13413,44 +13413,44 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128819697</v>
+        <v>128834375</v>
       </c>
       <c r="B129" t="n">
-        <v>96751</v>
+        <v>79152</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>2869</v>
+        <v>185</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13460,13 +13460,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>754263</v>
+        <v>754092</v>
       </c>
       <c r="R129" t="n">
-        <v>7293846</v>
+        <v>7293962</v>
       </c>
       <c r="S129" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -13510,44 +13510,44 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128819650</v>
+        <v>128819697</v>
       </c>
       <c r="B130" t="n">
-        <v>80225</v>
+        <v>96751</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6458</v>
+        <v>2869</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13557,10 +13557,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>754166</v>
+        <v>754263</v>
       </c>
       <c r="R130" t="n">
-        <v>7293978</v>
+        <v>7293846</v>
       </c>
       <c r="S130" t="n">
         <v>3</v>
@@ -13619,7 +13619,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128834418</v>
+        <v>128819650</v>
       </c>
       <c r="B131" t="n">
         <v>80225</v>
@@ -13654,13 +13654,13 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>754325</v>
+        <v>754166</v>
       </c>
       <c r="R131" t="n">
-        <v>7293826</v>
+        <v>7293978</v>
       </c>
       <c r="S131" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -13704,19 +13704,19 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128819653</v>
+        <v>128834418</v>
       </c>
       <c r="B132" t="n">
         <v>80225</v>
@@ -13751,13 +13751,13 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>754304</v>
+        <v>754325</v>
       </c>
       <c r="R132" t="n">
-        <v>7293805</v>
+        <v>7293826</v>
       </c>
       <c r="S132" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -13801,44 +13801,44 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128834474</v>
+        <v>128819653</v>
       </c>
       <c r="B133" t="n">
-        <v>98632</v>
+        <v>80225</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13848,13 +13848,13 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>754313</v>
+        <v>754304</v>
       </c>
       <c r="R133" t="n">
-        <v>7293834</v>
+        <v>7293805</v>
       </c>
       <c r="S133" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -13898,44 +13898,44 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128819694</v>
+        <v>128819671</v>
       </c>
       <c r="B134" t="n">
-        <v>56898</v>
+        <v>98632</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13945,10 +13945,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>754139</v>
+        <v>753685</v>
       </c>
       <c r="R134" t="n">
-        <v>7294034</v>
+        <v>7294093</v>
       </c>
       <c r="S134" t="n">
         <v>3</v>
@@ -14109,32 +14109,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128834498</v>
+        <v>128834372</v>
       </c>
       <c r="B136" t="n">
-        <v>80260</v>
+        <v>88768</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6463</v>
+        <v>4412</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14144,10 +14144,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>754129</v>
+        <v>754265</v>
       </c>
       <c r="R136" t="n">
-        <v>7294101</v>
+        <v>7293869</v>
       </c>
       <c r="S136" t="n">
         <v>5</v>
@@ -14692,32 +14692,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128834372</v>
+        <v>128834498</v>
       </c>
       <c r="B142" t="n">
-        <v>88768</v>
+        <v>80260</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>4412</v>
+        <v>6463</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14727,10 +14727,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>754265</v>
+        <v>754129</v>
       </c>
       <c r="R142" t="n">
-        <v>7293869</v>
+        <v>7294101</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -14789,32 +14789,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128834379</v>
+        <v>128834489</v>
       </c>
       <c r="B143" t="n">
-        <v>80254</v>
+        <v>98632</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14824,10 +14824,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>753674</v>
+        <v>754044</v>
       </c>
       <c r="R143" t="n">
-        <v>7293973</v>
+        <v>7294116</v>
       </c>
       <c r="S143" t="n">
         <v>5</v>
@@ -14886,32 +14886,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128834412</v>
+        <v>128834487</v>
       </c>
       <c r="B144" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -14921,10 +14921,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>754096</v>
+        <v>754147</v>
       </c>
       <c r="R144" t="n">
-        <v>7293963</v>
+        <v>7294086</v>
       </c>
       <c r="S144" t="n">
         <v>5</v>
@@ -14983,32 +14983,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128819667</v>
+        <v>128819682</v>
       </c>
       <c r="B145" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15018,10 +15018,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>754002</v>
+        <v>754120</v>
       </c>
       <c r="R145" t="n">
-        <v>7294106</v>
+        <v>7294078</v>
       </c>
       <c r="S145" t="n">
         <v>3</v>
@@ -15054,6 +15054,11 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>Riktig förekomst</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15080,7 +15085,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128819643</v>
+        <v>128819667</v>
       </c>
       <c r="B146" t="n">
         <v>80225</v>
@@ -15115,10 +15120,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>753951</v>
+        <v>754002</v>
       </c>
       <c r="R146" t="n">
-        <v>7293999</v>
+        <v>7294106</v>
       </c>
       <c r="S146" t="n">
         <v>3</v>
@@ -15177,10 +15182,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128819636</v>
+        <v>128819643</v>
       </c>
       <c r="B147" t="n">
-        <v>57876</v>
+        <v>80225</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15188,21 +15193,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15212,10 +15217,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>754361</v>
+        <v>753951</v>
       </c>
       <c r="R147" t="n">
-        <v>7293841</v>
+        <v>7293999</v>
       </c>
       <c r="S147" t="n">
         <v>3</v>
@@ -15248,11 +15253,6 @@
       <c r="AA147" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC147" t="inlineStr">
-        <is>
-          <t>6 individer</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15279,32 +15279,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128834489</v>
+        <v>128834379</v>
       </c>
       <c r="B148" t="n">
-        <v>98632</v>
+        <v>80254</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15314,10 +15314,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>754044</v>
+        <v>753674</v>
       </c>
       <c r="R148" t="n">
-        <v>7294116</v>
+        <v>7293973</v>
       </c>
       <c r="S148" t="n">
         <v>5</v>
@@ -15376,32 +15376,32 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128819682</v>
+        <v>128834412</v>
       </c>
       <c r="B149" t="n">
-        <v>98632</v>
+        <v>80225</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15411,13 +15411,13 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>754120</v>
+        <v>754096</v>
       </c>
       <c r="R149" t="n">
-        <v>7294078</v>
+        <v>7293963</v>
       </c>
       <c r="S149" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -15447,11 +15447,6 @@
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>Riktig förekomst</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15466,44 +15461,44 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128834487</v>
+        <v>128819636</v>
       </c>
       <c r="B150" t="n">
-        <v>98632</v>
+        <v>57876</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15513,13 +15508,13 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>754147</v>
+        <v>754361</v>
       </c>
       <c r="R150" t="n">
-        <v>7294086</v>
+        <v>7293841</v>
       </c>
       <c r="S150" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -15549,6 +15544,11 @@
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>6 individer</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -15563,12 +15563,12 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
@@ -16070,32 +16070,32 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128834413</v>
+        <v>128819692</v>
       </c>
       <c r="B156" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16105,13 +16105,13 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>754091</v>
+        <v>754049</v>
       </c>
       <c r="R156" t="n">
-        <v>7293941</v>
+        <v>7294082</v>
       </c>
       <c r="S156" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -16141,6 +16141,11 @@
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>Stor förekomst</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16155,44 +16160,44 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128819646</v>
+        <v>128819691</v>
       </c>
       <c r="B157" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16202,10 +16207,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>754143</v>
+        <v>754222</v>
       </c>
       <c r="R157" t="n">
-        <v>7294037</v>
+        <v>7293998</v>
       </c>
       <c r="S157" t="n">
         <v>3</v>
@@ -16238,6 +16243,11 @@
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>Större område</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16264,7 +16274,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128819692</v>
+        <v>128834485</v>
       </c>
       <c r="B158" t="n">
         <v>98632</v>
@@ -16299,13 +16309,13 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>754049</v>
+        <v>754182</v>
       </c>
       <c r="R158" t="n">
-        <v>7294082</v>
+        <v>7294034</v>
       </c>
       <c r="S158" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -16339,7 +16349,7 @@
       </c>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>Stor förekomst</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -16354,19 +16364,19 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128819691</v>
+        <v>128819688</v>
       </c>
       <c r="B159" t="n">
         <v>98632</v>
@@ -16401,10 +16411,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>754222</v>
+        <v>754342</v>
       </c>
       <c r="R159" t="n">
-        <v>7293998</v>
+        <v>7293868</v>
       </c>
       <c r="S159" t="n">
         <v>3</v>
@@ -16437,11 +16447,6 @@
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>Större område</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -16468,32 +16473,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128834485</v>
+        <v>128834413</v>
       </c>
       <c r="B160" t="n">
-        <v>98632</v>
+        <v>80225</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16503,10 +16508,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>754182</v>
+        <v>754091</v>
       </c>
       <c r="R160" t="n">
-        <v>7294034</v>
+        <v>7293941</v>
       </c>
       <c r="S160" t="n">
         <v>5</v>
@@ -16539,11 +16544,6 @@
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC160" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -16570,32 +16570,32 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128819688</v>
+        <v>128819646</v>
       </c>
       <c r="B161" t="n">
-        <v>98632</v>
+        <v>80225</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16605,10 +16605,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>754342</v>
+        <v>754143</v>
       </c>
       <c r="R161" t="n">
-        <v>7293868</v>
+        <v>7294037</v>
       </c>
       <c r="S161" t="n">
         <v>3</v>
@@ -16764,32 +16764,32 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>128834383</v>
+        <v>128834425</v>
       </c>
       <c r="B163" t="n">
-        <v>80254</v>
+        <v>80225</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -16799,10 +16799,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>754143</v>
+        <v>754321</v>
       </c>
       <c r="R163" t="n">
-        <v>7294098</v>
+        <v>7293944</v>
       </c>
       <c r="S163" t="n">
         <v>5</v>
@@ -16861,32 +16861,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128834425</v>
+        <v>128834383</v>
       </c>
       <c r="B164" t="n">
-        <v>80225</v>
+        <v>80254</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -16896,10 +16896,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>754321</v>
+        <v>754143</v>
       </c>
       <c r="R164" t="n">
-        <v>7293944</v>
+        <v>7294098</v>
       </c>
       <c r="S164" t="n">
         <v>5</v>

--- a/artfynd/A 41034-2025 artfynd.xlsx
+++ b/artfynd/A 41034-2025 artfynd.xlsx
@@ -3688,7 +3688,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128834411</v>
+        <v>128834415</v>
       </c>
       <c r="B30" t="n">
         <v>80225</v>
@@ -3723,10 +3723,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>754071</v>
+        <v>754084</v>
       </c>
       <c r="R30" t="n">
-        <v>7293962</v>
+        <v>7293943</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3882,32 +3882,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128834415</v>
+        <v>128819672</v>
       </c>
       <c r="B32" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3917,13 +3917,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>754084</v>
+        <v>753733</v>
       </c>
       <c r="R32" t="n">
-        <v>7293943</v>
+        <v>7294060</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3953,6 +3953,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Mycket Riklig förekomst</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3967,19 +3972,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128819672</v>
+        <v>128834473</v>
       </c>
       <c r="B33" t="n">
         <v>98632</v>
@@ -4014,13 +4019,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>753733</v>
+        <v>754284</v>
       </c>
       <c r="R33" t="n">
-        <v>7294060</v>
+        <v>7293849</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4050,11 +4055,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Mycket Riklig förekomst</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4069,19 +4069,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128834473</v>
+        <v>128819673</v>
       </c>
       <c r="B34" t="n">
         <v>98632</v>
@@ -4116,13 +4116,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>754284</v>
+        <v>753787</v>
       </c>
       <c r="R34" t="n">
-        <v>7293849</v>
+        <v>7294025</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4152,6 +4152,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Mycket riktig förekomst</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4166,19 +4171,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128819673</v>
+        <v>128834490</v>
       </c>
       <c r="B35" t="n">
         <v>98632</v>
@@ -4213,13 +4218,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>753787</v>
+        <v>754042</v>
       </c>
       <c r="R35" t="n">
-        <v>7294025</v>
+        <v>7294151</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4253,7 +4258,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Mycket riktig förekomst</t>
+          <t>Riklig förekomst ca 10m diam</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4268,44 +4273,44 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128834490</v>
+        <v>128834411</v>
       </c>
       <c r="B36" t="n">
-        <v>98632</v>
+        <v>80225</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4315,10 +4320,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>754042</v>
+        <v>754071</v>
       </c>
       <c r="R36" t="n">
-        <v>7294151</v>
+        <v>7293962</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4351,11 +4356,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Riklig förekomst ca 10m diam</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4382,32 +4382,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128834434</v>
+        <v>128834417</v>
       </c>
       <c r="B37" t="n">
-        <v>95482</v>
+        <v>80225</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2387</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4417,10 +4417,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>753879</v>
+        <v>754171</v>
       </c>
       <c r="R37" t="n">
-        <v>7293890</v>
+        <v>7293926</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4479,32 +4479,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128834417</v>
+        <v>128819696</v>
       </c>
       <c r="B38" t="n">
-        <v>80225</v>
+        <v>80260</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4514,13 +4514,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>754171</v>
+        <v>754302</v>
       </c>
       <c r="R38" t="n">
-        <v>7293926</v>
+        <v>7293804</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4564,44 +4564,44 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128834390</v>
+        <v>128834405</v>
       </c>
       <c r="B39" t="n">
-        <v>80129</v>
+        <v>80225</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>754064</v>
+        <v>753772</v>
       </c>
       <c r="R39" t="n">
-        <v>7294121</v>
+        <v>7293986</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4673,32 +4673,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128819663</v>
+        <v>128834462</v>
       </c>
       <c r="B40" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4708,13 +4708,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>754152</v>
+        <v>754024</v>
       </c>
       <c r="R40" t="n">
-        <v>7294076</v>
+        <v>7293998</v>
       </c>
       <c r="S40" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4758,22 +4758,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128819696</v>
+        <v>128834434</v>
       </c>
       <c r="B41" t="n">
-        <v>80260</v>
+        <v>95482</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4781,21 +4781,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6463</v>
+        <v>2387</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4805,13 +4805,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>754302</v>
+        <v>753879</v>
       </c>
       <c r="R41" t="n">
-        <v>7293804</v>
+        <v>7293890</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4855,44 +4855,44 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128834405</v>
+        <v>128834378</v>
       </c>
       <c r="B42" t="n">
-        <v>80225</v>
+        <v>80254</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>753772</v>
+        <v>753636</v>
       </c>
       <c r="R42" t="n">
-        <v>7293986</v>
+        <v>7294023</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4964,10 +4964,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128834378</v>
+        <v>128834390</v>
       </c>
       <c r="B43" t="n">
-        <v>80254</v>
+        <v>80129</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4975,21 +4975,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>753636</v>
+        <v>754064</v>
       </c>
       <c r="R43" t="n">
-        <v>7294023</v>
+        <v>7294121</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5061,32 +5061,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128834462</v>
+        <v>128819663</v>
       </c>
       <c r="B44" t="n">
-        <v>98632</v>
+        <v>80225</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5096,13 +5096,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>754024</v>
+        <v>754152</v>
       </c>
       <c r="R44" t="n">
-        <v>7293998</v>
+        <v>7294076</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5146,22 +5146,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128834386</v>
+        <v>128834410</v>
       </c>
       <c r="B45" t="n">
-        <v>57713</v>
+        <v>80225</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5169,21 +5169,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5193,10 +5193,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>753889</v>
+        <v>754046</v>
       </c>
       <c r="R45" t="n">
-        <v>7294195</v>
+        <v>7293956</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5229,11 +5229,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Hack vid trädbas</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5260,10 +5255,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128834410</v>
+        <v>128834386</v>
       </c>
       <c r="B46" t="n">
-        <v>80225</v>
+        <v>57713</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5271,21 +5266,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5295,10 +5290,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>754046</v>
+        <v>753889</v>
       </c>
       <c r="R46" t="n">
-        <v>7293956</v>
+        <v>7294195</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5331,6 +5326,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Hack vid trädbas</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5357,32 +5357,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128819642</v>
+        <v>128834454</v>
       </c>
       <c r="B47" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5392,13 +5392,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>753744</v>
+        <v>753898</v>
       </c>
       <c r="R47" t="n">
-        <v>7294126</v>
+        <v>7293898</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5428,6 +5428,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>3mtr diam</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5442,19 +5447,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128834454</v>
+        <v>128819675</v>
       </c>
       <c r="B48" t="n">
         <v>98632</v>
@@ -5489,13 +5494,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>753898</v>
+        <v>753812</v>
       </c>
       <c r="R48" t="n">
-        <v>7293898</v>
+        <v>7293999</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5529,7 +5534,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>3mtr diam</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5544,44 +5549,44 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128819675</v>
+        <v>128819642</v>
       </c>
       <c r="B49" t="n">
-        <v>98632</v>
+        <v>80225</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5591,10 +5596,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>753812</v>
+        <v>753744</v>
       </c>
       <c r="R49" t="n">
-        <v>7293999</v>
+        <v>7294126</v>
       </c>
       <c r="S49" t="n">
         <v>3</v>
@@ -5627,11 +5632,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5658,7 +5658,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128834406</v>
+        <v>128834430</v>
       </c>
       <c r="B50" t="n">
         <v>80225</v>
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>753974</v>
+        <v>754027</v>
       </c>
       <c r="R50" t="n">
-        <v>7294029</v>
+        <v>7294150</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5755,7 +5755,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128834430</v>
+        <v>128834406</v>
       </c>
       <c r="B51" t="n">
         <v>80225</v>
@@ -5790,10 +5790,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>754027</v>
+        <v>753974</v>
       </c>
       <c r="R51" t="n">
-        <v>7294150</v>
+        <v>7294029</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6153,32 +6153,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128834376</v>
+        <v>128834446</v>
       </c>
       <c r="B55" t="n">
-        <v>91504</v>
+        <v>98632</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6188,10 +6188,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>754253</v>
+        <v>753638</v>
       </c>
       <c r="R55" t="n">
-        <v>7293898</v>
+        <v>7293994</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6224,6 +6224,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Mycket rikligt bestånd</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6250,32 +6255,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128819639</v>
+        <v>128834449</v>
       </c>
       <c r="B56" t="n">
-        <v>91800</v>
+        <v>98632</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6285,13 +6290,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>754249</v>
+        <v>753732</v>
       </c>
       <c r="R56" t="n">
-        <v>7293891</v>
+        <v>7293989</v>
       </c>
       <c r="S56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6325,7 +6330,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>10 fruktkroppar</t>
+          <t>Mycket rikligt bestånd</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6340,44 +6345,44 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128834433</v>
+        <v>128819680</v>
       </c>
       <c r="B57" t="n">
-        <v>95482</v>
+        <v>98632</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2387</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6387,13 +6392,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>753867</v>
+        <v>754079</v>
       </c>
       <c r="R57" t="n">
-        <v>7293877</v>
+        <v>7294043</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6423,6 +6428,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Rik förekomst</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6437,22 +6447,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128819648</v>
+        <v>128819639</v>
       </c>
       <c r="B58" t="n">
-        <v>80225</v>
+        <v>91800</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6460,21 +6470,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6484,10 +6494,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>754142</v>
+        <v>754249</v>
       </c>
       <c r="R58" t="n">
-        <v>7293999</v>
+        <v>7293891</v>
       </c>
       <c r="S58" t="n">
         <v>3</v>
@@ -6520,6 +6530,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>10 fruktkroppar</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6546,7 +6561,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128834404</v>
+        <v>128819648</v>
       </c>
       <c r="B59" t="n">
         <v>80225</v>
@@ -6581,13 +6596,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>753693</v>
+        <v>754142</v>
       </c>
       <c r="R59" t="n">
-        <v>7293978</v>
+        <v>7293999</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6631,44 +6646,44 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128834446</v>
+        <v>128834404</v>
       </c>
       <c r="B60" t="n">
-        <v>98632</v>
+        <v>80225</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6678,10 +6693,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>753638</v>
+        <v>753693</v>
       </c>
       <c r="R60" t="n">
-        <v>7293994</v>
+        <v>7293978</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6714,11 +6729,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Mycket rikligt bestånd</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6745,32 +6755,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128834449</v>
+        <v>128834376</v>
       </c>
       <c r="B61" t="n">
-        <v>98632</v>
+        <v>91504</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6780,10 +6790,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>753732</v>
+        <v>754253</v>
       </c>
       <c r="R61" t="n">
-        <v>7293989</v>
+        <v>7293898</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6816,11 +6826,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Mycket rikligt bestånd</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6847,32 +6852,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128819680</v>
+        <v>128834433</v>
       </c>
       <c r="B62" t="n">
-        <v>98632</v>
+        <v>95482</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>2387</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6882,13 +6887,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>754079</v>
+        <v>753867</v>
       </c>
       <c r="R62" t="n">
-        <v>7294043</v>
+        <v>7293877</v>
       </c>
       <c r="S62" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6918,11 +6923,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Rik förekomst</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6937,12 +6937,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7046,32 +7046,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128834457</v>
+        <v>128834407</v>
       </c>
       <c r="B64" t="n">
-        <v>98632</v>
+        <v>80225</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7081,10 +7081,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>753947</v>
+        <v>753989</v>
       </c>
       <c r="R64" t="n">
-        <v>7293964</v>
+        <v>7294010</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7117,11 +7117,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>5mtr diam</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7148,32 +7143,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128834463</v>
+        <v>128834416</v>
       </c>
       <c r="B65" t="n">
-        <v>98632</v>
+        <v>80225</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7183,10 +7178,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>754071</v>
+        <v>754148</v>
       </c>
       <c r="R65" t="n">
-        <v>7293964</v>
+        <v>7293935</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7245,32 +7240,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128834458</v>
+        <v>128834380</v>
       </c>
       <c r="B66" t="n">
-        <v>98632</v>
+        <v>80254</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7280,10 +7275,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>753959</v>
+        <v>754091</v>
       </c>
       <c r="R66" t="n">
-        <v>7294022</v>
+        <v>7293941</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7316,11 +7311,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>3m diam</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7347,7 +7337,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128819677</v>
+        <v>128834457</v>
       </c>
       <c r="B67" t="n">
         <v>98632</v>
@@ -7382,13 +7372,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>753875</v>
+        <v>753947</v>
       </c>
       <c r="R67" t="n">
-        <v>7294001</v>
+        <v>7293964</v>
       </c>
       <c r="S67" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7418,6 +7408,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>5mtr diam</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7432,19 +7427,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128834461</v>
+        <v>128834463</v>
       </c>
       <c r="B68" t="n">
         <v>98632</v>
@@ -7479,10 +7474,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>753981</v>
+        <v>754071</v>
       </c>
       <c r="R68" t="n">
-        <v>7294022</v>
+        <v>7293964</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7541,32 +7536,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128834407</v>
+        <v>128834458</v>
       </c>
       <c r="B69" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7576,10 +7571,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>753989</v>
+        <v>753959</v>
       </c>
       <c r="R69" t="n">
-        <v>7294010</v>
+        <v>7294022</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7612,6 +7607,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>3m diam</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7638,32 +7638,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128834416</v>
+        <v>128819677</v>
       </c>
       <c r="B70" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7673,13 +7673,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>754148</v>
+        <v>753875</v>
       </c>
       <c r="R70" t="n">
-        <v>7293935</v>
+        <v>7294001</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7723,44 +7723,44 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128834380</v>
+        <v>128834461</v>
       </c>
       <c r="B71" t="n">
-        <v>80254</v>
+        <v>98632</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7770,10 +7770,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>754091</v>
+        <v>753981</v>
       </c>
       <c r="R71" t="n">
-        <v>7293941</v>
+        <v>7294022</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7832,7 +7832,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128834409</v>
+        <v>128819652</v>
       </c>
       <c r="B72" t="n">
         <v>80225</v>
@@ -7867,13 +7867,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>754042</v>
+        <v>754297</v>
       </c>
       <c r="R72" t="n">
-        <v>7293966</v>
+        <v>7293780</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7917,12 +7917,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -8026,7 +8026,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128834401</v>
+        <v>128834409</v>
       </c>
       <c r="B74" t="n">
         <v>80225</v>
@@ -8061,10 +8061,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>753629</v>
+        <v>754042</v>
       </c>
       <c r="R74" t="n">
-        <v>7294009</v>
+        <v>7293966</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8123,7 +8123,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128819652</v>
+        <v>128834401</v>
       </c>
       <c r="B75" t="n">
         <v>80225</v>
@@ -8158,13 +8158,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>754297</v>
+        <v>753629</v>
       </c>
       <c r="R75" t="n">
-        <v>7293780</v>
+        <v>7294009</v>
       </c>
       <c r="S75" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8208,12 +8208,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -8623,32 +8623,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128819637</v>
+        <v>128834497</v>
       </c>
       <c r="B80" t="n">
-        <v>57713</v>
+        <v>80260</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8658,13 +8658,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>753970</v>
+        <v>754176</v>
       </c>
       <c r="R80" t="n">
-        <v>7294021</v>
+        <v>7293924</v>
       </c>
       <c r="S80" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8708,44 +8708,44 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128819655</v>
+        <v>128834381</v>
       </c>
       <c r="B81" t="n">
-        <v>80225</v>
+        <v>80254</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8755,13 +8755,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>754314</v>
+        <v>754177</v>
       </c>
       <c r="R81" t="n">
-        <v>7293792</v>
+        <v>7293925</v>
       </c>
       <c r="S81" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8805,19 +8805,19 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128819664</v>
+        <v>128819655</v>
       </c>
       <c r="B82" t="n">
         <v>80225</v>
@@ -8852,10 +8852,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>754142</v>
+        <v>754314</v>
       </c>
       <c r="R82" t="n">
-        <v>7294080</v>
+        <v>7293792</v>
       </c>
       <c r="S82" t="n">
         <v>3</v>
@@ -8914,32 +8914,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128834497</v>
+        <v>128819664</v>
       </c>
       <c r="B83" t="n">
-        <v>80260</v>
+        <v>80225</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8949,13 +8949,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>754176</v>
+        <v>754142</v>
       </c>
       <c r="R83" t="n">
-        <v>7293924</v>
+        <v>7294080</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8999,44 +8999,44 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128834381</v>
+        <v>128819637</v>
       </c>
       <c r="B84" t="n">
-        <v>80254</v>
+        <v>57713</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9046,13 +9046,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>754177</v>
+        <v>753970</v>
       </c>
       <c r="R84" t="n">
-        <v>7293925</v>
+        <v>7294021</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9096,12 +9096,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -9991,32 +9991,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128834435</v>
+        <v>128834482</v>
       </c>
       <c r="B94" t="n">
-        <v>95482</v>
+        <v>98632</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2387</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10026,10 +10026,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>753941</v>
+        <v>754298</v>
       </c>
       <c r="R94" t="n">
-        <v>7294196</v>
+        <v>7293981</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10088,7 +10088,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128834482</v>
+        <v>128819686</v>
       </c>
       <c r="B95" t="n">
         <v>98632</v>
@@ -10123,13 +10123,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>754298</v>
+        <v>754145</v>
       </c>
       <c r="R95" t="n">
-        <v>7293981</v>
+        <v>7293994</v>
       </c>
       <c r="S95" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10173,19 +10173,19 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128819686</v>
+        <v>128834455</v>
       </c>
       <c r="B96" t="n">
         <v>98632</v>
@@ -10220,13 +10220,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>754145</v>
+        <v>753903</v>
       </c>
       <c r="R96" t="n">
-        <v>7293994</v>
+        <v>7293910</v>
       </c>
       <c r="S96" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10256,6 +10256,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>4mtr diam</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10270,44 +10275,44 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128834455</v>
+        <v>128834435</v>
       </c>
       <c r="B97" t="n">
-        <v>98632</v>
+        <v>95482</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>2387</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10317,10 +10322,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>753903</v>
+        <v>753941</v>
       </c>
       <c r="R97" t="n">
-        <v>7293910</v>
+        <v>7294196</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10353,11 +10358,6 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>4mtr diam</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10578,32 +10578,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128819679</v>
+        <v>128834399</v>
       </c>
       <c r="B100" t="n">
-        <v>98632</v>
+        <v>80225</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10613,13 +10613,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>754015</v>
+        <v>753717</v>
       </c>
       <c r="R100" t="n">
-        <v>7294040</v>
+        <v>7294108</v>
       </c>
       <c r="S100" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10649,11 +10649,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10668,44 +10663,44 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128834451</v>
+        <v>128834428</v>
       </c>
       <c r="B101" t="n">
-        <v>98632</v>
+        <v>80225</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10715,10 +10710,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>753769</v>
+        <v>754137</v>
       </c>
       <c r="R101" t="n">
-        <v>7293962</v>
+        <v>7294102</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -10777,32 +10772,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128834448</v>
+        <v>128819644</v>
       </c>
       <c r="B102" t="n">
-        <v>98632</v>
+        <v>80225</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10812,13 +10807,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>753692</v>
+        <v>754003</v>
       </c>
       <c r="R102" t="n">
-        <v>7293978</v>
+        <v>7294039</v>
       </c>
       <c r="S102" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -10862,44 +10857,44 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128819644</v>
+        <v>128819679</v>
       </c>
       <c r="B103" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10909,10 +10904,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>754003</v>
+        <v>754015</v>
       </c>
       <c r="R103" t="n">
-        <v>7294039</v>
+        <v>7294040</v>
       </c>
       <c r="S103" t="n">
         <v>3</v>
@@ -10945,6 +10940,11 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10971,32 +10971,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128834399</v>
+        <v>128834451</v>
       </c>
       <c r="B104" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11006,10 +11006,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>753717</v>
+        <v>753769</v>
       </c>
       <c r="R104" t="n">
-        <v>7294108</v>
+        <v>7293962</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -11068,32 +11068,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128834428</v>
+        <v>128834448</v>
       </c>
       <c r="B105" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11103,10 +11103,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>754137</v>
+        <v>753692</v>
       </c>
       <c r="R105" t="n">
-        <v>7294102</v>
+        <v>7293978</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -11854,32 +11854,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128834408</v>
+        <v>128819689</v>
       </c>
       <c r="B113" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11889,13 +11889,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>754013</v>
+        <v>754240</v>
       </c>
       <c r="R113" t="n">
-        <v>7293996</v>
+        <v>7293924</v>
       </c>
       <c r="S113" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -11925,6 +11925,11 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Större förekomst</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11939,44 +11944,44 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128819689</v>
+        <v>128834419</v>
       </c>
       <c r="B114" t="n">
-        <v>98632</v>
+        <v>80225</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11986,13 +11991,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>754240</v>
+        <v>754329</v>
       </c>
       <c r="R114" t="n">
-        <v>7293924</v>
+        <v>7293829</v>
       </c>
       <c r="S114" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12022,11 +12027,6 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Större förekomst</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12041,19 +12041,19 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128834419</v>
+        <v>128819668</v>
       </c>
       <c r="B115" t="n">
         <v>80225</v>
@@ -12088,13 +12088,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>754329</v>
+        <v>753980</v>
       </c>
       <c r="R115" t="n">
-        <v>7293829</v>
+        <v>7294135</v>
       </c>
       <c r="S115" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12138,19 +12138,19 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128819668</v>
+        <v>128819647</v>
       </c>
       <c r="B116" t="n">
         <v>80225</v>
@@ -12185,10 +12185,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>753980</v>
+        <v>754139</v>
       </c>
       <c r="R116" t="n">
-        <v>7294135</v>
+        <v>7294012</v>
       </c>
       <c r="S116" t="n">
         <v>3</v>
@@ -12247,7 +12247,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128819647</v>
+        <v>128834408</v>
       </c>
       <c r="B117" t="n">
         <v>80225</v>
@@ -12282,13 +12282,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>754139</v>
+        <v>754013</v>
       </c>
       <c r="R117" t="n">
-        <v>7294012</v>
+        <v>7293996</v>
       </c>
       <c r="S117" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12332,60 +12332,57 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128834499</v>
+        <v>128834400</v>
       </c>
       <c r="B118" t="n">
-        <v>91876</v>
+        <v>80225</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1505</v>
+        <v>6458</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Stormansberget, Nb</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>754035</v>
+        <v>753636</v>
       </c>
       <c r="R118" t="n">
-        <v>7294132</v>
+        <v>7294018</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -12426,7 +12423,6 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -12445,32 +12441,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128834400</v>
+        <v>128834477</v>
       </c>
       <c r="B119" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12480,10 +12476,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>753636</v>
+        <v>754356</v>
       </c>
       <c r="R119" t="n">
-        <v>7294018</v>
+        <v>7293813</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -12516,6 +12512,11 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Ca 2m diam</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12542,32 +12543,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128834429</v>
+        <v>128834469</v>
       </c>
       <c r="B120" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12577,10 +12578,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>754063</v>
+        <v>754222</v>
       </c>
       <c r="R120" t="n">
-        <v>7294120</v>
+        <v>7293912</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -12613,6 +12614,11 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>10m diam mycket riklig förekomst</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12639,7 +12645,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128834477</v>
+        <v>128834444</v>
       </c>
       <c r="B121" t="n">
         <v>98632</v>
@@ -12674,10 +12680,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>754356</v>
+        <v>753729</v>
       </c>
       <c r="R121" t="n">
-        <v>7293813</v>
+        <v>7294103</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -12710,11 +12716,6 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Ca 2m diam</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12741,10 +12742,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128834469</v>
+        <v>128834499</v>
       </c>
       <c r="B122" t="n">
-        <v>98632</v>
+        <v>91876</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12752,34 +12753,37 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>220787</v>
+        <v>1505</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Stormansberget, Nb</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>754222</v>
+        <v>754035</v>
       </c>
       <c r="R122" t="n">
-        <v>7293912</v>
+        <v>7294132</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -12814,17 +12818,13 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>10m diam mycket riklig förekomst</t>
-        </is>
-      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -12843,32 +12843,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128834444</v>
+        <v>128834429</v>
       </c>
       <c r="B123" t="n">
-        <v>98632</v>
+        <v>80225</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12878,10 +12878,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>753729</v>
+        <v>754063</v>
       </c>
       <c r="R123" t="n">
-        <v>7294103</v>
+        <v>7294120</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -12940,32 +12940,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128834373</v>
+        <v>128819697</v>
       </c>
       <c r="B124" t="n">
-        <v>91679</v>
+        <v>96751</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1588</v>
+        <v>2869</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12975,13 +12975,13 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>754056</v>
+        <v>754263</v>
       </c>
       <c r="R124" t="n">
-        <v>7294109</v>
+        <v>7293846</v>
       </c>
       <c r="S124" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13025,22 +13025,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128819694</v>
+        <v>128834418</v>
       </c>
       <c r="B125" t="n">
-        <v>56898</v>
+        <v>80225</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13048,21 +13048,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13072,13 +13072,13 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>754139</v>
+        <v>754325</v>
       </c>
       <c r="R125" t="n">
-        <v>7294034</v>
+        <v>7293826</v>
       </c>
       <c r="S125" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -13122,44 +13122,44 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128834452</v>
+        <v>128819653</v>
       </c>
       <c r="B126" t="n">
-        <v>98632</v>
+        <v>80225</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13169,13 +13169,13 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>753833</v>
+        <v>754304</v>
       </c>
       <c r="R126" t="n">
-        <v>7293877</v>
+        <v>7293805</v>
       </c>
       <c r="S126" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13219,44 +13219,44 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128834474</v>
+        <v>128819650</v>
       </c>
       <c r="B127" t="n">
-        <v>98632</v>
+        <v>80225</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13266,13 +13266,13 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>754313</v>
+        <v>754166</v>
       </c>
       <c r="R127" t="n">
-        <v>7293834</v>
+        <v>7293978</v>
       </c>
       <c r="S127" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -13316,44 +13316,44 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128819683</v>
+        <v>128819694</v>
       </c>
       <c r="B128" t="n">
-        <v>98632</v>
+        <v>56898</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13363,10 +13363,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>754142</v>
+        <v>754139</v>
       </c>
       <c r="R128" t="n">
-        <v>7294040</v>
+        <v>7294034</v>
       </c>
       <c r="S128" t="n">
         <v>3</v>
@@ -13522,32 +13522,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128819697</v>
+        <v>128834373</v>
       </c>
       <c r="B130" t="n">
-        <v>96751</v>
+        <v>91679</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>2869</v>
+        <v>1588</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13557,13 +13557,13 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>754263</v>
+        <v>754056</v>
       </c>
       <c r="R130" t="n">
-        <v>7293846</v>
+        <v>7294109</v>
       </c>
       <c r="S130" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -13607,44 +13607,44 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128819650</v>
+        <v>128819671</v>
       </c>
       <c r="B131" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13654,10 +13654,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>754166</v>
+        <v>753685</v>
       </c>
       <c r="R131" t="n">
-        <v>7293978</v>
+        <v>7294093</v>
       </c>
       <c r="S131" t="n">
         <v>3</v>
@@ -13716,32 +13716,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128834418</v>
+        <v>128834453</v>
       </c>
       <c r="B132" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13751,10 +13751,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>754325</v>
+        <v>753894</v>
       </c>
       <c r="R132" t="n">
-        <v>7293826</v>
+        <v>7293894</v>
       </c>
       <c r="S132" t="n">
         <v>5</v>
@@ -13787,6 +13787,11 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>5mtr mycket rikligt bestånd</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -13813,32 +13818,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128819653</v>
+        <v>128834452</v>
       </c>
       <c r="B133" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13848,13 +13853,13 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>754304</v>
+        <v>753833</v>
       </c>
       <c r="R133" t="n">
-        <v>7293805</v>
+        <v>7293877</v>
       </c>
       <c r="S133" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -13898,19 +13903,19 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128819671</v>
+        <v>128834474</v>
       </c>
       <c r="B134" t="n">
         <v>98632</v>
@@ -13945,13 +13950,13 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>753685</v>
+        <v>754313</v>
       </c>
       <c r="R134" t="n">
-        <v>7294093</v>
+        <v>7293834</v>
       </c>
       <c r="S134" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -13995,19 +14000,19 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128834453</v>
+        <v>128819683</v>
       </c>
       <c r="B135" t="n">
         <v>98632</v>
@@ -14042,13 +14047,13 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>753894</v>
+        <v>754142</v>
       </c>
       <c r="R135" t="n">
-        <v>7293894</v>
+        <v>7294040</v>
       </c>
       <c r="S135" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -14078,11 +14083,6 @@
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>5mtr mycket rikligt bestånd</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14097,22 +14097,22 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128834372</v>
+        <v>128819645</v>
       </c>
       <c r="B136" t="n">
-        <v>88768</v>
+        <v>80225</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14120,21 +14120,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>4412</v>
+        <v>6458</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14144,13 +14144,13 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>754265</v>
+        <v>754081</v>
       </c>
       <c r="R136" t="n">
-        <v>7293869</v>
+        <v>7294036</v>
       </c>
       <c r="S136" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -14194,19 +14194,19 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128819651</v>
+        <v>128834402</v>
       </c>
       <c r="B137" t="n">
         <v>80225</v>
@@ -14241,13 +14241,13 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>754220</v>
+        <v>753663</v>
       </c>
       <c r="R137" t="n">
-        <v>7293908</v>
+        <v>7293971</v>
       </c>
       <c r="S137" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -14291,44 +14291,44 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128819669</v>
+        <v>128834498</v>
       </c>
       <c r="B138" t="n">
-        <v>80225</v>
+        <v>80260</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14338,13 +14338,13 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>753872</v>
+        <v>754129</v>
       </c>
       <c r="R138" t="n">
-        <v>7294169</v>
+        <v>7294101</v>
       </c>
       <c r="S138" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -14388,19 +14388,19 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128819645</v>
+        <v>128819651</v>
       </c>
       <c r="B139" t="n">
         <v>80225</v>
@@ -14435,10 +14435,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>754081</v>
+        <v>754220</v>
       </c>
       <c r="R139" t="n">
-        <v>7294036</v>
+        <v>7293908</v>
       </c>
       <c r="S139" t="n">
         <v>3</v>
@@ -14497,7 +14497,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128819640</v>
+        <v>128819669</v>
       </c>
       <c r="B140" t="n">
         <v>80225</v>
@@ -14532,10 +14532,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>754021</v>
+        <v>753872</v>
       </c>
       <c r="R140" t="n">
-        <v>7294099</v>
+        <v>7294169</v>
       </c>
       <c r="S140" t="n">
         <v>3</v>
@@ -14576,7 +14576,6 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -14595,7 +14594,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128834402</v>
+        <v>128819640</v>
       </c>
       <c r="B141" t="n">
         <v>80225</v>
@@ -14630,13 +14629,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>753663</v>
+        <v>754021</v>
       </c>
       <c r="R141" t="n">
-        <v>7293971</v>
+        <v>7294099</v>
       </c>
       <c r="S141" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -14674,50 +14673,51 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
+      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128834498</v>
+        <v>128834372</v>
       </c>
       <c r="B142" t="n">
-        <v>80260</v>
+        <v>88768</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6463</v>
+        <v>4412</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14727,10 +14727,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>754129</v>
+        <v>754265</v>
       </c>
       <c r="R142" t="n">
-        <v>7294101</v>
+        <v>7293869</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -14789,32 +14789,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128834489</v>
+        <v>128819667</v>
       </c>
       <c r="B143" t="n">
-        <v>98632</v>
+        <v>80225</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14824,13 +14824,13 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>754044</v>
+        <v>754002</v>
       </c>
       <c r="R143" t="n">
-        <v>7294116</v>
+        <v>7294106</v>
       </c>
       <c r="S143" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -14874,44 +14874,44 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128834487</v>
+        <v>128819643</v>
       </c>
       <c r="B144" t="n">
-        <v>98632</v>
+        <v>80225</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -14921,13 +14921,13 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>754147</v>
+        <v>753951</v>
       </c>
       <c r="R144" t="n">
-        <v>7294086</v>
+        <v>7293999</v>
       </c>
       <c r="S144" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -14971,44 +14971,44 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128819682</v>
+        <v>128819636</v>
       </c>
       <c r="B145" t="n">
-        <v>98632</v>
+        <v>57876</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15018,10 +15018,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>754120</v>
+        <v>754361</v>
       </c>
       <c r="R145" t="n">
-        <v>7294078</v>
+        <v>7293841</v>
       </c>
       <c r="S145" t="n">
         <v>3</v>
@@ -15058,7 +15058,7 @@
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>Riktig förekomst</t>
+          <t>6 individer</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15085,32 +15085,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128819667</v>
+        <v>128834379</v>
       </c>
       <c r="B146" t="n">
-        <v>80225</v>
+        <v>80254</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15120,13 +15120,13 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>754002</v>
+        <v>753674</v>
       </c>
       <c r="R146" t="n">
-        <v>7294106</v>
+        <v>7293973</v>
       </c>
       <c r="S146" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -15170,19 +15170,19 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128819643</v>
+        <v>128834412</v>
       </c>
       <c r="B147" t="n">
         <v>80225</v>
@@ -15217,13 +15217,13 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>753951</v>
+        <v>754096</v>
       </c>
       <c r="R147" t="n">
-        <v>7293999</v>
+        <v>7293963</v>
       </c>
       <c r="S147" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -15267,44 +15267,44 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128834379</v>
+        <v>128834489</v>
       </c>
       <c r="B148" t="n">
-        <v>80254</v>
+        <v>98632</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15314,10 +15314,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>753674</v>
+        <v>754044</v>
       </c>
       <c r="R148" t="n">
-        <v>7293973</v>
+        <v>7294116</v>
       </c>
       <c r="S148" t="n">
         <v>5</v>
@@ -15376,32 +15376,32 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128834412</v>
+        <v>128834487</v>
       </c>
       <c r="B149" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15411,10 +15411,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>754096</v>
+        <v>754147</v>
       </c>
       <c r="R149" t="n">
-        <v>7293963</v>
+        <v>7294086</v>
       </c>
       <c r="S149" t="n">
         <v>5</v>
@@ -15473,32 +15473,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128819636</v>
+        <v>128819682</v>
       </c>
       <c r="B150" t="n">
-        <v>57876</v>
+        <v>98632</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15508,10 +15508,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>754361</v>
+        <v>754120</v>
       </c>
       <c r="R150" t="n">
-        <v>7293841</v>
+        <v>7294078</v>
       </c>
       <c r="S150" t="n">
         <v>3</v>
@@ -15548,7 +15548,7 @@
       </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>6 individer</t>
+          <t>Riktig förekomst</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -15575,32 +15575,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128834472</v>
+        <v>128834389</v>
       </c>
       <c r="B151" t="n">
-        <v>98632</v>
+        <v>80129</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15610,10 +15610,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>754273</v>
+        <v>754026</v>
       </c>
       <c r="R151" t="n">
-        <v>7293868</v>
+        <v>7293997</v>
       </c>
       <c r="S151" t="n">
         <v>5</v>
@@ -15646,11 +15646,6 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>Ca 8 m diam</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -15677,32 +15672,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128834475</v>
+        <v>128834422</v>
       </c>
       <c r="B152" t="n">
-        <v>98632</v>
+        <v>80225</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15712,10 +15707,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>754330</v>
+        <v>754355</v>
       </c>
       <c r="R152" t="n">
-        <v>7293823</v>
+        <v>7293811</v>
       </c>
       <c r="S152" t="n">
         <v>5</v>
@@ -15748,11 +15743,6 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>4mtr diam</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -15779,32 +15769,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128834422</v>
+        <v>128834472</v>
       </c>
       <c r="B153" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -15814,10 +15804,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>754355</v>
+        <v>754273</v>
       </c>
       <c r="R153" t="n">
-        <v>7293811</v>
+        <v>7293868</v>
       </c>
       <c r="S153" t="n">
         <v>5</v>
@@ -15850,6 +15840,11 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>Ca 8 m diam</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -15876,32 +15871,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128834389</v>
+        <v>128834475</v>
       </c>
       <c r="B154" t="n">
-        <v>80129</v>
+        <v>98632</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -15911,10 +15906,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>754026</v>
+        <v>754330</v>
       </c>
       <c r="R154" t="n">
-        <v>7293997</v>
+        <v>7293823</v>
       </c>
       <c r="S154" t="n">
         <v>5</v>
@@ -15947,6 +15942,11 @@
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>4mtr diam</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -15973,32 +15973,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128834470</v>
+        <v>128834413</v>
       </c>
       <c r="B155" t="n">
-        <v>98632</v>
+        <v>80225</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16008,10 +16008,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>754249</v>
+        <v>754091</v>
       </c>
       <c r="R155" t="n">
-        <v>7293901</v>
+        <v>7293941</v>
       </c>
       <c r="S155" t="n">
         <v>5</v>
@@ -16070,32 +16070,32 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128819692</v>
+        <v>128819646</v>
       </c>
       <c r="B156" t="n">
-        <v>98632</v>
+        <v>80225</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16105,10 +16105,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>754049</v>
+        <v>754143</v>
       </c>
       <c r="R156" t="n">
-        <v>7294082</v>
+        <v>7294037</v>
       </c>
       <c r="S156" t="n">
         <v>3</v>
@@ -16141,11 +16141,6 @@
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>Stor förekomst</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16172,32 +16167,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128819691</v>
+        <v>128834391</v>
       </c>
       <c r="B157" t="n">
-        <v>98632</v>
+        <v>97503</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16207,13 +16202,13 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>754222</v>
+        <v>754184</v>
       </c>
       <c r="R157" t="n">
-        <v>7293998</v>
+        <v>7294045</v>
       </c>
       <c r="S157" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -16243,11 +16238,6 @@
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>Större område</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16262,19 +16252,19 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128834485</v>
+        <v>128834470</v>
       </c>
       <c r="B158" t="n">
         <v>98632</v>
@@ -16309,10 +16299,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>754182</v>
+        <v>754249</v>
       </c>
       <c r="R158" t="n">
-        <v>7294034</v>
+        <v>7293901</v>
       </c>
       <c r="S158" t="n">
         <v>5</v>
@@ -16345,11 +16335,6 @@
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -16376,7 +16361,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128819688</v>
+        <v>128819692</v>
       </c>
       <c r="B159" t="n">
         <v>98632</v>
@@ -16411,10 +16396,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>754342</v>
+        <v>754049</v>
       </c>
       <c r="R159" t="n">
-        <v>7293868</v>
+        <v>7294082</v>
       </c>
       <c r="S159" t="n">
         <v>3</v>
@@ -16447,6 +16432,11 @@
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>Stor förekomst</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -16473,32 +16463,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128834413</v>
+        <v>128819691</v>
       </c>
       <c r="B160" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16508,13 +16498,13 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>754091</v>
+        <v>754222</v>
       </c>
       <c r="R160" t="n">
-        <v>7293941</v>
+        <v>7293998</v>
       </c>
       <c r="S160" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -16544,6 +16534,11 @@
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>Större område</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -16558,44 +16553,44 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128819646</v>
+        <v>128834485</v>
       </c>
       <c r="B161" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16605,13 +16600,13 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>754143</v>
+        <v>754182</v>
       </c>
       <c r="R161" t="n">
-        <v>7294037</v>
+        <v>7294034</v>
       </c>
       <c r="S161" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -16641,6 +16636,11 @@
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -16655,44 +16655,44 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128834391</v>
+        <v>128819688</v>
       </c>
       <c r="B162" t="n">
-        <v>97503</v>
+        <v>98632</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -16702,13 +16702,13 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>754184</v>
+        <v>754342</v>
       </c>
       <c r="R162" t="n">
-        <v>7294045</v>
+        <v>7293868</v>
       </c>
       <c r="S162" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -16752,12 +16752,12 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>

--- a/artfynd/A 41034-2025 artfynd.xlsx
+++ b/artfynd/A 41034-2025 artfynd.xlsx
@@ -3688,10 +3688,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128834415</v>
+        <v>128834411</v>
       </c>
       <c r="B30" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3723,10 +3723,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>754084</v>
+        <v>754071</v>
       </c>
       <c r="R30" t="n">
-        <v>7293943</v>
+        <v>7293962</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3788,7 +3788,7 @@
         <v>128834420</v>
       </c>
       <c r="B31" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3882,32 +3882,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128819672</v>
+        <v>128834415</v>
       </c>
       <c r="B32" t="n">
-        <v>98632</v>
+        <v>80229</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3917,13 +3917,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>753733</v>
+        <v>754084</v>
       </c>
       <c r="R32" t="n">
-        <v>7294060</v>
+        <v>7293943</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3953,11 +3953,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Mycket Riklig förekomst</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3972,22 +3967,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128834473</v>
+        <v>128819672</v>
       </c>
       <c r="B33" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4019,13 +4014,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>754284</v>
+        <v>753733</v>
       </c>
       <c r="R33" t="n">
-        <v>7293849</v>
+        <v>7294060</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4055,6 +4050,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Mycket Riklig förekomst</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4069,22 +4069,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128819673</v>
+        <v>128834473</v>
       </c>
       <c r="B34" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4116,13 +4116,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>753787</v>
+        <v>754284</v>
       </c>
       <c r="R34" t="n">
-        <v>7294025</v>
+        <v>7293849</v>
       </c>
       <c r="S34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4152,11 +4152,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Mycket riktig förekomst</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4171,22 +4166,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128834490</v>
+        <v>128819673</v>
       </c>
       <c r="B35" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4218,13 +4213,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>754042</v>
+        <v>753787</v>
       </c>
       <c r="R35" t="n">
-        <v>7294151</v>
+        <v>7294025</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4258,7 +4253,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Riklig förekomst ca 10m diam</t>
+          <t>Mycket riktig förekomst</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4273,44 +4268,44 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128834411</v>
+        <v>128834490</v>
       </c>
       <c r="B36" t="n">
-        <v>80225</v>
+        <v>98636</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4320,10 +4315,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>754071</v>
+        <v>754042</v>
       </c>
       <c r="R36" t="n">
-        <v>7293962</v>
+        <v>7294151</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4356,6 +4351,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Riklig förekomst ca 10m diam</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4382,32 +4382,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128834417</v>
+        <v>128834434</v>
       </c>
       <c r="B37" t="n">
-        <v>80225</v>
+        <v>95486</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>2387</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4417,10 +4417,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>754171</v>
+        <v>753879</v>
       </c>
       <c r="R37" t="n">
-        <v>7293926</v>
+        <v>7293890</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4479,32 +4479,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128819696</v>
+        <v>128834405</v>
       </c>
       <c r="B38" t="n">
-        <v>80260</v>
+        <v>80229</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4514,13 +4514,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>754302</v>
+        <v>753772</v>
       </c>
       <c r="R38" t="n">
-        <v>7293804</v>
+        <v>7293986</v>
       </c>
       <c r="S38" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4564,22 +4564,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128834405</v>
+        <v>128834417</v>
       </c>
       <c r="B39" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>753772</v>
+        <v>754171</v>
       </c>
       <c r="R39" t="n">
-        <v>7293986</v>
+        <v>7293926</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4673,32 +4673,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128834462</v>
+        <v>128834390</v>
       </c>
       <c r="B40" t="n">
-        <v>98632</v>
+        <v>80133</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4708,10 +4708,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>754024</v>
+        <v>754064</v>
       </c>
       <c r="R40" t="n">
-        <v>7293998</v>
+        <v>7294121</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4770,10 +4770,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128834434</v>
+        <v>128819696</v>
       </c>
       <c r="B41" t="n">
-        <v>95482</v>
+        <v>80264</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4781,21 +4781,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2387</v>
+        <v>6463</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4805,13 +4805,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>753879</v>
+        <v>754302</v>
       </c>
       <c r="R41" t="n">
-        <v>7293890</v>
+        <v>7293804</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4855,44 +4855,44 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128834378</v>
+        <v>128819663</v>
       </c>
       <c r="B42" t="n">
-        <v>80254</v>
+        <v>80229</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4902,13 +4902,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>753636</v>
+        <v>754152</v>
       </c>
       <c r="R42" t="n">
-        <v>7294023</v>
+        <v>7294076</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4952,22 +4952,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128834390</v>
+        <v>128834378</v>
       </c>
       <c r="B43" t="n">
-        <v>80129</v>
+        <v>80258</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4975,21 +4975,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>754064</v>
+        <v>753636</v>
       </c>
       <c r="R43" t="n">
-        <v>7294121</v>
+        <v>7294023</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5061,32 +5061,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128819663</v>
+        <v>128834462</v>
       </c>
       <c r="B44" t="n">
-        <v>80225</v>
+        <v>98636</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5096,13 +5096,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>754152</v>
+        <v>754024</v>
       </c>
       <c r="R44" t="n">
-        <v>7294076</v>
+        <v>7293998</v>
       </c>
       <c r="S44" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5146,12 +5146,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5161,7 +5161,7 @@
         <v>128834410</v>
       </c>
       <c r="B45" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5255,10 +5255,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128834386</v>
+        <v>128819642</v>
       </c>
       <c r="B46" t="n">
-        <v>57713</v>
+        <v>80229</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5266,21 +5266,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5290,13 +5290,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>753889</v>
+        <v>753744</v>
       </c>
       <c r="R46" t="n">
-        <v>7294195</v>
+        <v>7294126</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5326,11 +5326,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Hack vid trädbas</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5345,44 +5340,44 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128834454</v>
+        <v>128834386</v>
       </c>
       <c r="B47" t="n">
-        <v>98632</v>
+        <v>57717</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5392,10 +5387,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>753898</v>
+        <v>753889</v>
       </c>
       <c r="R47" t="n">
-        <v>7293898</v>
+        <v>7294195</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5432,7 +5427,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>3mtr diam</t>
+          <t>Hack vid trädbas</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5459,10 +5454,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128819675</v>
+        <v>128834454</v>
       </c>
       <c r="B48" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5494,13 +5489,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>753812</v>
+        <v>753898</v>
       </c>
       <c r="R48" t="n">
-        <v>7293999</v>
+        <v>7293898</v>
       </c>
       <c r="S48" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5534,7 +5529,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>3mtr diam</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5549,44 +5544,44 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128819642</v>
+        <v>128819675</v>
       </c>
       <c r="B49" t="n">
-        <v>80225</v>
+        <v>98636</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5596,10 +5591,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>753744</v>
+        <v>753812</v>
       </c>
       <c r="R49" t="n">
-        <v>7294126</v>
+        <v>7293999</v>
       </c>
       <c r="S49" t="n">
         <v>3</v>
@@ -5632,6 +5627,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5658,32 +5658,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128834430</v>
+        <v>128819693</v>
       </c>
       <c r="B50" t="n">
-        <v>80225</v>
+        <v>98636</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5693,13 +5693,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>754027</v>
+        <v>754024</v>
       </c>
       <c r="R50" t="n">
-        <v>7294150</v>
+        <v>7294106</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5729,6 +5729,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>På ett större område mer än 30 individer</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5743,44 +5748,44 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128834406</v>
+        <v>128834484</v>
       </c>
       <c r="B51" t="n">
-        <v>80225</v>
+        <v>98636</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5790,10 +5795,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>753974</v>
+        <v>754289</v>
       </c>
       <c r="R51" t="n">
-        <v>7294029</v>
+        <v>7293999</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5826,6 +5831,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Riklig förekomst  ca 6m diam</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5852,32 +5862,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128819690</v>
+        <v>128834406</v>
       </c>
       <c r="B52" t="n">
-        <v>98632</v>
+        <v>80229</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5887,13 +5897,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>754224</v>
+        <v>753974</v>
       </c>
       <c r="R52" t="n">
-        <v>7293966</v>
+        <v>7294029</v>
       </c>
       <c r="S52" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5937,44 +5947,44 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128819693</v>
+        <v>128834430</v>
       </c>
       <c r="B53" t="n">
-        <v>98632</v>
+        <v>80229</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5984,13 +5994,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>754024</v>
+        <v>754027</v>
       </c>
       <c r="R53" t="n">
-        <v>7294106</v>
+        <v>7294150</v>
       </c>
       <c r="S53" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6020,11 +6030,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>På ett större område mer än 30 individer</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6039,22 +6044,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128834484</v>
+        <v>128819690</v>
       </c>
       <c r="B54" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6086,13 +6091,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>754289</v>
+        <v>754224</v>
       </c>
       <c r="R54" t="n">
-        <v>7293999</v>
+        <v>7293966</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6122,11 +6127,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Riklig förekomst  ca 6m diam</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6141,12 +6141,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6156,7 +6156,7 @@
         <v>128834446</v>
       </c>
       <c r="B55" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>128834449</v>
       </c>
       <c r="B56" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6360,7 +6360,7 @@
         <v>128819680</v>
       </c>
       <c r="B57" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6462,7 +6462,7 @@
         <v>128819639</v>
       </c>
       <c r="B58" t="n">
-        <v>91800</v>
+        <v>91804</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6561,10 +6561,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128819648</v>
+        <v>128834376</v>
       </c>
       <c r="B59" t="n">
-        <v>80225</v>
+        <v>91508</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6572,21 +6572,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6596,13 +6596,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>754142</v>
+        <v>754253</v>
       </c>
       <c r="R59" t="n">
-        <v>7293999</v>
+        <v>7293898</v>
       </c>
       <c r="S59" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6646,22 +6646,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128834404</v>
+        <v>128834491</v>
       </c>
       <c r="B60" t="n">
-        <v>80225</v>
+        <v>56901</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6669,21 +6669,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6693,10 +6693,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>753693</v>
+        <v>753881</v>
       </c>
       <c r="R60" t="n">
-        <v>7293978</v>
+        <v>7293891</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6755,32 +6755,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128834376</v>
+        <v>128834433</v>
       </c>
       <c r="B61" t="n">
-        <v>91504</v>
+        <v>95486</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>2387</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6790,10 +6790,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>754253</v>
+        <v>753867</v>
       </c>
       <c r="R61" t="n">
-        <v>7293898</v>
+        <v>7293877</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6852,32 +6852,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128834433</v>
+        <v>128834404</v>
       </c>
       <c r="B62" t="n">
-        <v>95482</v>
+        <v>80229</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2387</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6887,10 +6887,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>753867</v>
+        <v>753693</v>
       </c>
       <c r="R62" t="n">
-        <v>7293877</v>
+        <v>7293978</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6949,10 +6949,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128834491</v>
+        <v>128819648</v>
       </c>
       <c r="B63" t="n">
-        <v>56898</v>
+        <v>80229</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6960,21 +6960,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6984,13 +6984,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>753881</v>
+        <v>754142</v>
       </c>
       <c r="R63" t="n">
-        <v>7293891</v>
+        <v>7293999</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7034,22 +7034,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128834407</v>
+        <v>128834416</v>
       </c>
       <c r="B64" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7081,10 +7081,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>753989</v>
+        <v>754148</v>
       </c>
       <c r="R64" t="n">
-        <v>7294010</v>
+        <v>7293935</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7143,10 +7143,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128834416</v>
+        <v>128834407</v>
       </c>
       <c r="B65" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7178,10 +7178,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>754148</v>
+        <v>753989</v>
       </c>
       <c r="R65" t="n">
-        <v>7293935</v>
+        <v>7294010</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7243,7 +7243,7 @@
         <v>128834380</v>
       </c>
       <c r="B66" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7340,7 +7340,7 @@
         <v>128834457</v>
       </c>
       <c r="B67" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         <v>128834463</v>
       </c>
       <c r="B68" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>128834458</v>
       </c>
       <c r="B69" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7641,7 +7641,7 @@
         <v>128819677</v>
       </c>
       <c r="B70" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         <v>128834461</v>
       </c>
       <c r="B71" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7832,10 +7832,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128819652</v>
+        <v>128834401</v>
       </c>
       <c r="B72" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7867,13 +7867,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>754297</v>
+        <v>753629</v>
       </c>
       <c r="R72" t="n">
-        <v>7293780</v>
+        <v>7294009</v>
       </c>
       <c r="S72" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7917,44 +7917,44 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128834431</v>
+        <v>128834409</v>
       </c>
       <c r="B73" t="n">
-        <v>80261</v>
+        <v>80229</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7964,10 +7964,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>754087</v>
+        <v>754042</v>
       </c>
       <c r="R73" t="n">
-        <v>7293941</v>
+        <v>7293966</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8026,10 +8026,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128834409</v>
+        <v>128819652</v>
       </c>
       <c r="B74" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8061,13 +8061,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>754042</v>
+        <v>754297</v>
       </c>
       <c r="R74" t="n">
-        <v>7293966</v>
+        <v>7293780</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8111,44 +8111,44 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128834401</v>
+        <v>128834431</v>
       </c>
       <c r="B75" t="n">
-        <v>80225</v>
+        <v>80265</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8158,10 +8158,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>753629</v>
+        <v>754087</v>
       </c>
       <c r="R75" t="n">
-        <v>7294009</v>
+        <v>7293941</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8223,7 +8223,7 @@
         <v>128819676</v>
       </c>
       <c r="B76" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8325,7 +8325,7 @@
         <v>128834476</v>
       </c>
       <c r="B77" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
         <v>128834443</v>
       </c>
       <c r="B78" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>128834456</v>
       </c>
       <c r="B79" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8623,32 +8623,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128834497</v>
+        <v>128819637</v>
       </c>
       <c r="B80" t="n">
-        <v>80260</v>
+        <v>57717</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8658,13 +8658,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>754176</v>
+        <v>753970</v>
       </c>
       <c r="R80" t="n">
-        <v>7293924</v>
+        <v>7294021</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8708,44 +8708,44 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128834381</v>
+        <v>128834492</v>
       </c>
       <c r="B81" t="n">
-        <v>80254</v>
+        <v>56901</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6462</v>
+        <v>102612</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8755,10 +8755,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>754177</v>
+        <v>753985</v>
       </c>
       <c r="R81" t="n">
-        <v>7293925</v>
+        <v>7294023</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -8817,32 +8817,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128819655</v>
+        <v>128834497</v>
       </c>
       <c r="B82" t="n">
-        <v>80225</v>
+        <v>80264</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8852,13 +8852,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>754314</v>
+        <v>754176</v>
       </c>
       <c r="R82" t="n">
-        <v>7293792</v>
+        <v>7293924</v>
       </c>
       <c r="S82" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8902,22 +8902,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128819664</v>
+        <v>128819655</v>
       </c>
       <c r="B83" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8949,10 +8949,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>754142</v>
+        <v>754314</v>
       </c>
       <c r="R83" t="n">
-        <v>7294080</v>
+        <v>7293792</v>
       </c>
       <c r="S83" t="n">
         <v>3</v>
@@ -9011,10 +9011,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128819637</v>
+        <v>128819664</v>
       </c>
       <c r="B84" t="n">
-        <v>57713</v>
+        <v>80229</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9022,21 +9022,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9046,10 +9046,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>753970</v>
+        <v>754142</v>
       </c>
       <c r="R84" t="n">
-        <v>7294021</v>
+        <v>7294080</v>
       </c>
       <c r="S84" t="n">
         <v>3</v>
@@ -9108,32 +9108,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128834492</v>
+        <v>128834381</v>
       </c>
       <c r="B85" t="n">
-        <v>56898</v>
+        <v>80258</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>102612</v>
+        <v>6462</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9143,10 +9143,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>753985</v>
+        <v>754177</v>
       </c>
       <c r="R85" t="n">
-        <v>7294023</v>
+        <v>7293925</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9208,7 +9208,7 @@
         <v>128819685</v>
       </c>
       <c r="B86" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9305,7 +9305,7 @@
         <v>128834488</v>
       </c>
       <c r="B87" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9402,7 +9402,7 @@
         <v>128834466</v>
       </c>
       <c r="B88" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9501,32 +9501,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128834427</v>
+        <v>128834432</v>
       </c>
       <c r="B89" t="n">
-        <v>80225</v>
+        <v>80133</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9536,10 +9536,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>754149</v>
+        <v>754056</v>
       </c>
       <c r="R89" t="n">
-        <v>7294074</v>
+        <v>7293965</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -9598,32 +9598,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128834432</v>
+        <v>128834427</v>
       </c>
       <c r="B90" t="n">
-        <v>80129</v>
+        <v>80229</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9633,10 +9633,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>754056</v>
+        <v>754149</v>
       </c>
       <c r="R90" t="n">
-        <v>7293965</v>
+        <v>7294074</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -9698,7 +9698,7 @@
         <v>128819681</v>
       </c>
       <c r="B91" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9800,7 +9800,7 @@
         <v>128834459</v>
       </c>
       <c r="B92" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         <v>128834471</v>
       </c>
       <c r="B93" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9991,32 +9991,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128834482</v>
+        <v>128834435</v>
       </c>
       <c r="B94" t="n">
-        <v>98632</v>
+        <v>95486</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>2387</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10026,10 +10026,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>754298</v>
+        <v>753941</v>
       </c>
       <c r="R94" t="n">
-        <v>7293981</v>
+        <v>7294196</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10088,32 +10088,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128819686</v>
+        <v>128819654</v>
       </c>
       <c r="B95" t="n">
-        <v>98632</v>
+        <v>80229</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10123,10 +10123,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>754145</v>
+        <v>754303</v>
       </c>
       <c r="R95" t="n">
-        <v>7293994</v>
+        <v>7293804</v>
       </c>
       <c r="S95" t="n">
         <v>3</v>
@@ -10185,32 +10185,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128834455</v>
+        <v>128819649</v>
       </c>
       <c r="B96" t="n">
-        <v>98632</v>
+        <v>80229</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10220,13 +10220,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>753903</v>
+        <v>754149</v>
       </c>
       <c r="R96" t="n">
-        <v>7293910</v>
+        <v>7293983</v>
       </c>
       <c r="S96" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10256,11 +10256,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>4mtr diam</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10275,44 +10270,44 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128834435</v>
+        <v>128834482</v>
       </c>
       <c r="B97" t="n">
-        <v>95482</v>
+        <v>98636</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>2387</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10322,10 +10317,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>753941</v>
+        <v>754298</v>
       </c>
       <c r="R97" t="n">
-        <v>7294196</v>
+        <v>7293981</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10384,32 +10379,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128819654</v>
+        <v>128819686</v>
       </c>
       <c r="B98" t="n">
-        <v>80225</v>
+        <v>98636</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10419,10 +10414,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>754303</v>
+        <v>754145</v>
       </c>
       <c r="R98" t="n">
-        <v>7293804</v>
+        <v>7293994</v>
       </c>
       <c r="S98" t="n">
         <v>3</v>
@@ -10481,32 +10476,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128819649</v>
+        <v>128834455</v>
       </c>
       <c r="B99" t="n">
-        <v>80225</v>
+        <v>98636</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10516,13 +10511,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>754149</v>
+        <v>753903</v>
       </c>
       <c r="R99" t="n">
-        <v>7293983</v>
+        <v>7293910</v>
       </c>
       <c r="S99" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10552,6 +10547,11 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>4mtr diam</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10566,44 +10566,44 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128834399</v>
+        <v>128819679</v>
       </c>
       <c r="B100" t="n">
-        <v>80225</v>
+        <v>98636</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10613,13 +10613,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>753717</v>
+        <v>754015</v>
       </c>
       <c r="R100" t="n">
-        <v>7294108</v>
+        <v>7294040</v>
       </c>
       <c r="S100" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10649,6 +10649,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10663,44 +10668,44 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128834428</v>
+        <v>128834451</v>
       </c>
       <c r="B101" t="n">
-        <v>80225</v>
+        <v>98636</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10710,10 +10715,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>754137</v>
+        <v>753769</v>
       </c>
       <c r="R101" t="n">
-        <v>7294102</v>
+        <v>7293962</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -10772,32 +10777,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128819644</v>
+        <v>128834448</v>
       </c>
       <c r="B102" t="n">
-        <v>80225</v>
+        <v>98636</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10807,13 +10812,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>754003</v>
+        <v>753692</v>
       </c>
       <c r="R102" t="n">
-        <v>7294039</v>
+        <v>7293978</v>
       </c>
       <c r="S102" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -10857,44 +10862,44 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128819679</v>
+        <v>128834428</v>
       </c>
       <c r="B103" t="n">
-        <v>98632</v>
+        <v>80229</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10904,13 +10909,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>754015</v>
+        <v>754137</v>
       </c>
       <c r="R103" t="n">
-        <v>7294040</v>
+        <v>7294102</v>
       </c>
       <c r="S103" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -10940,11 +10945,6 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10959,44 +10959,44 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128834451</v>
+        <v>128834399</v>
       </c>
       <c r="B104" t="n">
-        <v>98632</v>
+        <v>80229</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11006,10 +11006,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>753769</v>
+        <v>753717</v>
       </c>
       <c r="R104" t="n">
-        <v>7293962</v>
+        <v>7294108</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -11068,32 +11068,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128834448</v>
+        <v>128819644</v>
       </c>
       <c r="B105" t="n">
-        <v>98632</v>
+        <v>80229</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11103,13 +11103,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>753692</v>
+        <v>754003</v>
       </c>
       <c r="R105" t="n">
-        <v>7293978</v>
+        <v>7294039</v>
       </c>
       <c r="S105" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11153,12 +11153,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
@@ -11168,7 +11168,7 @@
         <v>128834436</v>
       </c>
       <c r="B106" t="n">
-        <v>95482</v>
+        <v>95486</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11265,7 +11265,7 @@
         <v>128834450</v>
       </c>
       <c r="B107" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11362,7 +11362,7 @@
         <v>128819670</v>
       </c>
       <c r="B108" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11464,7 +11464,7 @@
         <v>128819684</v>
       </c>
       <c r="B109" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11561,7 +11561,7 @@
         <v>128834465</v>
       </c>
       <c r="B110" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
         <v>128834445</v>
       </c>
       <c r="B111" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11760,7 +11760,7 @@
         <v>128834468</v>
       </c>
       <c r="B112" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11854,32 +11854,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128819689</v>
+        <v>128819668</v>
       </c>
       <c r="B113" t="n">
-        <v>98632</v>
+        <v>80229</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11889,10 +11889,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>754240</v>
+        <v>753980</v>
       </c>
       <c r="R113" t="n">
-        <v>7293924</v>
+        <v>7294135</v>
       </c>
       <c r="S113" t="n">
         <v>3</v>
@@ -11925,11 +11925,6 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Större förekomst</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11956,10 +11951,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128834419</v>
+        <v>128819647</v>
       </c>
       <c r="B114" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11991,13 +11986,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>754329</v>
+        <v>754139</v>
       </c>
       <c r="R114" t="n">
-        <v>7293829</v>
+        <v>7294012</v>
       </c>
       <c r="S114" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12041,22 +12036,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128819668</v>
+        <v>128834419</v>
       </c>
       <c r="B115" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12088,13 +12083,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>753980</v>
+        <v>754329</v>
       </c>
       <c r="R115" t="n">
-        <v>7294135</v>
+        <v>7293829</v>
       </c>
       <c r="S115" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12138,22 +12133,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128819647</v>
+        <v>128834408</v>
       </c>
       <c r="B116" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12185,13 +12180,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>754139</v>
+        <v>754013</v>
       </c>
       <c r="R116" t="n">
-        <v>7294012</v>
+        <v>7293996</v>
       </c>
       <c r="S116" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12235,44 +12230,44 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128834408</v>
+        <v>128819689</v>
       </c>
       <c r="B117" t="n">
-        <v>80225</v>
+        <v>98636</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12282,13 +12277,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>754013</v>
+        <v>754240</v>
       </c>
       <c r="R117" t="n">
-        <v>7293996</v>
+        <v>7293924</v>
       </c>
       <c r="S117" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12318,6 +12313,11 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Större förekomst</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12332,44 +12332,44 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128834400</v>
+        <v>128834477</v>
       </c>
       <c r="B118" t="n">
-        <v>80225</v>
+        <v>98636</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12379,10 +12379,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>753636</v>
+        <v>754356</v>
       </c>
       <c r="R118" t="n">
-        <v>7294018</v>
+        <v>7293813</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -12415,6 +12415,11 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Ca 2m diam</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12441,10 +12446,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128834477</v>
+        <v>128834469</v>
       </c>
       <c r="B119" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12476,10 +12481,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>754356</v>
+        <v>754222</v>
       </c>
       <c r="R119" t="n">
-        <v>7293813</v>
+        <v>7293912</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -12516,7 +12521,7 @@
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>Ca 2m diam</t>
+          <t>10m diam mycket riklig förekomst</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12543,10 +12548,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128834469</v>
+        <v>128834444</v>
       </c>
       <c r="B120" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12578,10 +12583,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>754222</v>
+        <v>753729</v>
       </c>
       <c r="R120" t="n">
-        <v>7293912</v>
+        <v>7294103</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -12614,11 +12619,6 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>10m diam mycket riklig förekomst</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12645,32 +12645,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128834444</v>
+        <v>128834400</v>
       </c>
       <c r="B121" t="n">
-        <v>98632</v>
+        <v>80229</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12680,10 +12680,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>753729</v>
+        <v>753636</v>
       </c>
       <c r="R121" t="n">
-        <v>7294103</v>
+        <v>7294018</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -12742,48 +12742,45 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128834499</v>
+        <v>128834429</v>
       </c>
       <c r="B122" t="n">
-        <v>91876</v>
+        <v>80229</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1505</v>
+        <v>6458</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Stormansberget, Nb</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>754035</v>
+        <v>754063</v>
       </c>
       <c r="R122" t="n">
-        <v>7294132</v>
+        <v>7294120</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -12824,7 +12821,6 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -12843,45 +12839,48 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128834429</v>
+        <v>128834499</v>
       </c>
       <c r="B123" t="n">
-        <v>80225</v>
+        <v>91880</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6458</v>
+        <v>1505</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Stormansberget, Nb</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>754063</v>
+        <v>754035</v>
       </c>
       <c r="R123" t="n">
-        <v>7294120</v>
+        <v>7294132</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -12922,6 +12921,7 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -12940,32 +12940,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128819697</v>
+        <v>128834373</v>
       </c>
       <c r="B124" t="n">
-        <v>96751</v>
+        <v>91683</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>2869</v>
+        <v>1588</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12975,13 +12975,13 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>754263</v>
+        <v>754056</v>
       </c>
       <c r="R124" t="n">
-        <v>7293846</v>
+        <v>7294109</v>
       </c>
       <c r="S124" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13025,22 +13025,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128834418</v>
+        <v>128834375</v>
       </c>
       <c r="B125" t="n">
-        <v>80225</v>
+        <v>79156</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13048,21 +13048,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13072,10 +13072,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>754325</v>
+        <v>754092</v>
       </c>
       <c r="R125" t="n">
-        <v>7293826</v>
+        <v>7293962</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -13134,10 +13134,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128819653</v>
+        <v>128834418</v>
       </c>
       <c r="B126" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13169,13 +13169,13 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>754304</v>
+        <v>754325</v>
       </c>
       <c r="R126" t="n">
-        <v>7293805</v>
+        <v>7293826</v>
       </c>
       <c r="S126" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13219,22 +13219,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128819650</v>
+        <v>128819694</v>
       </c>
       <c r="B127" t="n">
-        <v>80225</v>
+        <v>56901</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13242,21 +13242,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13266,10 +13266,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>754166</v>
+        <v>754139</v>
       </c>
       <c r="R127" t="n">
-        <v>7293978</v>
+        <v>7294034</v>
       </c>
       <c r="S127" t="n">
         <v>3</v>
@@ -13328,32 +13328,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128819694</v>
+        <v>128819671</v>
       </c>
       <c r="B128" t="n">
-        <v>56898</v>
+        <v>98636</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13363,10 +13363,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>754139</v>
+        <v>753685</v>
       </c>
       <c r="R128" t="n">
-        <v>7294034</v>
+        <v>7294093</v>
       </c>
       <c r="S128" t="n">
         <v>3</v>
@@ -13425,32 +13425,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128834375</v>
+        <v>128834453</v>
       </c>
       <c r="B129" t="n">
-        <v>79152</v>
+        <v>98636</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13460,10 +13460,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>754092</v>
+        <v>753894</v>
       </c>
       <c r="R129" t="n">
-        <v>7293962</v>
+        <v>7293894</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -13496,6 +13496,11 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>5mtr mycket rikligt bestånd</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13522,32 +13527,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128834373</v>
+        <v>128834452</v>
       </c>
       <c r="B130" t="n">
-        <v>91679</v>
+        <v>98636</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1588</v>
+        <v>220787</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13557,10 +13562,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>754056</v>
+        <v>753833</v>
       </c>
       <c r="R130" t="n">
-        <v>7294109</v>
+        <v>7293877</v>
       </c>
       <c r="S130" t="n">
         <v>5</v>
@@ -13619,10 +13624,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128819671</v>
+        <v>128834474</v>
       </c>
       <c r="B131" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13654,13 +13659,13 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>753685</v>
+        <v>754313</v>
       </c>
       <c r="R131" t="n">
-        <v>7294093</v>
+        <v>7293834</v>
       </c>
       <c r="S131" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -13704,22 +13709,22 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128834453</v>
+        <v>128819683</v>
       </c>
       <c r="B132" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13751,13 +13756,13 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>753894</v>
+        <v>754142</v>
       </c>
       <c r="R132" t="n">
-        <v>7293894</v>
+        <v>7294040</v>
       </c>
       <c r="S132" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -13787,11 +13792,6 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>5mtr mycket rikligt bestånd</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -13806,44 +13806,44 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128834452</v>
+        <v>128819697</v>
       </c>
       <c r="B133" t="n">
-        <v>98632</v>
+        <v>96755</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13853,13 +13853,13 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>753833</v>
+        <v>754263</v>
       </c>
       <c r="R133" t="n">
-        <v>7293877</v>
+        <v>7293846</v>
       </c>
       <c r="S133" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -13903,44 +13903,44 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128834474</v>
+        <v>128819650</v>
       </c>
       <c r="B134" t="n">
-        <v>98632</v>
+        <v>80229</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13950,13 +13950,13 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>754313</v>
+        <v>754166</v>
       </c>
       <c r="R134" t="n">
-        <v>7293834</v>
+        <v>7293978</v>
       </c>
       <c r="S134" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14000,44 +14000,44 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128819683</v>
+        <v>128819653</v>
       </c>
       <c r="B135" t="n">
-        <v>98632</v>
+        <v>80229</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14047,10 +14047,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>754142</v>
+        <v>754304</v>
       </c>
       <c r="R135" t="n">
-        <v>7294040</v>
+        <v>7293805</v>
       </c>
       <c r="S135" t="n">
         <v>3</v>
@@ -14109,10 +14109,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128819645</v>
+        <v>128834372</v>
       </c>
       <c r="B136" t="n">
-        <v>80225</v>
+        <v>88772</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14120,21 +14120,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6458</v>
+        <v>4412</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14144,13 +14144,13 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>754081</v>
+        <v>754265</v>
       </c>
       <c r="R136" t="n">
-        <v>7294036</v>
+        <v>7293869</v>
       </c>
       <c r="S136" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -14194,22 +14194,22 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128834402</v>
+        <v>128819651</v>
       </c>
       <c r="B137" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14241,13 +14241,13 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>753663</v>
+        <v>754220</v>
       </c>
       <c r="R137" t="n">
-        <v>7293971</v>
+        <v>7293908</v>
       </c>
       <c r="S137" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -14291,44 +14291,44 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128834498</v>
+        <v>128819669</v>
       </c>
       <c r="B138" t="n">
-        <v>80260</v>
+        <v>80229</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14338,13 +14338,13 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>754129</v>
+        <v>753872</v>
       </c>
       <c r="R138" t="n">
-        <v>7294101</v>
+        <v>7294169</v>
       </c>
       <c r="S138" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -14388,22 +14388,22 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128819651</v>
+        <v>128819645</v>
       </c>
       <c r="B139" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14435,10 +14435,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>754220</v>
+        <v>754081</v>
       </c>
       <c r="R139" t="n">
-        <v>7293908</v>
+        <v>7294036</v>
       </c>
       <c r="S139" t="n">
         <v>3</v>
@@ -14497,10 +14497,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128819669</v>
+        <v>128819640</v>
       </c>
       <c r="B140" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14532,10 +14532,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>753872</v>
+        <v>754021</v>
       </c>
       <c r="R140" t="n">
-        <v>7294169</v>
+        <v>7294099</v>
       </c>
       <c r="S140" t="n">
         <v>3</v>
@@ -14576,6 +14576,7 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -14594,10 +14595,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128819640</v>
+        <v>128834402</v>
       </c>
       <c r="B141" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14629,13 +14630,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>754021</v>
+        <v>753663</v>
       </c>
       <c r="R141" t="n">
-        <v>7294099</v>
+        <v>7293971</v>
       </c>
       <c r="S141" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -14673,51 +14674,50 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
-      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128834372</v>
+        <v>128834498</v>
       </c>
       <c r="B142" t="n">
-        <v>88768</v>
+        <v>80264</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>4412</v>
+        <v>6463</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14727,10 +14727,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>754265</v>
+        <v>754129</v>
       </c>
       <c r="R142" t="n">
-        <v>7293869</v>
+        <v>7294101</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -14789,10 +14789,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128819667</v>
+        <v>128819636</v>
       </c>
       <c r="B143" t="n">
-        <v>80225</v>
+        <v>57880</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14800,21 +14800,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14824,10 +14824,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>754002</v>
+        <v>754361</v>
       </c>
       <c r="R143" t="n">
-        <v>7294106</v>
+        <v>7293841</v>
       </c>
       <c r="S143" t="n">
         <v>3</v>
@@ -14860,6 +14860,11 @@
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>6 individer</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -14886,10 +14891,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128819643</v>
+        <v>128834412</v>
       </c>
       <c r="B144" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14921,13 +14926,13 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>753951</v>
+        <v>754096</v>
       </c>
       <c r="R144" t="n">
-        <v>7293999</v>
+        <v>7293963</v>
       </c>
       <c r="S144" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -14971,44 +14976,44 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128819636</v>
+        <v>128834379</v>
       </c>
       <c r="B145" t="n">
-        <v>57876</v>
+        <v>80258</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15018,13 +15023,13 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>754361</v>
+        <v>753674</v>
       </c>
       <c r="R145" t="n">
-        <v>7293841</v>
+        <v>7293973</v>
       </c>
       <c r="S145" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -15054,11 +15059,6 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>6 individer</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15073,44 +15073,44 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128834379</v>
+        <v>128819667</v>
       </c>
       <c r="B146" t="n">
-        <v>80254</v>
+        <v>80229</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15120,13 +15120,13 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>753674</v>
+        <v>754002</v>
       </c>
       <c r="R146" t="n">
-        <v>7293973</v>
+        <v>7294106</v>
       </c>
       <c r="S146" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -15170,22 +15170,22 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128834412</v>
+        <v>128819643</v>
       </c>
       <c r="B147" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15217,13 +15217,13 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>754096</v>
+        <v>753951</v>
       </c>
       <c r="R147" t="n">
-        <v>7293963</v>
+        <v>7293999</v>
       </c>
       <c r="S147" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -15267,12 +15267,12 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
@@ -15282,7 +15282,7 @@
         <v>128834489</v>
       </c>
       <c r="B148" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15379,7 +15379,7 @@
         <v>128834487</v>
       </c>
       <c r="B149" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15476,7 +15476,7 @@
         <v>128819682</v>
       </c>
       <c r="B150" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15578,7 +15578,7 @@
         <v>128834389</v>
       </c>
       <c r="B151" t="n">
-        <v>80129</v>
+        <v>80133</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15675,7 +15675,7 @@
         <v>128834422</v>
       </c>
       <c r="B152" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15772,7 +15772,7 @@
         <v>128834472</v>
       </c>
       <c r="B153" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15874,7 +15874,7 @@
         <v>128834475</v>
       </c>
       <c r="B154" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15973,32 +15973,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128834413</v>
+        <v>128834391</v>
       </c>
       <c r="B155" t="n">
-        <v>80225</v>
+        <v>97507</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16008,10 +16008,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>754091</v>
+        <v>754184</v>
       </c>
       <c r="R155" t="n">
-        <v>7293941</v>
+        <v>7294045</v>
       </c>
       <c r="S155" t="n">
         <v>5</v>
@@ -16070,32 +16070,32 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128819646</v>
+        <v>128834470</v>
       </c>
       <c r="B156" t="n">
-        <v>80225</v>
+        <v>98636</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16105,13 +16105,13 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>754143</v>
+        <v>754249</v>
       </c>
       <c r="R156" t="n">
-        <v>7294037</v>
+        <v>7293901</v>
       </c>
       <c r="S156" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -16155,44 +16155,44 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128834391</v>
+        <v>128819692</v>
       </c>
       <c r="B157" t="n">
-        <v>97503</v>
+        <v>98636</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16202,13 +16202,13 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>754184</v>
+        <v>754049</v>
       </c>
       <c r="R157" t="n">
-        <v>7294045</v>
+        <v>7294082</v>
       </c>
       <c r="S157" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -16238,6 +16238,11 @@
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>Stor förekomst</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16252,22 +16257,22 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128834470</v>
+        <v>128819691</v>
       </c>
       <c r="B158" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16299,13 +16304,13 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>754249</v>
+        <v>754222</v>
       </c>
       <c r="R158" t="n">
-        <v>7293901</v>
+        <v>7293998</v>
       </c>
       <c r="S158" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -16335,6 +16340,11 @@
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>Större område</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -16349,22 +16359,22 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128819692</v>
+        <v>128834485</v>
       </c>
       <c r="B159" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16396,13 +16406,13 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>754049</v>
+        <v>754182</v>
       </c>
       <c r="R159" t="n">
-        <v>7294082</v>
+        <v>7294034</v>
       </c>
       <c r="S159" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -16436,7 +16446,7 @@
       </c>
       <c r="AC159" t="inlineStr">
         <is>
-          <t>Stor förekomst</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -16451,22 +16461,22 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128819691</v>
+        <v>128819688</v>
       </c>
       <c r="B160" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16498,10 +16508,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>754222</v>
+        <v>754342</v>
       </c>
       <c r="R160" t="n">
-        <v>7293998</v>
+        <v>7293868</v>
       </c>
       <c r="S160" t="n">
         <v>3</v>
@@ -16534,11 +16544,6 @@
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC160" t="inlineStr">
-        <is>
-          <t>Större område</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -16565,32 +16570,32 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128834485</v>
+        <v>128834413</v>
       </c>
       <c r="B161" t="n">
-        <v>98632</v>
+        <v>80229</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16600,10 +16605,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>754182</v>
+        <v>754091</v>
       </c>
       <c r="R161" t="n">
-        <v>7294034</v>
+        <v>7293941</v>
       </c>
       <c r="S161" t="n">
         <v>5</v>
@@ -16636,11 +16641,6 @@
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC161" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -16667,32 +16667,32 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128819688</v>
+        <v>128819646</v>
       </c>
       <c r="B162" t="n">
-        <v>98632</v>
+        <v>80229</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -16702,10 +16702,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>754342</v>
+        <v>754143</v>
       </c>
       <c r="R162" t="n">
-        <v>7293868</v>
+        <v>7294037</v>
       </c>
       <c r="S162" t="n">
         <v>3</v>
@@ -16767,7 +16767,7 @@
         <v>128834425</v>
       </c>
       <c r="B163" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16864,7 +16864,7 @@
         <v>128834383</v>
       </c>
       <c r="B164" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>

--- a/artfynd/A 41034-2025 artfynd.xlsx
+++ b/artfynd/A 41034-2025 artfynd.xlsx
@@ -3688,7 +3688,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128834411</v>
+        <v>128834420</v>
       </c>
       <c r="B30" t="n">
         <v>80229</v>
@@ -3723,10 +3723,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>754071</v>
+        <v>754338</v>
       </c>
       <c r="R30" t="n">
-        <v>7293962</v>
+        <v>7293821</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3785,7 +3785,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128834420</v>
+        <v>128834411</v>
       </c>
       <c r="B31" t="n">
         <v>80229</v>
@@ -3820,10 +3820,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>754338</v>
+        <v>754071</v>
       </c>
       <c r="R31" t="n">
-        <v>7293821</v>
+        <v>7293962</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4382,10 +4382,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128834434</v>
+        <v>128834378</v>
       </c>
       <c r="B37" t="n">
-        <v>95486</v>
+        <v>80258</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4393,21 +4393,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2387</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4417,10 +4417,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>753879</v>
+        <v>753636</v>
       </c>
       <c r="R37" t="n">
-        <v>7293890</v>
+        <v>7294023</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4673,32 +4673,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128834390</v>
+        <v>128819663</v>
       </c>
       <c r="B40" t="n">
-        <v>80133</v>
+        <v>80229</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4708,13 +4708,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>754064</v>
+        <v>754152</v>
       </c>
       <c r="R40" t="n">
-        <v>7294121</v>
+        <v>7294076</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4758,12 +4758,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4867,32 +4867,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128819663</v>
+        <v>128834434</v>
       </c>
       <c r="B42" t="n">
-        <v>80229</v>
+        <v>95486</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>2387</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4902,13 +4902,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>754152</v>
+        <v>753879</v>
       </c>
       <c r="R42" t="n">
-        <v>7294076</v>
+        <v>7293890</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4952,22 +4952,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128834378</v>
+        <v>128834390</v>
       </c>
       <c r="B43" t="n">
-        <v>80258</v>
+        <v>80133</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4975,21 +4975,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>753636</v>
+        <v>754064</v>
       </c>
       <c r="R43" t="n">
-        <v>7294023</v>
+        <v>7294121</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5352,32 +5352,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128834386</v>
+        <v>128834454</v>
       </c>
       <c r="B47" t="n">
-        <v>57717</v>
+        <v>98636</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5387,10 +5387,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>753889</v>
+        <v>753898</v>
       </c>
       <c r="R47" t="n">
-        <v>7294195</v>
+        <v>7293898</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5427,7 +5427,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Hack vid trädbas</t>
+          <t>3mtr diam</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5454,7 +5454,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128834454</v>
+        <v>128819675</v>
       </c>
       <c r="B48" t="n">
         <v>98636</v>
@@ -5489,13 +5489,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>753898</v>
+        <v>753812</v>
       </c>
       <c r="R48" t="n">
-        <v>7293898</v>
+        <v>7293999</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>3mtr diam</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5544,44 +5544,44 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128819675</v>
+        <v>128834386</v>
       </c>
       <c r="B49" t="n">
-        <v>98636</v>
+        <v>57717</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5591,13 +5591,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>753812</v>
+        <v>753889</v>
       </c>
       <c r="R49" t="n">
-        <v>7293999</v>
+        <v>7294195</v>
       </c>
       <c r="S49" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Hack vid trädbas</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5646,44 +5646,44 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128819693</v>
+        <v>128834406</v>
       </c>
       <c r="B50" t="n">
-        <v>98636</v>
+        <v>80229</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5693,13 +5693,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>754024</v>
+        <v>753974</v>
       </c>
       <c r="R50" t="n">
-        <v>7294106</v>
+        <v>7294029</v>
       </c>
       <c r="S50" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5729,11 +5729,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>På ett större område mer än 30 individer</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5748,44 +5743,44 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128834484</v>
+        <v>128834430</v>
       </c>
       <c r="B51" t="n">
-        <v>98636</v>
+        <v>80229</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5795,10 +5790,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>754289</v>
+        <v>754027</v>
       </c>
       <c r="R51" t="n">
-        <v>7293999</v>
+        <v>7294150</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5831,11 +5826,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Riklig förekomst  ca 6m diam</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5862,32 +5852,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128834406</v>
+        <v>128819690</v>
       </c>
       <c r="B52" t="n">
-        <v>80229</v>
+        <v>98636</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5897,13 +5887,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>753974</v>
+        <v>754224</v>
       </c>
       <c r="R52" t="n">
-        <v>7294029</v>
+        <v>7293966</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5947,44 +5937,44 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128834430</v>
+        <v>128819693</v>
       </c>
       <c r="B53" t="n">
-        <v>80229</v>
+        <v>98636</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5994,13 +5984,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>754027</v>
+        <v>754024</v>
       </c>
       <c r="R53" t="n">
-        <v>7294150</v>
+        <v>7294106</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6030,6 +6020,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>På ett större område mer än 30 individer</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6044,19 +6039,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128819690</v>
+        <v>128834484</v>
       </c>
       <c r="B54" t="n">
         <v>98636</v>
@@ -6091,13 +6086,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>754224</v>
+        <v>754289</v>
       </c>
       <c r="R54" t="n">
-        <v>7293966</v>
+        <v>7293999</v>
       </c>
       <c r="S54" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6127,6 +6122,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Riklig förekomst  ca 6m diam</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6141,44 +6141,44 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128834446</v>
+        <v>128819639</v>
       </c>
       <c r="B55" t="n">
-        <v>98636</v>
+        <v>91804</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6188,13 +6188,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>753638</v>
+        <v>754249</v>
       </c>
       <c r="R55" t="n">
-        <v>7293994</v>
+        <v>7293891</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Mycket rikligt bestånd</t>
+          <t>10 fruktkroppar</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6243,44 +6243,44 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128834449</v>
+        <v>128834376</v>
       </c>
       <c r="B56" t="n">
-        <v>98636</v>
+        <v>91508</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6290,10 +6290,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>753732</v>
+        <v>754253</v>
       </c>
       <c r="R56" t="n">
-        <v>7293989</v>
+        <v>7293898</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6326,11 +6326,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Mycket rikligt bestånd</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6357,32 +6352,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128819680</v>
+        <v>128819648</v>
       </c>
       <c r="B57" t="n">
-        <v>98636</v>
+        <v>80229</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6392,10 +6387,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>754079</v>
+        <v>754142</v>
       </c>
       <c r="R57" t="n">
-        <v>7294043</v>
+        <v>7293999</v>
       </c>
       <c r="S57" t="n">
         <v>3</v>
@@ -6428,11 +6423,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Rik förekomst</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6459,10 +6449,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128819639</v>
+        <v>128834404</v>
       </c>
       <c r="B58" t="n">
-        <v>91804</v>
+        <v>80229</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6470,21 +6460,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6494,13 +6484,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>754249</v>
+        <v>753693</v>
       </c>
       <c r="R58" t="n">
-        <v>7293891</v>
+        <v>7293978</v>
       </c>
       <c r="S58" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6530,11 +6520,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>10 fruktkroppar</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6549,22 +6534,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128834376</v>
+        <v>128834491</v>
       </c>
       <c r="B59" t="n">
-        <v>91508</v>
+        <v>56901</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6572,21 +6557,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6596,10 +6581,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>754253</v>
+        <v>753881</v>
       </c>
       <c r="R59" t="n">
-        <v>7293898</v>
+        <v>7293891</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6658,32 +6643,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128834491</v>
+        <v>128834446</v>
       </c>
       <c r="B60" t="n">
-        <v>56901</v>
+        <v>98636</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6693,10 +6678,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>753881</v>
+        <v>753638</v>
       </c>
       <c r="R60" t="n">
-        <v>7293891</v>
+        <v>7293994</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6729,6 +6714,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Mycket rikligt bestånd</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6755,32 +6745,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128834433</v>
+        <v>128834449</v>
       </c>
       <c r="B61" t="n">
-        <v>95486</v>
+        <v>98636</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2387</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6790,10 +6780,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>753867</v>
+        <v>753732</v>
       </c>
       <c r="R61" t="n">
-        <v>7293877</v>
+        <v>7293989</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6826,6 +6816,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Mycket rikligt bestånd</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6852,32 +6847,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128834404</v>
+        <v>128819680</v>
       </c>
       <c r="B62" t="n">
-        <v>80229</v>
+        <v>98636</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6887,13 +6882,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>753693</v>
+        <v>754079</v>
       </c>
       <c r="R62" t="n">
-        <v>7293978</v>
+        <v>7294043</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6923,6 +6918,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Rik förekomst</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6937,44 +6937,44 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128819648</v>
+        <v>128834433</v>
       </c>
       <c r="B63" t="n">
-        <v>80229</v>
+        <v>95486</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>2387</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6984,13 +6984,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>754142</v>
+        <v>753867</v>
       </c>
       <c r="R63" t="n">
-        <v>7293999</v>
+        <v>7293877</v>
       </c>
       <c r="S63" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7034,44 +7034,44 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128834416</v>
+        <v>128834457</v>
       </c>
       <c r="B64" t="n">
-        <v>80229</v>
+        <v>98636</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7081,10 +7081,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>754148</v>
+        <v>753947</v>
       </c>
       <c r="R64" t="n">
-        <v>7293935</v>
+        <v>7293964</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7117,6 +7117,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>5mtr diam</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7143,32 +7148,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128834407</v>
+        <v>128834463</v>
       </c>
       <c r="B65" t="n">
-        <v>80229</v>
+        <v>98636</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7178,10 +7183,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>753989</v>
+        <v>754071</v>
       </c>
       <c r="R65" t="n">
-        <v>7294010</v>
+        <v>7293964</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7240,32 +7245,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128834380</v>
+        <v>128834458</v>
       </c>
       <c r="B66" t="n">
-        <v>80258</v>
+        <v>98636</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7275,10 +7280,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>754091</v>
+        <v>753959</v>
       </c>
       <c r="R66" t="n">
-        <v>7293941</v>
+        <v>7294022</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7311,6 +7316,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>3m diam</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7337,7 +7347,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128834457</v>
+        <v>128819677</v>
       </c>
       <c r="B67" t="n">
         <v>98636</v>
@@ -7372,13 +7382,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>753947</v>
+        <v>753875</v>
       </c>
       <c r="R67" t="n">
-        <v>7293964</v>
+        <v>7294001</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7408,11 +7418,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>5mtr diam</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7427,19 +7432,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128834463</v>
+        <v>128834461</v>
       </c>
       <c r="B68" t="n">
         <v>98636</v>
@@ -7474,10 +7479,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>754071</v>
+        <v>753981</v>
       </c>
       <c r="R68" t="n">
-        <v>7293964</v>
+        <v>7294022</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7536,32 +7541,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128834458</v>
+        <v>128834416</v>
       </c>
       <c r="B69" t="n">
-        <v>98636</v>
+        <v>80229</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7571,10 +7576,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>753959</v>
+        <v>754148</v>
       </c>
       <c r="R69" t="n">
-        <v>7294022</v>
+        <v>7293935</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7607,11 +7612,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>3m diam</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7638,32 +7638,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128819677</v>
+        <v>128834407</v>
       </c>
       <c r="B70" t="n">
-        <v>98636</v>
+        <v>80229</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7673,13 +7673,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>753875</v>
+        <v>753989</v>
       </c>
       <c r="R70" t="n">
-        <v>7294001</v>
+        <v>7294010</v>
       </c>
       <c r="S70" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7723,44 +7723,44 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128834461</v>
+        <v>128834380</v>
       </c>
       <c r="B71" t="n">
-        <v>98636</v>
+        <v>80258</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7770,10 +7770,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>753981</v>
+        <v>754091</v>
       </c>
       <c r="R71" t="n">
-        <v>7294022</v>
+        <v>7293941</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7832,32 +7832,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128834401</v>
+        <v>128819676</v>
       </c>
       <c r="B72" t="n">
-        <v>80229</v>
+        <v>98636</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7867,13 +7867,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>753629</v>
+        <v>753836</v>
       </c>
       <c r="R72" t="n">
-        <v>7294009</v>
+        <v>7293977</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7903,6 +7903,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7917,44 +7922,44 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128834409</v>
+        <v>128834476</v>
       </c>
       <c r="B73" t="n">
-        <v>80229</v>
+        <v>98636</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7964,10 +7969,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>754042</v>
+        <v>754345</v>
       </c>
       <c r="R73" t="n">
-        <v>7293966</v>
+        <v>7293808</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8000,6 +8005,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>3m diam</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8026,32 +8036,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128819652</v>
+        <v>128834443</v>
       </c>
       <c r="B74" t="n">
-        <v>80229</v>
+        <v>98636</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8061,13 +8071,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>754297</v>
+        <v>754042</v>
       </c>
       <c r="R74" t="n">
-        <v>7293780</v>
+        <v>7294129</v>
       </c>
       <c r="S74" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8097,6 +8107,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Måttlig förekomst 6m diam</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8111,44 +8126,44 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128834431</v>
+        <v>128834456</v>
       </c>
       <c r="B75" t="n">
-        <v>80265</v>
+        <v>98636</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8158,10 +8173,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>754087</v>
+        <v>753917</v>
       </c>
       <c r="R75" t="n">
-        <v>7293941</v>
+        <v>7293936</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8220,32 +8235,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128819676</v>
+        <v>128834401</v>
       </c>
       <c r="B76" t="n">
-        <v>98636</v>
+        <v>80229</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8255,13 +8270,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>753836</v>
+        <v>753629</v>
       </c>
       <c r="R76" t="n">
-        <v>7293977</v>
+        <v>7294009</v>
       </c>
       <c r="S76" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8291,11 +8306,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8310,44 +8320,44 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128834476</v>
+        <v>128834409</v>
       </c>
       <c r="B77" t="n">
-        <v>98636</v>
+        <v>80229</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8357,10 +8367,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>754345</v>
+        <v>754042</v>
       </c>
       <c r="R77" t="n">
-        <v>7293808</v>
+        <v>7293966</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8393,11 +8403,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>3m diam</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8424,32 +8429,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128834443</v>
+        <v>128834431</v>
       </c>
       <c r="B78" t="n">
-        <v>98636</v>
+        <v>80265</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8459,10 +8464,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>754042</v>
+        <v>754087</v>
       </c>
       <c r="R78" t="n">
-        <v>7294129</v>
+        <v>7293941</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8495,11 +8500,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Måttlig förekomst 6m diam</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8526,32 +8526,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128834456</v>
+        <v>128819652</v>
       </c>
       <c r="B79" t="n">
-        <v>98636</v>
+        <v>80229</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8561,13 +8561,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>753917</v>
+        <v>754297</v>
       </c>
       <c r="R79" t="n">
-        <v>7293936</v>
+        <v>7293780</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8611,44 +8611,44 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128819637</v>
+        <v>128834497</v>
       </c>
       <c r="B80" t="n">
-        <v>57717</v>
+        <v>80264</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8658,13 +8658,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>753970</v>
+        <v>754176</v>
       </c>
       <c r="R80" t="n">
-        <v>7294021</v>
+        <v>7293924</v>
       </c>
       <c r="S80" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8708,22 +8708,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128834492</v>
+        <v>128819655</v>
       </c>
       <c r="B81" t="n">
-        <v>56901</v>
+        <v>80229</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8731,21 +8731,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8755,13 +8755,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>753985</v>
+        <v>754314</v>
       </c>
       <c r="R81" t="n">
-        <v>7294023</v>
+        <v>7293792</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8805,22 +8805,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128834497</v>
+        <v>128834381</v>
       </c>
       <c r="B82" t="n">
-        <v>80264</v>
+        <v>80258</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8828,21 +8828,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8852,10 +8852,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>754176</v>
+        <v>754177</v>
       </c>
       <c r="R82" t="n">
-        <v>7293924</v>
+        <v>7293925</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -8914,7 +8914,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128819655</v>
+        <v>128819664</v>
       </c>
       <c r="B83" t="n">
         <v>80229</v>
@@ -8949,10 +8949,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>754314</v>
+        <v>754142</v>
       </c>
       <c r="R83" t="n">
-        <v>7293792</v>
+        <v>7294080</v>
       </c>
       <c r="S83" t="n">
         <v>3</v>
@@ -9011,10 +9011,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128819664</v>
+        <v>128819637</v>
       </c>
       <c r="B84" t="n">
-        <v>80229</v>
+        <v>57717</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9022,21 +9022,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9046,10 +9046,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>754142</v>
+        <v>753970</v>
       </c>
       <c r="R84" t="n">
-        <v>7294080</v>
+        <v>7294021</v>
       </c>
       <c r="S84" t="n">
         <v>3</v>
@@ -9108,32 +9108,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128834381</v>
+        <v>128834492</v>
       </c>
       <c r="B85" t="n">
-        <v>80258</v>
+        <v>56901</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6462</v>
+        <v>102612</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9143,10 +9143,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>754177</v>
+        <v>753985</v>
       </c>
       <c r="R85" t="n">
-        <v>7293925</v>
+        <v>7294023</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -10088,7 +10088,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128819654</v>
+        <v>128819649</v>
       </c>
       <c r="B95" t="n">
         <v>80229</v>
@@ -10123,10 +10123,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>754303</v>
+        <v>754149</v>
       </c>
       <c r="R95" t="n">
-        <v>7293804</v>
+        <v>7293983</v>
       </c>
       <c r="S95" t="n">
         <v>3</v>
@@ -10185,7 +10185,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128819649</v>
+        <v>128819654</v>
       </c>
       <c r="B96" t="n">
         <v>80229</v>
@@ -10220,10 +10220,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>754149</v>
+        <v>754303</v>
       </c>
       <c r="R96" t="n">
-        <v>7293983</v>
+        <v>7293804</v>
       </c>
       <c r="S96" t="n">
         <v>3</v>
@@ -10578,32 +10578,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128819679</v>
+        <v>128819644</v>
       </c>
       <c r="B100" t="n">
-        <v>98636</v>
+        <v>80229</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10613,10 +10613,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>754015</v>
+        <v>754003</v>
       </c>
       <c r="R100" t="n">
-        <v>7294040</v>
+        <v>7294039</v>
       </c>
       <c r="S100" t="n">
         <v>3</v>
@@ -10649,11 +10649,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10680,32 +10675,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128834451</v>
+        <v>128834428</v>
       </c>
       <c r="B101" t="n">
-        <v>98636</v>
+        <v>80229</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10715,10 +10710,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>753769</v>
+        <v>754137</v>
       </c>
       <c r="R101" t="n">
-        <v>7293962</v>
+        <v>7294102</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -10777,32 +10772,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128834448</v>
+        <v>128834399</v>
       </c>
       <c r="B102" t="n">
-        <v>98636</v>
+        <v>80229</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10812,10 +10807,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>753692</v>
+        <v>753717</v>
       </c>
       <c r="R102" t="n">
-        <v>7293978</v>
+        <v>7294108</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -10874,32 +10869,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128834428</v>
+        <v>128819679</v>
       </c>
       <c r="B103" t="n">
-        <v>80229</v>
+        <v>98636</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10909,13 +10904,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>754137</v>
+        <v>754015</v>
       </c>
       <c r="R103" t="n">
-        <v>7294102</v>
+        <v>7294040</v>
       </c>
       <c r="S103" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -10945,6 +10940,11 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10959,44 +10959,44 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128834399</v>
+        <v>128834451</v>
       </c>
       <c r="B104" t="n">
-        <v>80229</v>
+        <v>98636</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11006,10 +11006,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>753717</v>
+        <v>753769</v>
       </c>
       <c r="R104" t="n">
-        <v>7294108</v>
+        <v>7293962</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -11068,32 +11068,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128819644</v>
+        <v>128834448</v>
       </c>
       <c r="B105" t="n">
-        <v>80229</v>
+        <v>98636</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11103,13 +11103,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>754003</v>
+        <v>753692</v>
       </c>
       <c r="R105" t="n">
-        <v>7294039</v>
+        <v>7293978</v>
       </c>
       <c r="S105" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11153,12 +11153,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
@@ -11854,7 +11854,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128819668</v>
+        <v>128834408</v>
       </c>
       <c r="B113" t="n">
         <v>80229</v>
@@ -11889,13 +11889,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>753980</v>
+        <v>754013</v>
       </c>
       <c r="R113" t="n">
-        <v>7294135</v>
+        <v>7293996</v>
       </c>
       <c r="S113" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -11939,19 +11939,19 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128819647</v>
+        <v>128819668</v>
       </c>
       <c r="B114" t="n">
         <v>80229</v>
@@ -11986,10 +11986,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>754139</v>
+        <v>753980</v>
       </c>
       <c r="R114" t="n">
-        <v>7294012</v>
+        <v>7294135</v>
       </c>
       <c r="S114" t="n">
         <v>3</v>
@@ -12048,7 +12048,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128834419</v>
+        <v>128819647</v>
       </c>
       <c r="B115" t="n">
         <v>80229</v>
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>754329</v>
+        <v>754139</v>
       </c>
       <c r="R115" t="n">
-        <v>7293829</v>
+        <v>7294012</v>
       </c>
       <c r="S115" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12133,19 +12133,19 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128834408</v>
+        <v>128834419</v>
       </c>
       <c r="B116" t="n">
         <v>80229</v>
@@ -12180,10 +12180,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>754013</v>
+        <v>754329</v>
       </c>
       <c r="R116" t="n">
-        <v>7293996</v>
+        <v>7293829</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -12344,10 +12344,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128834477</v>
+        <v>128834499</v>
       </c>
       <c r="B118" t="n">
-        <v>98636</v>
+        <v>91880</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12355,34 +12355,37 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220787</v>
+        <v>1505</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Stormansberget, Nb</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>754356</v>
+        <v>754035</v>
       </c>
       <c r="R118" t="n">
-        <v>7293813</v>
+        <v>7294132</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -12417,17 +12420,13 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Ca 2m diam</t>
-        </is>
-      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
       <c r="AE118" t="b">
         <v>0</v>
       </c>
+      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -12446,32 +12445,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128834469</v>
+        <v>128834429</v>
       </c>
       <c r="B119" t="n">
-        <v>98636</v>
+        <v>80229</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12481,10 +12480,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>754222</v>
+        <v>754063</v>
       </c>
       <c r="R119" t="n">
-        <v>7293912</v>
+        <v>7294120</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -12517,11 +12516,6 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>10m diam mycket riklig förekomst</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12548,32 +12542,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128834444</v>
+        <v>128834400</v>
       </c>
       <c r="B120" t="n">
-        <v>98636</v>
+        <v>80229</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12583,10 +12577,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>753729</v>
+        <v>753636</v>
       </c>
       <c r="R120" t="n">
-        <v>7294103</v>
+        <v>7294018</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -12645,32 +12639,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128834400</v>
+        <v>128834469</v>
       </c>
       <c r="B121" t="n">
-        <v>80229</v>
+        <v>98636</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12680,10 +12674,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>753636</v>
+        <v>754222</v>
       </c>
       <c r="R121" t="n">
-        <v>7294018</v>
+        <v>7293912</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -12716,6 +12710,11 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>10m diam mycket riklig förekomst</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12742,32 +12741,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128834429</v>
+        <v>128834477</v>
       </c>
       <c r="B122" t="n">
-        <v>80229</v>
+        <v>98636</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12777,10 +12776,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>754063</v>
+        <v>754356</v>
       </c>
       <c r="R122" t="n">
-        <v>7294120</v>
+        <v>7293813</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -12813,6 +12812,11 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Ca 2m diam</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12839,10 +12843,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128834499</v>
+        <v>128834444</v>
       </c>
       <c r="B123" t="n">
-        <v>91880</v>
+        <v>98636</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12850,37 +12854,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1505</v>
+        <v>220787</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Stormansberget, Nb</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>754035</v>
+        <v>753729</v>
       </c>
       <c r="R123" t="n">
-        <v>7294132</v>
+        <v>7294103</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -12921,7 +12922,6 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -12940,32 +12940,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128834373</v>
+        <v>128819671</v>
       </c>
       <c r="B124" t="n">
-        <v>91683</v>
+        <v>98636</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1588</v>
+        <v>220787</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12975,13 +12975,13 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>754056</v>
+        <v>753685</v>
       </c>
       <c r="R124" t="n">
-        <v>7294109</v>
+        <v>7294093</v>
       </c>
       <c r="S124" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13025,44 +13025,44 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128834375</v>
+        <v>128834453</v>
       </c>
       <c r="B125" t="n">
-        <v>79156</v>
+        <v>98636</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13072,10 +13072,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>754092</v>
+        <v>753894</v>
       </c>
       <c r="R125" t="n">
-        <v>7293962</v>
+        <v>7293894</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -13108,6 +13108,11 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>5mtr mycket rikligt bestånd</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13134,32 +13139,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128834418</v>
+        <v>128834452</v>
       </c>
       <c r="B126" t="n">
-        <v>80229</v>
+        <v>98636</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13169,10 +13174,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>754325</v>
+        <v>753833</v>
       </c>
       <c r="R126" t="n">
-        <v>7293826</v>
+        <v>7293877</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -13231,32 +13236,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128819694</v>
+        <v>128834474</v>
       </c>
       <c r="B127" t="n">
-        <v>56901</v>
+        <v>98636</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13266,13 +13271,13 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>754139</v>
+        <v>754313</v>
       </c>
       <c r="R127" t="n">
-        <v>7294034</v>
+        <v>7293834</v>
       </c>
       <c r="S127" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -13316,19 +13321,19 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128819671</v>
+        <v>128819683</v>
       </c>
       <c r="B128" t="n">
         <v>98636</v>
@@ -13363,10 +13368,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>753685</v>
+        <v>754142</v>
       </c>
       <c r="R128" t="n">
-        <v>7294093</v>
+        <v>7294040</v>
       </c>
       <c r="S128" t="n">
         <v>3</v>
@@ -13425,32 +13430,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128834453</v>
+        <v>128819697</v>
       </c>
       <c r="B129" t="n">
-        <v>98636</v>
+        <v>96755</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13460,13 +13465,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>753894</v>
+        <v>754263</v>
       </c>
       <c r="R129" t="n">
-        <v>7293894</v>
+        <v>7293846</v>
       </c>
       <c r="S129" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -13496,11 +13501,6 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>5mtr mycket rikligt bestånd</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13515,44 +13515,44 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128834452</v>
+        <v>128834373</v>
       </c>
       <c r="B130" t="n">
-        <v>98636</v>
+        <v>91683</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>220787</v>
+        <v>1588</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13562,10 +13562,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>753833</v>
+        <v>754056</v>
       </c>
       <c r="R130" t="n">
-        <v>7293877</v>
+        <v>7294109</v>
       </c>
       <c r="S130" t="n">
         <v>5</v>
@@ -13624,32 +13624,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128834474</v>
+        <v>128834375</v>
       </c>
       <c r="B131" t="n">
-        <v>98636</v>
+        <v>79156</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13659,10 +13659,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>754313</v>
+        <v>754092</v>
       </c>
       <c r="R131" t="n">
-        <v>7293834</v>
+        <v>7293962</v>
       </c>
       <c r="S131" t="n">
         <v>5</v>
@@ -13721,32 +13721,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128819683</v>
+        <v>128819653</v>
       </c>
       <c r="B132" t="n">
-        <v>98636</v>
+        <v>80229</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13756,10 +13756,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>754142</v>
+        <v>754304</v>
       </c>
       <c r="R132" t="n">
-        <v>7294040</v>
+        <v>7293805</v>
       </c>
       <c r="S132" t="n">
         <v>3</v>
@@ -13818,32 +13818,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128819697</v>
+        <v>128819650</v>
       </c>
       <c r="B133" t="n">
-        <v>96755</v>
+        <v>80229</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>2869</v>
+        <v>6458</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13853,10 +13853,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>754263</v>
+        <v>754166</v>
       </c>
       <c r="R133" t="n">
-        <v>7293846</v>
+        <v>7293978</v>
       </c>
       <c r="S133" t="n">
         <v>3</v>
@@ -13915,7 +13915,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128819650</v>
+        <v>128834418</v>
       </c>
       <c r="B134" t="n">
         <v>80229</v>
@@ -13950,13 +13950,13 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>754166</v>
+        <v>754325</v>
       </c>
       <c r="R134" t="n">
-        <v>7293978</v>
+        <v>7293826</v>
       </c>
       <c r="S134" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14000,22 +14000,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128819653</v>
+        <v>128819694</v>
       </c>
       <c r="B135" t="n">
-        <v>80229</v>
+        <v>56901</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14023,21 +14023,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14047,10 +14047,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>754304</v>
+        <v>754139</v>
       </c>
       <c r="R135" t="n">
-        <v>7293805</v>
+        <v>7294034</v>
       </c>
       <c r="S135" t="n">
         <v>3</v>
@@ -14206,7 +14206,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128819651</v>
+        <v>128819669</v>
       </c>
       <c r="B137" t="n">
         <v>80229</v>
@@ -14241,10 +14241,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>754220</v>
+        <v>753872</v>
       </c>
       <c r="R137" t="n">
-        <v>7293908</v>
+        <v>7294169</v>
       </c>
       <c r="S137" t="n">
         <v>3</v>
@@ -14303,7 +14303,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128819669</v>
+        <v>128819640</v>
       </c>
       <c r="B138" t="n">
         <v>80229</v>
@@ -14338,10 +14338,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>753872</v>
+        <v>754021</v>
       </c>
       <c r="R138" t="n">
-        <v>7294169</v>
+        <v>7294099</v>
       </c>
       <c r="S138" t="n">
         <v>3</v>
@@ -14382,6 +14382,7 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
+      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -14400,7 +14401,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128819645</v>
+        <v>128834402</v>
       </c>
       <c r="B139" t="n">
         <v>80229</v>
@@ -14435,13 +14436,13 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>754081</v>
+        <v>753663</v>
       </c>
       <c r="R139" t="n">
-        <v>7294036</v>
+        <v>7293971</v>
       </c>
       <c r="S139" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -14485,19 +14486,19 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128819640</v>
+        <v>128819645</v>
       </c>
       <c r="B140" t="n">
         <v>80229</v>
@@ -14532,10 +14533,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>754021</v>
+        <v>754081</v>
       </c>
       <c r="R140" t="n">
-        <v>7294099</v>
+        <v>7294036</v>
       </c>
       <c r="S140" t="n">
         <v>3</v>
@@ -14576,7 +14577,6 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -14595,32 +14595,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128834402</v>
+        <v>128834498</v>
       </c>
       <c r="B141" t="n">
-        <v>80229</v>
+        <v>80264</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14630,10 +14630,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>753663</v>
+        <v>754129</v>
       </c>
       <c r="R141" t="n">
-        <v>7293971</v>
+        <v>7294101</v>
       </c>
       <c r="S141" t="n">
         <v>5</v>
@@ -14692,32 +14692,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128834498</v>
+        <v>128819651</v>
       </c>
       <c r="B142" t="n">
-        <v>80264</v>
+        <v>80229</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14727,13 +14727,13 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>754129</v>
+        <v>754220</v>
       </c>
       <c r="R142" t="n">
-        <v>7294101</v>
+        <v>7293908</v>
       </c>
       <c r="S142" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -14777,12 +14777,12 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
@@ -14891,32 +14891,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128834412</v>
+        <v>128834489</v>
       </c>
       <c r="B144" t="n">
-        <v>80229</v>
+        <v>98636</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -14926,10 +14926,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>754096</v>
+        <v>754044</v>
       </c>
       <c r="R144" t="n">
-        <v>7293963</v>
+        <v>7294116</v>
       </c>
       <c r="S144" t="n">
         <v>5</v>
@@ -14988,32 +14988,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128834379</v>
+        <v>128834487</v>
       </c>
       <c r="B145" t="n">
-        <v>80258</v>
+        <v>98636</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15023,10 +15023,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>753674</v>
+        <v>754147</v>
       </c>
       <c r="R145" t="n">
-        <v>7293973</v>
+        <v>7294086</v>
       </c>
       <c r="S145" t="n">
         <v>5</v>
@@ -15085,32 +15085,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128819667</v>
+        <v>128819682</v>
       </c>
       <c r="B146" t="n">
-        <v>80229</v>
+        <v>98636</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15120,10 +15120,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>754002</v>
+        <v>754120</v>
       </c>
       <c r="R146" t="n">
-        <v>7294106</v>
+        <v>7294078</v>
       </c>
       <c r="S146" t="n">
         <v>3</v>
@@ -15156,6 +15156,11 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>Riktig förekomst</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15182,7 +15187,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128819643</v>
+        <v>128834412</v>
       </c>
       <c r="B147" t="n">
         <v>80229</v>
@@ -15217,13 +15222,13 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>753951</v>
+        <v>754096</v>
       </c>
       <c r="R147" t="n">
-        <v>7293999</v>
+        <v>7293963</v>
       </c>
       <c r="S147" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -15267,44 +15272,44 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128834489</v>
+        <v>128819667</v>
       </c>
       <c r="B148" t="n">
-        <v>98636</v>
+        <v>80229</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15314,13 +15319,13 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>754044</v>
+        <v>754002</v>
       </c>
       <c r="R148" t="n">
-        <v>7294116</v>
+        <v>7294106</v>
       </c>
       <c r="S148" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -15364,44 +15369,44 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128834487</v>
+        <v>128834379</v>
       </c>
       <c r="B149" t="n">
-        <v>98636</v>
+        <v>80258</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15411,10 +15416,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>754147</v>
+        <v>753674</v>
       </c>
       <c r="R149" t="n">
-        <v>7294086</v>
+        <v>7293973</v>
       </c>
       <c r="S149" t="n">
         <v>5</v>
@@ -15473,32 +15478,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128819682</v>
+        <v>128819643</v>
       </c>
       <c r="B150" t="n">
-        <v>98636</v>
+        <v>80229</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15508,10 +15513,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>754120</v>
+        <v>753951</v>
       </c>
       <c r="R150" t="n">
-        <v>7294078</v>
+        <v>7293999</v>
       </c>
       <c r="S150" t="n">
         <v>3</v>
@@ -15544,11 +15549,6 @@
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>Riktig förekomst</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -15672,32 +15672,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128834422</v>
+        <v>128834472</v>
       </c>
       <c r="B152" t="n">
-        <v>80229</v>
+        <v>98636</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15707,10 +15707,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>754355</v>
+        <v>754273</v>
       </c>
       <c r="R152" t="n">
-        <v>7293811</v>
+        <v>7293868</v>
       </c>
       <c r="S152" t="n">
         <v>5</v>
@@ -15743,6 +15743,11 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>Ca 8 m diam</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -15769,7 +15774,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128834472</v>
+        <v>128834475</v>
       </c>
       <c r="B153" t="n">
         <v>98636</v>
@@ -15804,10 +15809,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>754273</v>
+        <v>754330</v>
       </c>
       <c r="R153" t="n">
-        <v>7293868</v>
+        <v>7293823</v>
       </c>
       <c r="S153" t="n">
         <v>5</v>
@@ -15844,7 +15849,7 @@
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>Ca 8 m diam</t>
+          <t>4mtr diam</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -15871,32 +15876,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128834475</v>
+        <v>128834422</v>
       </c>
       <c r="B154" t="n">
-        <v>98636</v>
+        <v>80229</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -15906,10 +15911,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>754330</v>
+        <v>754355</v>
       </c>
       <c r="R154" t="n">
-        <v>7293823</v>
+        <v>7293811</v>
       </c>
       <c r="S154" t="n">
         <v>5</v>
@@ -15942,11 +15947,6 @@
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>4mtr diam</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -15973,32 +15973,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128834391</v>
+        <v>128834413</v>
       </c>
       <c r="B155" t="n">
-        <v>97507</v>
+        <v>80229</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16008,10 +16008,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>754184</v>
+        <v>754091</v>
       </c>
       <c r="R155" t="n">
-        <v>7294045</v>
+        <v>7293941</v>
       </c>
       <c r="S155" t="n">
         <v>5</v>
@@ -16070,32 +16070,32 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128834470</v>
+        <v>128819646</v>
       </c>
       <c r="B156" t="n">
-        <v>98636</v>
+        <v>80229</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16105,13 +16105,13 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>754249</v>
+        <v>754143</v>
       </c>
       <c r="R156" t="n">
-        <v>7293901</v>
+        <v>7294037</v>
       </c>
       <c r="S156" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -16155,19 +16155,19 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128819692</v>
+        <v>128834470</v>
       </c>
       <c r="B157" t="n">
         <v>98636</v>
@@ -16202,13 +16202,13 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>754049</v>
+        <v>754249</v>
       </c>
       <c r="R157" t="n">
-        <v>7294082</v>
+        <v>7293901</v>
       </c>
       <c r="S157" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -16238,11 +16238,6 @@
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>Stor förekomst</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16257,19 +16252,19 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128819691</v>
+        <v>128819692</v>
       </c>
       <c r="B158" t="n">
         <v>98636</v>
@@ -16304,10 +16299,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>754222</v>
+        <v>754049</v>
       </c>
       <c r="R158" t="n">
-        <v>7293998</v>
+        <v>7294082</v>
       </c>
       <c r="S158" t="n">
         <v>3</v>
@@ -16344,7 +16339,7 @@
       </c>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>Större område</t>
+          <t>Stor förekomst</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -16371,7 +16366,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128834485</v>
+        <v>128819691</v>
       </c>
       <c r="B159" t="n">
         <v>98636</v>
@@ -16406,13 +16401,13 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>754182</v>
+        <v>754222</v>
       </c>
       <c r="R159" t="n">
-        <v>7294034</v>
+        <v>7293998</v>
       </c>
       <c r="S159" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -16446,7 +16441,7 @@
       </c>
       <c r="AC159" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Större område</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -16461,19 +16456,19 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128819688</v>
+        <v>128834485</v>
       </c>
       <c r="B160" t="n">
         <v>98636</v>
@@ -16508,13 +16503,13 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>754342</v>
+        <v>754182</v>
       </c>
       <c r="R160" t="n">
-        <v>7293868</v>
+        <v>7294034</v>
       </c>
       <c r="S160" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -16544,6 +16539,11 @@
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -16558,44 +16558,44 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128834413</v>
+        <v>128819688</v>
       </c>
       <c r="B161" t="n">
-        <v>80229</v>
+        <v>98636</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>754091</v>
+        <v>754342</v>
       </c>
       <c r="R161" t="n">
-        <v>7293941</v>
+        <v>7293868</v>
       </c>
       <c r="S161" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -16655,44 +16655,44 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128819646</v>
+        <v>128834391</v>
       </c>
       <c r="B162" t="n">
-        <v>80229</v>
+        <v>97507</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -16702,13 +16702,13 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>754143</v>
+        <v>754184</v>
       </c>
       <c r="R162" t="n">
-        <v>7294037</v>
+        <v>7294045</v>
       </c>
       <c r="S162" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -16752,44 +16752,44 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>128834425</v>
+        <v>128834383</v>
       </c>
       <c r="B163" t="n">
-        <v>80229</v>
+        <v>80258</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -16799,10 +16799,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>754321</v>
+        <v>754143</v>
       </c>
       <c r="R163" t="n">
-        <v>7293944</v>
+        <v>7294098</v>
       </c>
       <c r="S163" t="n">
         <v>5</v>
@@ -16861,32 +16861,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128834383</v>
+        <v>128834425</v>
       </c>
       <c r="B164" t="n">
-        <v>80258</v>
+        <v>80229</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -16896,10 +16896,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>754143</v>
+        <v>754321</v>
       </c>
       <c r="R164" t="n">
-        <v>7294098</v>
+        <v>7293944</v>
       </c>
       <c r="S164" t="n">
         <v>5</v>

--- a/artfynd/A 41034-2025 artfynd.xlsx
+++ b/artfynd/A 41034-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY164"/>
+  <dimension ref="A1:AY169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3688,7 +3688,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128834420</v>
+        <v>128834415</v>
       </c>
       <c r="B30" t="n">
         <v>80229</v>
@@ -3723,10 +3723,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>754338</v>
+        <v>754084</v>
       </c>
       <c r="R30" t="n">
-        <v>7293821</v>
+        <v>7293943</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3882,7 +3882,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128834415</v>
+        <v>128834420</v>
       </c>
       <c r="B32" t="n">
         <v>80229</v>
@@ -3917,10 +3917,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>754084</v>
+        <v>754338</v>
       </c>
       <c r="R32" t="n">
-        <v>7293943</v>
+        <v>7293821</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4382,32 +4382,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128834378</v>
+        <v>128834462</v>
       </c>
       <c r="B37" t="n">
-        <v>80258</v>
+        <v>98636</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4417,10 +4417,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>753636</v>
+        <v>754024</v>
       </c>
       <c r="R37" t="n">
-        <v>7294023</v>
+        <v>7293998</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4479,32 +4479,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128834405</v>
+        <v>128834434</v>
       </c>
       <c r="B38" t="n">
-        <v>80229</v>
+        <v>95486</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>2387</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>753772</v>
+        <v>753879</v>
       </c>
       <c r="R38" t="n">
-        <v>7293986</v>
+        <v>7293890</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4673,32 +4673,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128819663</v>
+        <v>128819696</v>
       </c>
       <c r="B40" t="n">
-        <v>80229</v>
+        <v>80264</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4708,10 +4708,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>754152</v>
+        <v>754302</v>
       </c>
       <c r="R40" t="n">
-        <v>7294076</v>
+        <v>7293804</v>
       </c>
       <c r="S40" t="n">
         <v>3</v>
@@ -4770,32 +4770,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128819696</v>
+        <v>128834405</v>
       </c>
       <c r="B41" t="n">
-        <v>80264</v>
+        <v>80229</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4805,13 +4805,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>754302</v>
+        <v>753772</v>
       </c>
       <c r="R41" t="n">
-        <v>7293804</v>
+        <v>7293986</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4855,22 +4855,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128834434</v>
+        <v>128834390</v>
       </c>
       <c r="B42" t="n">
-        <v>95486</v>
+        <v>80133</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4878,21 +4878,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2387</v>
+        <v>6456</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>753879</v>
+        <v>754064</v>
       </c>
       <c r="R42" t="n">
-        <v>7293890</v>
+        <v>7294121</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4964,32 +4964,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128834390</v>
+        <v>128819663</v>
       </c>
       <c r="B43" t="n">
-        <v>80133</v>
+        <v>80229</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4999,13 +4999,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>754064</v>
+        <v>754152</v>
       </c>
       <c r="R43" t="n">
-        <v>7294121</v>
+        <v>7294076</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5049,44 +5049,44 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128834462</v>
+        <v>128834378</v>
       </c>
       <c r="B44" t="n">
-        <v>98636</v>
+        <v>80258</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5096,10 +5096,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>754024</v>
+        <v>753636</v>
       </c>
       <c r="R44" t="n">
-        <v>7293998</v>
+        <v>7294023</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5352,32 +5352,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128834454</v>
+        <v>128834386</v>
       </c>
       <c r="B47" t="n">
-        <v>98636</v>
+        <v>57717</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5387,10 +5387,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>753898</v>
+        <v>753889</v>
       </c>
       <c r="R47" t="n">
-        <v>7293898</v>
+        <v>7294195</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5427,7 +5427,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>3mtr diam</t>
+          <t>Hack vid trädbas</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5454,7 +5454,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128819675</v>
+        <v>128834454</v>
       </c>
       <c r="B48" t="n">
         <v>98636</v>
@@ -5489,13 +5489,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>753812</v>
+        <v>753898</v>
       </c>
       <c r="R48" t="n">
-        <v>7293999</v>
+        <v>7293898</v>
       </c>
       <c r="S48" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>3mtr diam</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5544,44 +5544,44 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128834386</v>
+        <v>128819675</v>
       </c>
       <c r="B49" t="n">
-        <v>57717</v>
+        <v>98636</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5591,13 +5591,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>753889</v>
+        <v>753812</v>
       </c>
       <c r="R49" t="n">
-        <v>7294195</v>
+        <v>7293999</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Hack vid trädbas</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5646,12 +5646,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -6153,10 +6153,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128819639</v>
+        <v>128834376</v>
       </c>
       <c r="B55" t="n">
-        <v>91804</v>
+        <v>91508</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6164,21 +6164,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6188,13 +6188,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>754249</v>
+        <v>754253</v>
       </c>
       <c r="R55" t="n">
-        <v>7293891</v>
+        <v>7293898</v>
       </c>
       <c r="S55" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6224,11 +6224,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>10 fruktkroppar</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6243,22 +6238,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128834376</v>
+        <v>128819639</v>
       </c>
       <c r="B56" t="n">
-        <v>91508</v>
+        <v>91804</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6266,21 +6261,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6290,13 +6285,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>754253</v>
+        <v>754249</v>
       </c>
       <c r="R56" t="n">
-        <v>7293898</v>
+        <v>7293891</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6326,6 +6321,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>10 fruktkroppar</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6340,44 +6340,44 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128819648</v>
+        <v>128834433</v>
       </c>
       <c r="B57" t="n">
-        <v>80229</v>
+        <v>95486</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>2387</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6387,13 +6387,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>754142</v>
+        <v>753867</v>
       </c>
       <c r="R57" t="n">
-        <v>7293999</v>
+        <v>7293877</v>
       </c>
       <c r="S57" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6437,19 +6437,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128834404</v>
+        <v>128819648</v>
       </c>
       <c r="B58" t="n">
         <v>80229</v>
@@ -6484,13 +6484,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>753693</v>
+        <v>754142</v>
       </c>
       <c r="R58" t="n">
-        <v>7293978</v>
+        <v>7293999</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6534,22 +6534,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128834491</v>
+        <v>128834404</v>
       </c>
       <c r="B59" t="n">
-        <v>56901</v>
+        <v>80229</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6557,21 +6557,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6581,10 +6581,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>753881</v>
+        <v>753693</v>
       </c>
       <c r="R59" t="n">
-        <v>7293891</v>
+        <v>7293978</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6643,32 +6643,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128834446</v>
+        <v>128834491</v>
       </c>
       <c r="B60" t="n">
-        <v>98636</v>
+        <v>56901</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>753638</v>
+        <v>753881</v>
       </c>
       <c r="R60" t="n">
-        <v>7293994</v>
+        <v>7293891</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6714,11 +6714,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Mycket rikligt bestånd</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6745,7 +6740,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128834449</v>
+        <v>128834446</v>
       </c>
       <c r="B61" t="n">
         <v>98636</v>
@@ -6780,10 +6775,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>753732</v>
+        <v>753638</v>
       </c>
       <c r="R61" t="n">
-        <v>7293989</v>
+        <v>7293994</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6847,7 +6842,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128819680</v>
+        <v>128834449</v>
       </c>
       <c r="B62" t="n">
         <v>98636</v>
@@ -6882,13 +6877,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>754079</v>
+        <v>753732</v>
       </c>
       <c r="R62" t="n">
-        <v>7294043</v>
+        <v>7293989</v>
       </c>
       <c r="S62" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6922,7 +6917,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Rik förekomst</t>
+          <t>Mycket rikligt bestånd</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6937,44 +6932,44 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128834433</v>
+        <v>128819680</v>
       </c>
       <c r="B63" t="n">
-        <v>95486</v>
+        <v>98636</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2387</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6984,13 +6979,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>753867</v>
+        <v>754079</v>
       </c>
       <c r="R63" t="n">
-        <v>7293877</v>
+        <v>7294043</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7020,6 +7015,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Rik förekomst</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7034,44 +7034,44 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128834457</v>
+        <v>128834407</v>
       </c>
       <c r="B64" t="n">
-        <v>98636</v>
+        <v>80229</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7081,10 +7081,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>753947</v>
+        <v>753989</v>
       </c>
       <c r="R64" t="n">
-        <v>7293964</v>
+        <v>7294010</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7117,11 +7117,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>5mtr diam</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7148,32 +7143,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128834463</v>
+        <v>128834416</v>
       </c>
       <c r="B65" t="n">
-        <v>98636</v>
+        <v>80229</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7183,10 +7178,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>754071</v>
+        <v>754148</v>
       </c>
       <c r="R65" t="n">
-        <v>7293964</v>
+        <v>7293935</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7245,32 +7240,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128834458</v>
+        <v>128834380</v>
       </c>
       <c r="B66" t="n">
-        <v>98636</v>
+        <v>80258</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7280,10 +7275,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>753959</v>
+        <v>754091</v>
       </c>
       <c r="R66" t="n">
-        <v>7294022</v>
+        <v>7293941</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7316,11 +7311,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>3m diam</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7347,7 +7337,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128819677</v>
+        <v>128834457</v>
       </c>
       <c r="B67" t="n">
         <v>98636</v>
@@ -7382,13 +7372,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>753875</v>
+        <v>753947</v>
       </c>
       <c r="R67" t="n">
-        <v>7294001</v>
+        <v>7293964</v>
       </c>
       <c r="S67" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7418,6 +7408,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>5mtr diam</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7432,19 +7427,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128834461</v>
+        <v>128834463</v>
       </c>
       <c r="B68" t="n">
         <v>98636</v>
@@ -7479,10 +7474,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>753981</v>
+        <v>754071</v>
       </c>
       <c r="R68" t="n">
-        <v>7294022</v>
+        <v>7293964</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7541,32 +7536,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128834416</v>
+        <v>128834458</v>
       </c>
       <c r="B69" t="n">
-        <v>80229</v>
+        <v>98636</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7576,10 +7571,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>754148</v>
+        <v>753959</v>
       </c>
       <c r="R69" t="n">
-        <v>7293935</v>
+        <v>7294022</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7612,6 +7607,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>3m diam</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7638,32 +7638,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128834407</v>
+        <v>128819677</v>
       </c>
       <c r="B70" t="n">
-        <v>80229</v>
+        <v>98636</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7673,13 +7673,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>753989</v>
+        <v>753875</v>
       </c>
       <c r="R70" t="n">
-        <v>7294010</v>
+        <v>7294001</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7723,44 +7723,44 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128834380</v>
+        <v>128834461</v>
       </c>
       <c r="B71" t="n">
-        <v>80258</v>
+        <v>98636</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7770,10 +7770,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>754091</v>
+        <v>753981</v>
       </c>
       <c r="R71" t="n">
-        <v>7293941</v>
+        <v>7294022</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7832,7 +7832,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128819676</v>
+        <v>128834456</v>
       </c>
       <c r="B72" t="n">
         <v>98636</v>
@@ -7867,13 +7867,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>753836</v>
+        <v>753917</v>
       </c>
       <c r="R72" t="n">
-        <v>7293977</v>
+        <v>7293936</v>
       </c>
       <c r="S72" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7903,11 +7903,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7922,44 +7917,44 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128834476</v>
+        <v>128834409</v>
       </c>
       <c r="B73" t="n">
-        <v>98636</v>
+        <v>80229</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7969,10 +7964,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>754345</v>
+        <v>754042</v>
       </c>
       <c r="R73" t="n">
-        <v>7293808</v>
+        <v>7293966</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8005,11 +8000,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>3m diam</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8036,32 +8026,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128834443</v>
+        <v>128834401</v>
       </c>
       <c r="B74" t="n">
-        <v>98636</v>
+        <v>80229</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8071,10 +8061,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>754042</v>
+        <v>753629</v>
       </c>
       <c r="R74" t="n">
-        <v>7294129</v>
+        <v>7294009</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8107,11 +8097,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Måttlig förekomst 6m diam</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8138,32 +8123,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128834456</v>
+        <v>128819652</v>
       </c>
       <c r="B75" t="n">
-        <v>98636</v>
+        <v>80229</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8173,13 +8158,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>753917</v>
+        <v>754297</v>
       </c>
       <c r="R75" t="n">
-        <v>7293936</v>
+        <v>7293780</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8223,44 +8208,44 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128834401</v>
+        <v>128834431</v>
       </c>
       <c r="B76" t="n">
-        <v>80229</v>
+        <v>80265</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8270,10 +8255,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>753629</v>
+        <v>754087</v>
       </c>
       <c r="R76" t="n">
-        <v>7294009</v>
+        <v>7293941</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8332,32 +8317,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128834409</v>
+        <v>128819676</v>
       </c>
       <c r="B77" t="n">
-        <v>80229</v>
+        <v>98636</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8367,13 +8352,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>754042</v>
+        <v>753836</v>
       </c>
       <c r="R77" t="n">
-        <v>7293966</v>
+        <v>7293977</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8403,6 +8388,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8417,44 +8407,44 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128834431</v>
+        <v>128834476</v>
       </c>
       <c r="B78" t="n">
-        <v>80265</v>
+        <v>98636</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8464,10 +8454,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>754087</v>
+        <v>754345</v>
       </c>
       <c r="R78" t="n">
-        <v>7293941</v>
+        <v>7293808</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8500,6 +8490,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>3m diam</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8526,32 +8521,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128819652</v>
+        <v>128834443</v>
       </c>
       <c r="B79" t="n">
-        <v>80229</v>
+        <v>98636</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8561,13 +8556,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>754297</v>
+        <v>754042</v>
       </c>
       <c r="R79" t="n">
-        <v>7293780</v>
+        <v>7294129</v>
       </c>
       <c r="S79" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8597,6 +8592,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Måttlig förekomst 6m diam</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8611,12 +8611,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -8817,32 +8817,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128834381</v>
+        <v>128819664</v>
       </c>
       <c r="B82" t="n">
-        <v>80258</v>
+        <v>80229</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8852,13 +8852,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>754177</v>
+        <v>754142</v>
       </c>
       <c r="R82" t="n">
-        <v>7293925</v>
+        <v>7294080</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8902,44 +8902,44 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128819664</v>
+        <v>128834381</v>
       </c>
       <c r="B83" t="n">
-        <v>80229</v>
+        <v>80258</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8949,13 +8949,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>754142</v>
+        <v>754177</v>
       </c>
       <c r="R83" t="n">
-        <v>7294080</v>
+        <v>7293925</v>
       </c>
       <c r="S83" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8999,12 +8999,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -9501,32 +9501,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128834432</v>
+        <v>128834427</v>
       </c>
       <c r="B89" t="n">
-        <v>80133</v>
+        <v>80229</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9536,10 +9536,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>754056</v>
+        <v>754149</v>
       </c>
       <c r="R89" t="n">
-        <v>7293965</v>
+        <v>7294074</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -9598,32 +9598,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128834427</v>
+        <v>128834432</v>
       </c>
       <c r="B90" t="n">
-        <v>80229</v>
+        <v>80133</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9633,10 +9633,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>754149</v>
+        <v>754056</v>
       </c>
       <c r="R90" t="n">
-        <v>7294074</v>
+        <v>7293965</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -9695,7 +9695,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128819681</v>
+        <v>128834459</v>
       </c>
       <c r="B91" t="n">
         <v>98636</v>
@@ -9730,13 +9730,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>754100</v>
+        <v>753972</v>
       </c>
       <c r="R91" t="n">
-        <v>7294064</v>
+        <v>7294032</v>
       </c>
       <c r="S91" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9766,11 +9766,6 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Mycket Riklig förekomst</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9785,19 +9780,19 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128834459</v>
+        <v>128819681</v>
       </c>
       <c r="B92" t="n">
         <v>98636</v>
@@ -9832,13 +9827,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>753972</v>
+        <v>754100</v>
       </c>
       <c r="R92" t="n">
-        <v>7294032</v>
+        <v>7294064</v>
       </c>
       <c r="S92" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -9868,6 +9863,11 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Mycket Riklig förekomst</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9882,12 +9882,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -9991,32 +9991,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128834435</v>
+        <v>128834482</v>
       </c>
       <c r="B94" t="n">
-        <v>95486</v>
+        <v>98636</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2387</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10026,10 +10026,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>753941</v>
+        <v>754298</v>
       </c>
       <c r="R94" t="n">
-        <v>7294196</v>
+        <v>7293981</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10088,32 +10088,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128819649</v>
+        <v>128819686</v>
       </c>
       <c r="B95" t="n">
-        <v>80229</v>
+        <v>98636</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10123,10 +10123,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>754149</v>
+        <v>754145</v>
       </c>
       <c r="R95" t="n">
-        <v>7293983</v>
+        <v>7293994</v>
       </c>
       <c r="S95" t="n">
         <v>3</v>
@@ -10185,32 +10185,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128819654</v>
+        <v>128834455</v>
       </c>
       <c r="B96" t="n">
-        <v>80229</v>
+        <v>98636</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10220,13 +10220,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>754303</v>
+        <v>753903</v>
       </c>
       <c r="R96" t="n">
-        <v>7293804</v>
+        <v>7293910</v>
       </c>
       <c r="S96" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10256,6 +10256,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>4mtr diam</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10270,44 +10275,44 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128834482</v>
+        <v>128819654</v>
       </c>
       <c r="B97" t="n">
-        <v>98636</v>
+        <v>80229</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10317,13 +10322,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>754298</v>
+        <v>754303</v>
       </c>
       <c r="R97" t="n">
-        <v>7293981</v>
+        <v>7293804</v>
       </c>
       <c r="S97" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10367,44 +10372,44 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128819686</v>
+        <v>128819649</v>
       </c>
       <c r="B98" t="n">
-        <v>98636</v>
+        <v>80229</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10414,10 +10419,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>754145</v>
+        <v>754149</v>
       </c>
       <c r="R98" t="n">
-        <v>7293994</v>
+        <v>7293983</v>
       </c>
       <c r="S98" t="n">
         <v>3</v>
@@ -10476,32 +10481,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128834455</v>
+        <v>128834435</v>
       </c>
       <c r="B99" t="n">
-        <v>98636</v>
+        <v>95486</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>2387</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10511,10 +10516,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>753903</v>
+        <v>753941</v>
       </c>
       <c r="R99" t="n">
-        <v>7293910</v>
+        <v>7294196</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -10547,11 +10552,6 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>4mtr diam</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10578,32 +10578,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128819644</v>
+        <v>128819679</v>
       </c>
       <c r="B100" t="n">
-        <v>80229</v>
+        <v>98636</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10613,10 +10613,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>754003</v>
+        <v>754015</v>
       </c>
       <c r="R100" t="n">
-        <v>7294039</v>
+        <v>7294040</v>
       </c>
       <c r="S100" t="n">
         <v>3</v>
@@ -10649,6 +10649,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10675,32 +10680,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128834428</v>
+        <v>128834451</v>
       </c>
       <c r="B101" t="n">
-        <v>80229</v>
+        <v>98636</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10710,10 +10715,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>754137</v>
+        <v>753769</v>
       </c>
       <c r="R101" t="n">
-        <v>7294102</v>
+        <v>7293962</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -10772,7 +10777,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128834399</v>
+        <v>128819644</v>
       </c>
       <c r="B102" t="n">
         <v>80229</v>
@@ -10807,13 +10812,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>753717</v>
+        <v>754003</v>
       </c>
       <c r="R102" t="n">
-        <v>7294108</v>
+        <v>7294039</v>
       </c>
       <c r="S102" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -10857,44 +10862,44 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128819679</v>
+        <v>128834399</v>
       </c>
       <c r="B103" t="n">
-        <v>98636</v>
+        <v>80229</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10904,13 +10909,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>754015</v>
+        <v>753717</v>
       </c>
       <c r="R103" t="n">
-        <v>7294040</v>
+        <v>7294108</v>
       </c>
       <c r="S103" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -10940,11 +10945,6 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10959,44 +10959,44 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128834451</v>
+        <v>128834428</v>
       </c>
       <c r="B104" t="n">
-        <v>98636</v>
+        <v>80229</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11006,10 +11006,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>753769</v>
+        <v>754137</v>
       </c>
       <c r="R104" t="n">
-        <v>7293962</v>
+        <v>7294102</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -11165,32 +11165,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128834436</v>
+        <v>128834450</v>
       </c>
       <c r="B106" t="n">
-        <v>95486</v>
+        <v>98636</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>2387</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11200,10 +11200,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>753913</v>
+        <v>753753</v>
       </c>
       <c r="R106" t="n">
-        <v>7294181</v>
+        <v>7293995</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -11262,7 +11262,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128834450</v>
+        <v>128819670</v>
       </c>
       <c r="B107" t="n">
         <v>98636</v>
@@ -11297,13 +11297,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>753753</v>
+        <v>753799</v>
       </c>
       <c r="R107" t="n">
-        <v>7293995</v>
+        <v>7294127</v>
       </c>
       <c r="S107" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11333,6 +11333,11 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Mycket riktig förekomst</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11347,19 +11352,19 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128819670</v>
+        <v>128834465</v>
       </c>
       <c r="B108" t="n">
         <v>98636</v>
@@ -11394,13 +11399,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>753799</v>
+        <v>754148</v>
       </c>
       <c r="R108" t="n">
-        <v>7294127</v>
+        <v>7293932</v>
       </c>
       <c r="S108" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11430,11 +11435,6 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Mycket riktig förekomst</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11449,19 +11449,19 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128819684</v>
+        <v>128834445</v>
       </c>
       <c r="B109" t="n">
         <v>98636</v>
@@ -11496,13 +11496,13 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>754145</v>
+        <v>753685</v>
       </c>
       <c r="R109" t="n">
-        <v>7294023</v>
+        <v>7294059</v>
       </c>
       <c r="S109" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -11532,6 +11532,11 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>3mtr diam</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11546,19 +11551,19 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128834465</v>
+        <v>128834468</v>
       </c>
       <c r="B110" t="n">
         <v>98636</v>
@@ -11593,10 +11598,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>754148</v>
+        <v>754196</v>
       </c>
       <c r="R110" t="n">
-        <v>7293932</v>
+        <v>7293923</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -11655,7 +11660,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128834445</v>
+        <v>128819684</v>
       </c>
       <c r="B111" t="n">
         <v>98636</v>
@@ -11690,13 +11695,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>753685</v>
+        <v>754145</v>
       </c>
       <c r="R111" t="n">
-        <v>7294059</v>
+        <v>7294023</v>
       </c>
       <c r="S111" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -11726,11 +11731,6 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>3mtr diam</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11745,44 +11745,44 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128834468</v>
+        <v>128834436</v>
       </c>
       <c r="B112" t="n">
-        <v>98636</v>
+        <v>95486</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>220787</v>
+        <v>2387</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11792,10 +11792,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>754196</v>
+        <v>753913</v>
       </c>
       <c r="R112" t="n">
-        <v>7293923</v>
+        <v>7294181</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -11951,7 +11951,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128819668</v>
+        <v>128834419</v>
       </c>
       <c r="B114" t="n">
         <v>80229</v>
@@ -11986,13 +11986,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>753980</v>
+        <v>754329</v>
       </c>
       <c r="R114" t="n">
-        <v>7294135</v>
+        <v>7293829</v>
       </c>
       <c r="S114" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12036,19 +12036,19 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128819647</v>
+        <v>128819668</v>
       </c>
       <c r="B115" t="n">
         <v>80229</v>
@@ -12083,10 +12083,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>754139</v>
+        <v>753980</v>
       </c>
       <c r="R115" t="n">
-        <v>7294012</v>
+        <v>7294135</v>
       </c>
       <c r="S115" t="n">
         <v>3</v>
@@ -12145,7 +12145,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128834419</v>
+        <v>128819647</v>
       </c>
       <c r="B116" t="n">
         <v>80229</v>
@@ -12180,13 +12180,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>754329</v>
+        <v>754139</v>
       </c>
       <c r="R116" t="n">
-        <v>7293829</v>
+        <v>7294012</v>
       </c>
       <c r="S116" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12230,12 +12230,12 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
@@ -12344,10 +12344,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128834499</v>
+        <v>128834477</v>
       </c>
       <c r="B118" t="n">
-        <v>91880</v>
+        <v>98636</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12355,37 +12355,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1505</v>
+        <v>220787</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Stormansberget, Nb</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>754035</v>
+        <v>754356</v>
       </c>
       <c r="R118" t="n">
-        <v>7294132</v>
+        <v>7293813</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -12420,13 +12417,17 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Ca 2m diam</t>
+        </is>
+      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -12445,32 +12446,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128834429</v>
+        <v>128834469</v>
       </c>
       <c r="B119" t="n">
-        <v>80229</v>
+        <v>98636</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12480,10 +12481,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>754063</v>
+        <v>754222</v>
       </c>
       <c r="R119" t="n">
-        <v>7294120</v>
+        <v>7293912</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -12516,6 +12517,11 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>10m diam mycket riklig förekomst</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12542,45 +12548,48 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128834400</v>
+        <v>128834499</v>
       </c>
       <c r="B120" t="n">
-        <v>80229</v>
+        <v>91880</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6458</v>
+        <v>1505</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Stormansberget, Nb</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>753636</v>
+        <v>754035</v>
       </c>
       <c r="R120" t="n">
-        <v>7294018</v>
+        <v>7294132</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -12621,6 +12630,7 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
+      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -12639,32 +12649,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128834469</v>
+        <v>128834400</v>
       </c>
       <c r="B121" t="n">
-        <v>98636</v>
+        <v>80229</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12674,10 +12684,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>754222</v>
+        <v>753636</v>
       </c>
       <c r="R121" t="n">
-        <v>7293912</v>
+        <v>7294018</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -12710,11 +12720,6 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>10m diam mycket riklig förekomst</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12741,32 +12746,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128834477</v>
+        <v>128834429</v>
       </c>
       <c r="B122" t="n">
-        <v>98636</v>
+        <v>80229</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12776,10 +12781,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>754356</v>
+        <v>754063</v>
       </c>
       <c r="R122" t="n">
-        <v>7293813</v>
+        <v>7294120</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -12812,11 +12817,6 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Ca 2m diam</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12940,32 +12940,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128819671</v>
+        <v>128834373</v>
       </c>
       <c r="B124" t="n">
-        <v>98636</v>
+        <v>91683</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>220787</v>
+        <v>1588</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12975,13 +12975,13 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>753685</v>
+        <v>754056</v>
       </c>
       <c r="R124" t="n">
-        <v>7294093</v>
+        <v>7294109</v>
       </c>
       <c r="S124" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13025,44 +13025,44 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128834453</v>
+        <v>128819650</v>
       </c>
       <c r="B125" t="n">
-        <v>98636</v>
+        <v>80229</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13072,13 +13072,13 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>753894</v>
+        <v>754166</v>
       </c>
       <c r="R125" t="n">
-        <v>7293894</v>
+        <v>7293978</v>
       </c>
       <c r="S125" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -13108,11 +13108,6 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>5mtr mycket rikligt bestånd</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13127,44 +13122,44 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128834452</v>
+        <v>128834418</v>
       </c>
       <c r="B126" t="n">
-        <v>98636</v>
+        <v>80229</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13174,10 +13169,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>753833</v>
+        <v>754325</v>
       </c>
       <c r="R126" t="n">
-        <v>7293877</v>
+        <v>7293826</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -13236,32 +13231,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128834474</v>
+        <v>128819653</v>
       </c>
       <c r="B127" t="n">
-        <v>98636</v>
+        <v>80229</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13271,13 +13266,13 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>754313</v>
+        <v>754304</v>
       </c>
       <c r="R127" t="n">
-        <v>7293834</v>
+        <v>7293805</v>
       </c>
       <c r="S127" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -13321,44 +13316,44 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128819683</v>
+        <v>128819694</v>
       </c>
       <c r="B128" t="n">
-        <v>98636</v>
+        <v>56901</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13368,10 +13363,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>754142</v>
+        <v>754139</v>
       </c>
       <c r="R128" t="n">
-        <v>7294040</v>
+        <v>7294034</v>
       </c>
       <c r="S128" t="n">
         <v>3</v>
@@ -13430,32 +13425,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128819697</v>
+        <v>128834375</v>
       </c>
       <c r="B129" t="n">
-        <v>96755</v>
+        <v>79156</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>2869</v>
+        <v>185</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13465,13 +13460,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>754263</v>
+        <v>754092</v>
       </c>
       <c r="R129" t="n">
-        <v>7293846</v>
+        <v>7293962</v>
       </c>
       <c r="S129" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -13515,44 +13510,44 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128834373</v>
+        <v>128819697</v>
       </c>
       <c r="B130" t="n">
-        <v>91683</v>
+        <v>96755</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1588</v>
+        <v>2869</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13562,13 +13557,13 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>754056</v>
+        <v>754263</v>
       </c>
       <c r="R130" t="n">
-        <v>7294109</v>
+        <v>7293846</v>
       </c>
       <c r="S130" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -13612,44 +13607,44 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128834375</v>
+        <v>128819671</v>
       </c>
       <c r="B131" t="n">
-        <v>79156</v>
+        <v>98636</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13659,13 +13654,13 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>754092</v>
+        <v>753685</v>
       </c>
       <c r="R131" t="n">
-        <v>7293962</v>
+        <v>7294093</v>
       </c>
       <c r="S131" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -13709,44 +13704,44 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128819653</v>
+        <v>128834453</v>
       </c>
       <c r="B132" t="n">
-        <v>80229</v>
+        <v>98636</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13756,13 +13751,13 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>754304</v>
+        <v>753894</v>
       </c>
       <c r="R132" t="n">
-        <v>7293805</v>
+        <v>7293894</v>
       </c>
       <c r="S132" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -13792,6 +13787,11 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>5mtr mycket rikligt bestånd</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -13806,44 +13806,44 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128819650</v>
+        <v>128834452</v>
       </c>
       <c r="B133" t="n">
-        <v>80229</v>
+        <v>98636</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13853,13 +13853,13 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>754166</v>
+        <v>753833</v>
       </c>
       <c r="R133" t="n">
-        <v>7293978</v>
+        <v>7293877</v>
       </c>
       <c r="S133" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -13903,44 +13903,44 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128834418</v>
+        <v>128834474</v>
       </c>
       <c r="B134" t="n">
-        <v>80229</v>
+        <v>98636</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13950,10 +13950,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>754325</v>
+        <v>754313</v>
       </c>
       <c r="R134" t="n">
-        <v>7293826</v>
+        <v>7293834</v>
       </c>
       <c r="S134" t="n">
         <v>5</v>
@@ -14012,32 +14012,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128819694</v>
+        <v>128819683</v>
       </c>
       <c r="B135" t="n">
-        <v>56901</v>
+        <v>98636</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14047,10 +14047,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>754139</v>
+        <v>754142</v>
       </c>
       <c r="R135" t="n">
-        <v>7294034</v>
+        <v>7294040</v>
       </c>
       <c r="S135" t="n">
         <v>3</v>
@@ -14109,10 +14109,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128834372</v>
+        <v>128819651</v>
       </c>
       <c r="B136" t="n">
-        <v>88772</v>
+        <v>80229</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14120,21 +14120,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>4412</v>
+        <v>6458</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14144,13 +14144,13 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>754265</v>
+        <v>754220</v>
       </c>
       <c r="R136" t="n">
-        <v>7293869</v>
+        <v>7293908</v>
       </c>
       <c r="S136" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -14194,12 +14194,12 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
@@ -14303,7 +14303,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128819640</v>
+        <v>128819645</v>
       </c>
       <c r="B138" t="n">
         <v>80229</v>
@@ -14338,10 +14338,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>754021</v>
+        <v>754081</v>
       </c>
       <c r="R138" t="n">
-        <v>7294099</v>
+        <v>7294036</v>
       </c>
       <c r="S138" t="n">
         <v>3</v>
@@ -14382,7 +14382,6 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
-      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -14401,7 +14400,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128834402</v>
+        <v>128819640</v>
       </c>
       <c r="B139" t="n">
         <v>80229</v>
@@ -14436,13 +14435,13 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>753663</v>
+        <v>754021</v>
       </c>
       <c r="R139" t="n">
-        <v>7293971</v>
+        <v>7294099</v>
       </c>
       <c r="S139" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -14480,25 +14479,26 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128819645</v>
+        <v>128834402</v>
       </c>
       <c r="B140" t="n">
         <v>80229</v>
@@ -14533,13 +14533,13 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>754081</v>
+        <v>753663</v>
       </c>
       <c r="R140" t="n">
-        <v>7294036</v>
+        <v>7293971</v>
       </c>
       <c r="S140" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -14583,12 +14583,12 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
@@ -14692,10 +14692,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128819651</v>
+        <v>128834372</v>
       </c>
       <c r="B142" t="n">
-        <v>80229</v>
+        <v>88772</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14703,21 +14703,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6458</v>
+        <v>4412</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14727,13 +14727,13 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>754220</v>
+        <v>754265</v>
       </c>
       <c r="R142" t="n">
-        <v>7293908</v>
+        <v>7293869</v>
       </c>
       <c r="S142" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -14777,44 +14777,44 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128819636</v>
+        <v>128834489</v>
       </c>
       <c r="B143" t="n">
-        <v>57880</v>
+        <v>98636</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14824,13 +14824,13 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>754361</v>
+        <v>754044</v>
       </c>
       <c r="R143" t="n">
-        <v>7293841</v>
+        <v>7294116</v>
       </c>
       <c r="S143" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -14860,11 +14860,6 @@
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>6 individer</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -14879,44 +14874,44 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128834489</v>
+        <v>128834379</v>
       </c>
       <c r="B144" t="n">
-        <v>98636</v>
+        <v>80258</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -14926,10 +14921,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>754044</v>
+        <v>753674</v>
       </c>
       <c r="R144" t="n">
-        <v>7294116</v>
+        <v>7293973</v>
       </c>
       <c r="S144" t="n">
         <v>5</v>
@@ -14988,32 +14983,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128834487</v>
+        <v>128834412</v>
       </c>
       <c r="B145" t="n">
-        <v>98636</v>
+        <v>80229</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15023,10 +15018,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>754147</v>
+        <v>754096</v>
       </c>
       <c r="R145" t="n">
-        <v>7294086</v>
+        <v>7293963</v>
       </c>
       <c r="S145" t="n">
         <v>5</v>
@@ -15085,32 +15080,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128819682</v>
+        <v>128819667</v>
       </c>
       <c r="B146" t="n">
-        <v>98636</v>
+        <v>80229</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15120,10 +15115,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>754120</v>
+        <v>754002</v>
       </c>
       <c r="R146" t="n">
-        <v>7294078</v>
+        <v>7294106</v>
       </c>
       <c r="S146" t="n">
         <v>3</v>
@@ -15156,11 +15151,6 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>Riktig förekomst</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15187,7 +15177,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128834412</v>
+        <v>128819643</v>
       </c>
       <c r="B147" t="n">
         <v>80229</v>
@@ -15222,13 +15212,13 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>754096</v>
+        <v>753951</v>
       </c>
       <c r="R147" t="n">
-        <v>7293963</v>
+        <v>7293999</v>
       </c>
       <c r="S147" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -15272,22 +15262,22 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128819667</v>
+        <v>128819636</v>
       </c>
       <c r="B148" t="n">
-        <v>80229</v>
+        <v>57880</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15295,21 +15285,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15319,10 +15309,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>754002</v>
+        <v>754361</v>
       </c>
       <c r="R148" t="n">
-        <v>7294106</v>
+        <v>7293841</v>
       </c>
       <c r="S148" t="n">
         <v>3</v>
@@ -15355,6 +15345,11 @@
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>6 individer</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15381,32 +15376,32 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128834379</v>
+        <v>128834487</v>
       </c>
       <c r="B149" t="n">
-        <v>80258</v>
+        <v>98636</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15416,10 +15411,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>753674</v>
+        <v>754147</v>
       </c>
       <c r="R149" t="n">
-        <v>7293973</v>
+        <v>7294086</v>
       </c>
       <c r="S149" t="n">
         <v>5</v>
@@ -15478,32 +15473,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128819643</v>
+        <v>128819682</v>
       </c>
       <c r="B150" t="n">
-        <v>80229</v>
+        <v>98636</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15513,10 +15508,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>753951</v>
+        <v>754120</v>
       </c>
       <c r="R150" t="n">
-        <v>7293999</v>
+        <v>7294078</v>
       </c>
       <c r="S150" t="n">
         <v>3</v>
@@ -15549,6 +15544,11 @@
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>Riktig förekomst</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -15575,32 +15575,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128834389</v>
+        <v>128834422</v>
       </c>
       <c r="B151" t="n">
-        <v>80133</v>
+        <v>80229</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15610,10 +15610,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>754026</v>
+        <v>754355</v>
       </c>
       <c r="R151" t="n">
-        <v>7293997</v>
+        <v>7293811</v>
       </c>
       <c r="S151" t="n">
         <v>5</v>
@@ -15672,32 +15672,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128834472</v>
+        <v>128834389</v>
       </c>
       <c r="B152" t="n">
-        <v>98636</v>
+        <v>80133</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15707,10 +15707,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>754273</v>
+        <v>754026</v>
       </c>
       <c r="R152" t="n">
-        <v>7293868</v>
+        <v>7293997</v>
       </c>
       <c r="S152" t="n">
         <v>5</v>
@@ -15743,11 +15743,6 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>Ca 8 m diam</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -15774,7 +15769,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128834475</v>
+        <v>128834472</v>
       </c>
       <c r="B153" t="n">
         <v>98636</v>
@@ -15809,10 +15804,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>754330</v>
+        <v>754273</v>
       </c>
       <c r="R153" t="n">
-        <v>7293823</v>
+        <v>7293868</v>
       </c>
       <c r="S153" t="n">
         <v>5</v>
@@ -15849,7 +15844,7 @@
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>4mtr diam</t>
+          <t>Ca 8 m diam</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -15876,32 +15871,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128834422</v>
+        <v>128834475</v>
       </c>
       <c r="B154" t="n">
-        <v>80229</v>
+        <v>98636</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -15911,10 +15906,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>754355</v>
+        <v>754330</v>
       </c>
       <c r="R154" t="n">
-        <v>7293811</v>
+        <v>7293823</v>
       </c>
       <c r="S154" t="n">
         <v>5</v>
@@ -15947,6 +15942,11 @@
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>4mtr diam</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16264,7 +16264,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128819692</v>
+        <v>128834485</v>
       </c>
       <c r="B158" t="n">
         <v>98636</v>
@@ -16299,13 +16299,13 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>754049</v>
+        <v>754182</v>
       </c>
       <c r="R158" t="n">
-        <v>7294082</v>
+        <v>7294034</v>
       </c>
       <c r="S158" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -16339,7 +16339,7 @@
       </c>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>Stor förekomst</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -16354,19 +16354,19 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128819691</v>
+        <v>128819692</v>
       </c>
       <c r="B159" t="n">
         <v>98636</v>
@@ -16401,10 +16401,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>754222</v>
+        <v>754049</v>
       </c>
       <c r="R159" t="n">
-        <v>7293998</v>
+        <v>7294082</v>
       </c>
       <c r="S159" t="n">
         <v>3</v>
@@ -16441,7 +16441,7 @@
       </c>
       <c r="AC159" t="inlineStr">
         <is>
-          <t>Större område</t>
+          <t>Stor förekomst</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -16468,7 +16468,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128834485</v>
+        <v>128819691</v>
       </c>
       <c r="B160" t="n">
         <v>98636</v>
@@ -16503,13 +16503,13 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>754182</v>
+        <v>754222</v>
       </c>
       <c r="R160" t="n">
-        <v>7294034</v>
+        <v>7293998</v>
       </c>
       <c r="S160" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -16543,7 +16543,7 @@
       </c>
       <c r="AC160" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Större område</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -16558,12 +16558,12 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
@@ -16956,6 +16956,536 @@
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>129001197</v>
+      </c>
+      <c r="B165" t="n">
+        <v>98636</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>Vistträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q165" t="n">
+        <v>754250</v>
+      </c>
+      <c r="R165" t="n">
+        <v>7293995</v>
+      </c>
+      <c r="S165" t="n">
+        <v>10</v>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT165" t="inlineStr"/>
+      <c r="AW165" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX165" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>129001199</v>
+      </c>
+      <c r="B166" t="n">
+        <v>98636</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>Vistträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q166" t="n">
+        <v>754160</v>
+      </c>
+      <c r="R166" t="n">
+        <v>7294135</v>
+      </c>
+      <c r="S166" t="n">
+        <v>20</v>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W166" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT166" t="inlineStr"/>
+      <c r="AW166" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX166" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>129001194</v>
+      </c>
+      <c r="B167" t="n">
+        <v>98636</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>Vistträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q167" t="n">
+        <v>754411</v>
+      </c>
+      <c r="R167" t="n">
+        <v>7294018</v>
+      </c>
+      <c r="S167" t="n">
+        <v>10</v>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT167" t="inlineStr"/>
+      <c r="AW167" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX167" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>129001082</v>
+      </c>
+      <c r="B168" t="n">
+        <v>91508</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>Vistträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q168" t="n">
+        <v>754163</v>
+      </c>
+      <c r="R168" t="n">
+        <v>7294133</v>
+      </c>
+      <c r="S168" t="n">
+        <v>10</v>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W168" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y168" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AC168" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT168" t="inlineStr"/>
+      <c r="AW168" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX168" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>129001198</v>
+      </c>
+      <c r="B169" t="n">
+        <v>98636</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>Vistträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q169" t="n">
+        <v>754203</v>
+      </c>
+      <c r="R169" t="n">
+        <v>7294060</v>
+      </c>
+      <c r="S169" t="n">
+        <v>10</v>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT169" t="inlineStr"/>
+      <c r="AW169" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX169" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY169" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41034-2025 artfynd.xlsx
+++ b/artfynd/A 41034-2025 artfynd.xlsx
@@ -3688,32 +3688,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128834415</v>
+        <v>128834473</v>
       </c>
       <c r="B30" t="n">
-        <v>80229</v>
+        <v>98643</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3723,10 +3723,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>754084</v>
+        <v>754284</v>
       </c>
       <c r="R30" t="n">
-        <v>7293943</v>
+        <v>7293849</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3785,32 +3785,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128834411</v>
+        <v>128819672</v>
       </c>
       <c r="B31" t="n">
-        <v>80229</v>
+        <v>98643</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3820,13 +3820,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>754071</v>
+        <v>753733</v>
       </c>
       <c r="R31" t="n">
-        <v>7293962</v>
+        <v>7294060</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3856,6 +3856,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Mycket Riklig förekomst</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3870,22 +3875,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128834420</v>
+        <v>128834415</v>
       </c>
       <c r="B32" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3917,10 +3922,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>754338</v>
+        <v>754084</v>
       </c>
       <c r="R32" t="n">
-        <v>7293821</v>
+        <v>7293943</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3979,32 +3984,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128819672</v>
+        <v>128834411</v>
       </c>
       <c r="B33" t="n">
-        <v>98636</v>
+        <v>80134</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4014,13 +4019,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>753733</v>
+        <v>754071</v>
       </c>
       <c r="R33" t="n">
-        <v>7294060</v>
+        <v>7293962</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4050,11 +4055,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Mycket Riklig förekomst</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4069,44 +4069,44 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128834473</v>
+        <v>128834420</v>
       </c>
       <c r="B34" t="n">
-        <v>98636</v>
+        <v>80134</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4116,10 +4116,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>754284</v>
+        <v>754338</v>
       </c>
       <c r="R34" t="n">
-        <v>7293849</v>
+        <v>7293821</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4178,10 +4178,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128819673</v>
+        <v>128834490</v>
       </c>
       <c r="B35" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4213,13 +4213,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>753787</v>
+        <v>754042</v>
       </c>
       <c r="R35" t="n">
-        <v>7294025</v>
+        <v>7294151</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Mycket riktig förekomst</t>
+          <t>Riklig förekomst ca 10m diam</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4268,22 +4268,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128834490</v>
+        <v>128819673</v>
       </c>
       <c r="B36" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>754042</v>
+        <v>753787</v>
       </c>
       <c r="R36" t="n">
-        <v>7294151</v>
+        <v>7294025</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Riklig förekomst ca 10m diam</t>
+          <t>Mycket riktig förekomst</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4370,12 +4370,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4385,7 +4385,7 @@
         <v>128834462</v>
       </c>
       <c r="B37" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4479,10 +4479,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128834434</v>
+        <v>128819696</v>
       </c>
       <c r="B38" t="n">
-        <v>95486</v>
+        <v>80169</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4490,21 +4490,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2387</v>
+        <v>6463</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4514,13 +4514,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>753879</v>
+        <v>754302</v>
       </c>
       <c r="R38" t="n">
-        <v>7293890</v>
+        <v>7293804</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4564,44 +4564,44 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128834417</v>
+        <v>128834378</v>
       </c>
       <c r="B39" t="n">
-        <v>80229</v>
+        <v>80163</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>754171</v>
+        <v>753636</v>
       </c>
       <c r="R39" t="n">
-        <v>7293926</v>
+        <v>7294023</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4673,10 +4673,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128819696</v>
+        <v>128834434</v>
       </c>
       <c r="B40" t="n">
-        <v>80264</v>
+        <v>95493</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4684,21 +4684,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6463</v>
+        <v>2387</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4708,13 +4708,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>754302</v>
+        <v>753879</v>
       </c>
       <c r="R40" t="n">
-        <v>7293804</v>
+        <v>7293890</v>
       </c>
       <c r="S40" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4758,22 +4758,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128834405</v>
+        <v>128834417</v>
       </c>
       <c r="B41" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4805,10 +4805,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>753772</v>
+        <v>754171</v>
       </c>
       <c r="R41" t="n">
-        <v>7293986</v>
+        <v>7293926</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4867,32 +4867,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128834390</v>
+        <v>128834405</v>
       </c>
       <c r="B42" t="n">
-        <v>80133</v>
+        <v>80134</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>754064</v>
+        <v>753772</v>
       </c>
       <c r="R42" t="n">
-        <v>7294121</v>
+        <v>7293986</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4964,32 +4964,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128819663</v>
+        <v>128834390</v>
       </c>
       <c r="B43" t="n">
-        <v>80229</v>
+        <v>80038</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4999,13 +4999,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>754152</v>
+        <v>754064</v>
       </c>
       <c r="R43" t="n">
-        <v>7294076</v>
+        <v>7294121</v>
       </c>
       <c r="S43" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5049,44 +5049,44 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128834378</v>
+        <v>128819663</v>
       </c>
       <c r="B44" t="n">
-        <v>80258</v>
+        <v>80134</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5096,13 +5096,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>753636</v>
+        <v>754152</v>
       </c>
       <c r="R44" t="n">
-        <v>7294023</v>
+        <v>7294076</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5146,12 +5146,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5161,7 +5161,7 @@
         <v>128834410</v>
       </c>
       <c r="B45" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>128819642</v>
       </c>
       <c r="B46" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5352,32 +5352,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128834386</v>
+        <v>128834454</v>
       </c>
       <c r="B47" t="n">
-        <v>57717</v>
+        <v>98643</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5387,10 +5387,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>753889</v>
+        <v>753898</v>
       </c>
       <c r="R47" t="n">
-        <v>7294195</v>
+        <v>7293898</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5427,7 +5427,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Hack vid trädbas</t>
+          <t>3mtr diam</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5454,10 +5454,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128834454</v>
+        <v>128819675</v>
       </c>
       <c r="B48" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5489,13 +5489,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>753898</v>
+        <v>753812</v>
       </c>
       <c r="R48" t="n">
-        <v>7293898</v>
+        <v>7293999</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>3mtr diam</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5544,44 +5544,44 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128819675</v>
+        <v>128834386</v>
       </c>
       <c r="B49" t="n">
-        <v>98636</v>
+        <v>57720</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5591,13 +5591,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>753812</v>
+        <v>753889</v>
       </c>
       <c r="R49" t="n">
-        <v>7293999</v>
+        <v>7294195</v>
       </c>
       <c r="S49" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Hack vid trädbas</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5646,12 +5646,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -5661,7 +5661,7 @@
         <v>128834406</v>
       </c>
       <c r="B50" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         <v>128834430</v>
       </c>
       <c r="B51" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5852,10 +5852,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128819690</v>
+        <v>128819693</v>
       </c>
       <c r="B52" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5887,10 +5887,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>754224</v>
+        <v>754024</v>
       </c>
       <c r="R52" t="n">
-        <v>7293966</v>
+        <v>7294106</v>
       </c>
       <c r="S52" t="n">
         <v>3</v>
@@ -5923,6 +5923,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>På ett större område mer än 30 individer</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5949,10 +5954,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128819693</v>
+        <v>128819690</v>
       </c>
       <c r="B53" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5984,10 +5989,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>754024</v>
+        <v>754224</v>
       </c>
       <c r="R53" t="n">
-        <v>7294106</v>
+        <v>7293966</v>
       </c>
       <c r="S53" t="n">
         <v>3</v>
@@ -6020,11 +6025,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>På ett större område mer än 30 individer</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6054,7 +6054,7 @@
         <v>128834484</v>
       </c>
       <c r="B54" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6153,32 +6153,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128834376</v>
+        <v>128834433</v>
       </c>
       <c r="B55" t="n">
-        <v>91508</v>
+        <v>95493</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>2387</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6188,10 +6188,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>754253</v>
+        <v>753867</v>
       </c>
       <c r="R55" t="n">
-        <v>7293898</v>
+        <v>7293877</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6250,10 +6250,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128819639</v>
+        <v>128819648</v>
       </c>
       <c r="B56" t="n">
-        <v>91804</v>
+        <v>80134</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6261,21 +6261,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6285,10 +6285,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>754249</v>
+        <v>754142</v>
       </c>
       <c r="R56" t="n">
-        <v>7293891</v>
+        <v>7293999</v>
       </c>
       <c r="S56" t="n">
         <v>3</v>
@@ -6321,11 +6321,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>10 fruktkroppar</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6352,32 +6347,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128834433</v>
+        <v>128834404</v>
       </c>
       <c r="B57" t="n">
-        <v>95486</v>
+        <v>80134</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2387</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6387,10 +6382,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>753867</v>
+        <v>753693</v>
       </c>
       <c r="R57" t="n">
-        <v>7293877</v>
+        <v>7293978</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6449,10 +6444,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128819648</v>
+        <v>128834491</v>
       </c>
       <c r="B58" t="n">
-        <v>80229</v>
+        <v>56904</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6460,21 +6455,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6484,13 +6479,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>754142</v>
+        <v>753881</v>
       </c>
       <c r="R58" t="n">
-        <v>7293999</v>
+        <v>7293891</v>
       </c>
       <c r="S58" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6534,44 +6529,44 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128834404</v>
+        <v>128834446</v>
       </c>
       <c r="B59" t="n">
-        <v>80229</v>
+        <v>98643</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6581,10 +6576,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>753693</v>
+        <v>753638</v>
       </c>
       <c r="R59" t="n">
-        <v>7293978</v>
+        <v>7293994</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6617,6 +6612,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Mycket rikligt bestånd</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6643,32 +6643,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128834491</v>
+        <v>128819680</v>
       </c>
       <c r="B60" t="n">
-        <v>56901</v>
+        <v>98643</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6678,13 +6678,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>753881</v>
+        <v>754079</v>
       </c>
       <c r="R60" t="n">
-        <v>7293891</v>
+        <v>7294043</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6714,6 +6714,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Rik förekomst</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6728,44 +6733,44 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128834446</v>
+        <v>128834376</v>
       </c>
       <c r="B61" t="n">
-        <v>98636</v>
+        <v>91513</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6775,10 +6780,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>753638</v>
+        <v>754253</v>
       </c>
       <c r="R61" t="n">
-        <v>7293994</v>
+        <v>7293898</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6811,11 +6816,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Mycket rikligt bestånd</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6842,32 +6842,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128834449</v>
+        <v>128819639</v>
       </c>
       <c r="B62" t="n">
-        <v>98636</v>
+        <v>91809</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6877,13 +6877,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>753732</v>
+        <v>754249</v>
       </c>
       <c r="R62" t="n">
-        <v>7293989</v>
+        <v>7293891</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Mycket rikligt bestånd</t>
+          <t>10 fruktkroppar</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6932,22 +6932,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128819680</v>
+        <v>128834449</v>
       </c>
       <c r="B63" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6979,13 +6979,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>754079</v>
+        <v>753732</v>
       </c>
       <c r="R63" t="n">
-        <v>7294043</v>
+        <v>7293989</v>
       </c>
       <c r="S63" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Rik förekomst</t>
+          <t>Mycket rikligt bestånd</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7034,22 +7034,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128834407</v>
+        <v>128834416</v>
       </c>
       <c r="B64" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7081,10 +7081,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>753989</v>
+        <v>754148</v>
       </c>
       <c r="R64" t="n">
-        <v>7294010</v>
+        <v>7293935</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7143,32 +7143,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128834416</v>
+        <v>128834380</v>
       </c>
       <c r="B65" t="n">
-        <v>80229</v>
+        <v>80163</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7178,10 +7178,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>754148</v>
+        <v>754091</v>
       </c>
       <c r="R65" t="n">
-        <v>7293935</v>
+        <v>7293941</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7240,32 +7240,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128834380</v>
+        <v>128834457</v>
       </c>
       <c r="B66" t="n">
-        <v>80258</v>
+        <v>98643</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7275,10 +7275,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>754091</v>
+        <v>753947</v>
       </c>
       <c r="R66" t="n">
-        <v>7293941</v>
+        <v>7293964</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7311,6 +7311,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>5mtr diam</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7337,10 +7342,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128834457</v>
+        <v>128834458</v>
       </c>
       <c r="B67" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7372,10 +7377,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>753947</v>
+        <v>753959</v>
       </c>
       <c r="R67" t="n">
-        <v>7293964</v>
+        <v>7294022</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7412,7 +7417,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>5mtr diam</t>
+          <t>3m diam</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7442,7 +7447,7 @@
         <v>128834463</v>
       </c>
       <c r="B68" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7536,10 +7541,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128834458</v>
+        <v>128819677</v>
       </c>
       <c r="B69" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7571,13 +7576,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>753959</v>
+        <v>753875</v>
       </c>
       <c r="R69" t="n">
-        <v>7294022</v>
+        <v>7294001</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7607,11 +7612,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>3m diam</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7626,44 +7626,44 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128819677</v>
+        <v>128834407</v>
       </c>
       <c r="B70" t="n">
-        <v>98636</v>
+        <v>80134</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7673,13 +7673,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>753875</v>
+        <v>753989</v>
       </c>
       <c r="R70" t="n">
-        <v>7294001</v>
+        <v>7294010</v>
       </c>
       <c r="S70" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7723,12 +7723,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -7738,7 +7738,7 @@
         <v>128834461</v>
       </c>
       <c r="B71" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>128834456</v>
       </c>
       <c r="B72" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7929,10 +7929,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128834409</v>
+        <v>128834401</v>
       </c>
       <c r="B73" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7964,10 +7964,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>754042</v>
+        <v>753629</v>
       </c>
       <c r="R73" t="n">
-        <v>7293966</v>
+        <v>7294009</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8026,10 +8026,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128834401</v>
+        <v>128819652</v>
       </c>
       <c r="B74" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8061,13 +8061,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>753629</v>
+        <v>754297</v>
       </c>
       <c r="R74" t="n">
-        <v>7294009</v>
+        <v>7293780</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8111,22 +8111,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128819652</v>
+        <v>128834409</v>
       </c>
       <c r="B75" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8158,13 +8158,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>754297</v>
+        <v>754042</v>
       </c>
       <c r="R75" t="n">
-        <v>7293780</v>
+        <v>7293966</v>
       </c>
       <c r="S75" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8208,12 +8208,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -8223,7 +8223,7 @@
         <v>128834431</v>
       </c>
       <c r="B76" t="n">
-        <v>80265</v>
+        <v>80170</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8317,10 +8317,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128819676</v>
+        <v>128834443</v>
       </c>
       <c r="B77" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8352,13 +8352,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>753836</v>
+        <v>754042</v>
       </c>
       <c r="R77" t="n">
-        <v>7293977</v>
+        <v>7294129</v>
       </c>
       <c r="S77" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Måttlig förekomst 6m diam</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8407,12 +8407,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -8422,7 +8422,7 @@
         <v>128834476</v>
       </c>
       <c r="B78" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8521,10 +8521,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128834443</v>
+        <v>128819676</v>
       </c>
       <c r="B79" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8556,13 +8556,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>754042</v>
+        <v>753836</v>
       </c>
       <c r="R79" t="n">
-        <v>7294129</v>
+        <v>7293977</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Måttlig förekomst 6m diam</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8611,44 +8611,44 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128834497</v>
+        <v>128819655</v>
       </c>
       <c r="B80" t="n">
-        <v>80264</v>
+        <v>80134</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8658,13 +8658,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>754176</v>
+        <v>754314</v>
       </c>
       <c r="R80" t="n">
-        <v>7293924</v>
+        <v>7293792</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8708,22 +8708,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128819655</v>
+        <v>128819664</v>
       </c>
       <c r="B81" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8755,10 +8755,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>754314</v>
+        <v>754142</v>
       </c>
       <c r="R81" t="n">
-        <v>7293792</v>
+        <v>7294080</v>
       </c>
       <c r="S81" t="n">
         <v>3</v>
@@ -8817,32 +8817,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128819664</v>
+        <v>128834497</v>
       </c>
       <c r="B82" t="n">
-        <v>80229</v>
+        <v>80169</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8852,13 +8852,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>754142</v>
+        <v>754176</v>
       </c>
       <c r="R82" t="n">
-        <v>7294080</v>
+        <v>7293924</v>
       </c>
       <c r="S82" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8902,12 +8902,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -8917,7 +8917,7 @@
         <v>128834381</v>
       </c>
       <c r="B83" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9014,7 +9014,7 @@
         <v>128819637</v>
       </c>
       <c r="B84" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9111,7 +9111,7 @@
         <v>128834492</v>
       </c>
       <c r="B85" t="n">
-        <v>56901</v>
+        <v>56904</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9205,10 +9205,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128819685</v>
+        <v>128834466</v>
       </c>
       <c r="B86" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9240,13 +9240,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>754139</v>
+        <v>754165</v>
       </c>
       <c r="R86" t="n">
-        <v>7294003</v>
+        <v>7293935</v>
       </c>
       <c r="S86" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9276,6 +9276,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>2m diam</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9290,22 +9295,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128834488</v>
+        <v>128819685</v>
       </c>
       <c r="B87" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9337,13 +9342,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>754049</v>
+        <v>754139</v>
       </c>
       <c r="R87" t="n">
-        <v>7294111</v>
+        <v>7294003</v>
       </c>
       <c r="S87" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9387,22 +9392,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128834466</v>
+        <v>128834488</v>
       </c>
       <c r="B88" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9434,10 +9439,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>754165</v>
+        <v>754049</v>
       </c>
       <c r="R88" t="n">
-        <v>7293935</v>
+        <v>7294111</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9470,11 +9475,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>2m diam</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9504,7 +9504,7 @@
         <v>128834427</v>
       </c>
       <c r="B89" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9598,32 +9598,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128834432</v>
+        <v>128819681</v>
       </c>
       <c r="B90" t="n">
-        <v>80133</v>
+        <v>98643</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9633,13 +9633,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>754056</v>
+        <v>754100</v>
       </c>
       <c r="R90" t="n">
-        <v>7293965</v>
+        <v>7294064</v>
       </c>
       <c r="S90" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9669,6 +9669,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Mycket Riklig förekomst</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9683,12 +9688,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
@@ -9698,7 +9703,7 @@
         <v>128834459</v>
       </c>
       <c r="B91" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9792,10 +9797,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128819681</v>
+        <v>128834471</v>
       </c>
       <c r="B92" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9827,13 +9832,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>754100</v>
+        <v>754251</v>
       </c>
       <c r="R92" t="n">
-        <v>7294064</v>
+        <v>7293891</v>
       </c>
       <c r="S92" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -9863,11 +9868,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Mycket Riklig förekomst</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9882,44 +9882,44 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128834471</v>
+        <v>128834432</v>
       </c>
       <c r="B93" t="n">
-        <v>98636</v>
+        <v>80038</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9929,10 +9929,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>754251</v>
+        <v>754056</v>
       </c>
       <c r="R93" t="n">
-        <v>7293891</v>
+        <v>7293965</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -9991,32 +9991,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128834482</v>
+        <v>128834435</v>
       </c>
       <c r="B94" t="n">
-        <v>98636</v>
+        <v>95493</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>2387</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10026,10 +10026,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>754298</v>
+        <v>753941</v>
       </c>
       <c r="R94" t="n">
-        <v>7293981</v>
+        <v>7294196</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10091,7 +10091,7 @@
         <v>128819686</v>
       </c>
       <c r="B95" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10188,7 +10188,7 @@
         <v>128834455</v>
       </c>
       <c r="B96" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10287,32 +10287,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128819654</v>
+        <v>128834482</v>
       </c>
       <c r="B97" t="n">
-        <v>80229</v>
+        <v>98643</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10322,13 +10322,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>754303</v>
+        <v>754298</v>
       </c>
       <c r="R97" t="n">
-        <v>7293804</v>
+        <v>7293981</v>
       </c>
       <c r="S97" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10372,12 +10372,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
@@ -10387,7 +10387,7 @@
         <v>128819649</v>
       </c>
       <c r="B98" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10481,32 +10481,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128834435</v>
+        <v>128819654</v>
       </c>
       <c r="B99" t="n">
-        <v>95486</v>
+        <v>80134</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2387</v>
+        <v>6458</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10516,13 +10516,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>753941</v>
+        <v>754303</v>
       </c>
       <c r="R99" t="n">
-        <v>7294196</v>
+        <v>7293804</v>
       </c>
       <c r="S99" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10566,44 +10566,44 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128819679</v>
+        <v>128834399</v>
       </c>
       <c r="B100" t="n">
-        <v>98636</v>
+        <v>80134</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10613,13 +10613,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>754015</v>
+        <v>753717</v>
       </c>
       <c r="R100" t="n">
-        <v>7294040</v>
+        <v>7294108</v>
       </c>
       <c r="S100" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10649,11 +10649,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10668,44 +10663,44 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128834451</v>
+        <v>128834428</v>
       </c>
       <c r="B101" t="n">
-        <v>98636</v>
+        <v>80134</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10715,10 +10710,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>753769</v>
+        <v>754137</v>
       </c>
       <c r="R101" t="n">
-        <v>7293962</v>
+        <v>7294102</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -10780,7 +10775,7 @@
         <v>128819644</v>
       </c>
       <c r="B102" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10874,32 +10869,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128834399</v>
+        <v>128819679</v>
       </c>
       <c r="B103" t="n">
-        <v>80229</v>
+        <v>98643</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10909,13 +10904,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>753717</v>
+        <v>754015</v>
       </c>
       <c r="R103" t="n">
-        <v>7294108</v>
+        <v>7294040</v>
       </c>
       <c r="S103" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -10945,6 +10940,11 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10959,44 +10959,44 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128834428</v>
+        <v>128834448</v>
       </c>
       <c r="B104" t="n">
-        <v>80229</v>
+        <v>98643</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11006,10 +11006,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>754137</v>
+        <v>753692</v>
       </c>
       <c r="R104" t="n">
-        <v>7294102</v>
+        <v>7293978</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -11068,10 +11068,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128834448</v>
+        <v>128834451</v>
       </c>
       <c r="B105" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11103,10 +11103,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>753692</v>
+        <v>753769</v>
       </c>
       <c r="R105" t="n">
-        <v>7293978</v>
+        <v>7293962</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -11165,10 +11165,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128834450</v>
+        <v>128819670</v>
       </c>
       <c r="B106" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11200,13 +11200,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>753753</v>
+        <v>753799</v>
       </c>
       <c r="R106" t="n">
-        <v>7293995</v>
+        <v>7294127</v>
       </c>
       <c r="S106" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11236,6 +11236,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Mycket riktig förekomst</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11250,22 +11255,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128819670</v>
+        <v>128834465</v>
       </c>
       <c r="B107" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11297,13 +11302,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>753799</v>
+        <v>754148</v>
       </c>
       <c r="R107" t="n">
-        <v>7294127</v>
+        <v>7293932</v>
       </c>
       <c r="S107" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11333,11 +11338,6 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Mycket riktig förekomst</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11352,22 +11352,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128834465</v>
+        <v>128834450</v>
       </c>
       <c r="B108" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11399,10 +11399,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>754148</v>
+        <v>753753</v>
       </c>
       <c r="R108" t="n">
-        <v>7293932</v>
+        <v>7293995</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -11461,10 +11461,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128834445</v>
+        <v>128819684</v>
       </c>
       <c r="B109" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11496,13 +11496,13 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>753685</v>
+        <v>754145</v>
       </c>
       <c r="R109" t="n">
-        <v>7294059</v>
+        <v>7294023</v>
       </c>
       <c r="S109" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -11532,11 +11532,6 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>3mtr diam</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11551,22 +11546,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128834468</v>
+        <v>128834445</v>
       </c>
       <c r="B110" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11598,10 +11593,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>754196</v>
+        <v>753685</v>
       </c>
       <c r="R110" t="n">
-        <v>7293923</v>
+        <v>7294059</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -11634,6 +11629,11 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>3mtr diam</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11660,10 +11660,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128819684</v>
+        <v>128834468</v>
       </c>
       <c r="B111" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11695,13 +11695,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>754145</v>
+        <v>754196</v>
       </c>
       <c r="R111" t="n">
-        <v>7294023</v>
+        <v>7293923</v>
       </c>
       <c r="S111" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -11745,12 +11745,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
@@ -11760,7 +11760,7 @@
         <v>128834436</v>
       </c>
       <c r="B112" t="n">
-        <v>95486</v>
+        <v>95493</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11857,7 +11857,7 @@
         <v>128834408</v>
       </c>
       <c r="B113" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11951,32 +11951,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128834419</v>
+        <v>128819689</v>
       </c>
       <c r="B114" t="n">
-        <v>80229</v>
+        <v>98643</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11986,13 +11986,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>754329</v>
+        <v>754240</v>
       </c>
       <c r="R114" t="n">
-        <v>7293829</v>
+        <v>7293924</v>
       </c>
       <c r="S114" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12022,6 +12022,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Större förekomst</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12036,22 +12041,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128819668</v>
+        <v>128834419</v>
       </c>
       <c r="B115" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12083,13 +12088,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>753980</v>
+        <v>754329</v>
       </c>
       <c r="R115" t="n">
-        <v>7294135</v>
+        <v>7293829</v>
       </c>
       <c r="S115" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12133,22 +12138,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128819647</v>
+        <v>128819668</v>
       </c>
       <c r="B116" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12180,10 +12185,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>754139</v>
+        <v>753980</v>
       </c>
       <c r="R116" t="n">
-        <v>7294012</v>
+        <v>7294135</v>
       </c>
       <c r="S116" t="n">
         <v>3</v>
@@ -12242,32 +12247,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128819689</v>
+        <v>128819647</v>
       </c>
       <c r="B117" t="n">
-        <v>98636</v>
+        <v>80134</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12277,10 +12282,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>754240</v>
+        <v>754139</v>
       </c>
       <c r="R117" t="n">
-        <v>7293924</v>
+        <v>7294012</v>
       </c>
       <c r="S117" t="n">
         <v>3</v>
@@ -12313,11 +12318,6 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Större förekomst</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12344,32 +12344,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128834477</v>
+        <v>128834400</v>
       </c>
       <c r="B118" t="n">
-        <v>98636</v>
+        <v>80134</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12379,10 +12379,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>754356</v>
+        <v>753636</v>
       </c>
       <c r="R118" t="n">
-        <v>7293813</v>
+        <v>7294018</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -12415,11 +12415,6 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Ca 2m diam</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12446,32 +12441,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128834469</v>
+        <v>128834429</v>
       </c>
       <c r="B119" t="n">
-        <v>98636</v>
+        <v>80134</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12481,10 +12476,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>754222</v>
+        <v>754063</v>
       </c>
       <c r="R119" t="n">
-        <v>7293912</v>
+        <v>7294120</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -12517,11 +12512,6 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>10m diam mycket riklig förekomst</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12548,10 +12538,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128834499</v>
+        <v>128834469</v>
       </c>
       <c r="B120" t="n">
-        <v>91880</v>
+        <v>98643</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12559,37 +12549,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1505</v>
+        <v>220787</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Stormansberget, Nb</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>754035</v>
+        <v>754222</v>
       </c>
       <c r="R120" t="n">
-        <v>7294132</v>
+        <v>7293912</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -12624,13 +12611,17 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>10m diam mycket riklig förekomst</t>
+        </is>
+      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -12649,32 +12640,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128834400</v>
+        <v>128834444</v>
       </c>
       <c r="B121" t="n">
-        <v>80229</v>
+        <v>98643</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12684,10 +12675,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>753636</v>
+        <v>753729</v>
       </c>
       <c r="R121" t="n">
-        <v>7294018</v>
+        <v>7294103</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -12746,45 +12737,48 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128834429</v>
+        <v>128834499</v>
       </c>
       <c r="B122" t="n">
-        <v>80229</v>
+        <v>91885</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6458</v>
+        <v>1505</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Stormansberget, Nb</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>754063</v>
+        <v>754035</v>
       </c>
       <c r="R122" t="n">
-        <v>7294120</v>
+        <v>7294132</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -12825,6 +12819,7 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -12843,10 +12838,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128834444</v>
+        <v>128834477</v>
       </c>
       <c r="B123" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12878,10 +12873,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>753729</v>
+        <v>754356</v>
       </c>
       <c r="R123" t="n">
-        <v>7294103</v>
+        <v>7293813</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -12914,6 +12909,11 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Ca 2m diam</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -12943,7 +12943,7 @@
         <v>128834373</v>
       </c>
       <c r="B124" t="n">
-        <v>91683</v>
+        <v>91688</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13037,32 +13037,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128819650</v>
+        <v>128819697</v>
       </c>
       <c r="B125" t="n">
-        <v>80229</v>
+        <v>96762</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6458</v>
+        <v>2869</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13072,10 +13072,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>754166</v>
+        <v>754263</v>
       </c>
       <c r="R125" t="n">
-        <v>7293978</v>
+        <v>7293846</v>
       </c>
       <c r="S125" t="n">
         <v>3</v>
@@ -13134,10 +13134,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128834418</v>
+        <v>128819650</v>
       </c>
       <c r="B126" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13169,13 +13169,13 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>754325</v>
+        <v>754166</v>
       </c>
       <c r="R126" t="n">
-        <v>7293826</v>
+        <v>7293978</v>
       </c>
       <c r="S126" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13219,22 +13219,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128819653</v>
+        <v>128834375</v>
       </c>
       <c r="B127" t="n">
-        <v>80229</v>
+        <v>79061</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13242,21 +13242,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13266,13 +13266,13 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>754304</v>
+        <v>754092</v>
       </c>
       <c r="R127" t="n">
-        <v>7293805</v>
+        <v>7293962</v>
       </c>
       <c r="S127" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -13316,22 +13316,22 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128819694</v>
+        <v>128834418</v>
       </c>
       <c r="B128" t="n">
-        <v>56901</v>
+        <v>80134</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13339,21 +13339,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13363,13 +13363,13 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>754139</v>
+        <v>754325</v>
       </c>
       <c r="R128" t="n">
-        <v>7294034</v>
+        <v>7293826</v>
       </c>
       <c r="S128" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13413,22 +13413,22 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128834375</v>
+        <v>128819653</v>
       </c>
       <c r="B129" t="n">
-        <v>79156</v>
+        <v>80134</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13436,21 +13436,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13460,13 +13460,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>754092</v>
+        <v>754304</v>
       </c>
       <c r="R129" t="n">
-        <v>7293962</v>
+        <v>7293805</v>
       </c>
       <c r="S129" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -13510,44 +13510,44 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128819697</v>
+        <v>128819694</v>
       </c>
       <c r="B130" t="n">
-        <v>96755</v>
+        <v>56904</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>2869</v>
+        <v>102612</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13557,10 +13557,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>754263</v>
+        <v>754139</v>
       </c>
       <c r="R130" t="n">
-        <v>7293846</v>
+        <v>7294034</v>
       </c>
       <c r="S130" t="n">
         <v>3</v>
@@ -13619,10 +13619,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128819671</v>
+        <v>128834453</v>
       </c>
       <c r="B131" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13654,13 +13654,13 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>753685</v>
+        <v>753894</v>
       </c>
       <c r="R131" t="n">
-        <v>7294093</v>
+        <v>7293894</v>
       </c>
       <c r="S131" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -13690,6 +13690,11 @@
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>5mtr mycket rikligt bestånd</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -13704,22 +13709,22 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128834453</v>
+        <v>128819671</v>
       </c>
       <c r="B132" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13751,13 +13756,13 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>753894</v>
+        <v>753685</v>
       </c>
       <c r="R132" t="n">
-        <v>7293894</v>
+        <v>7294093</v>
       </c>
       <c r="S132" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -13787,11 +13792,6 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>5mtr mycket rikligt bestånd</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -13806,22 +13806,22 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128834452</v>
+        <v>128834474</v>
       </c>
       <c r="B133" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13853,10 +13853,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>753833</v>
+        <v>754313</v>
       </c>
       <c r="R133" t="n">
-        <v>7293877</v>
+        <v>7293834</v>
       </c>
       <c r="S133" t="n">
         <v>5</v>
@@ -13915,10 +13915,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128834474</v>
+        <v>128834452</v>
       </c>
       <c r="B134" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13950,10 +13950,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>754313</v>
+        <v>753833</v>
       </c>
       <c r="R134" t="n">
-        <v>7293834</v>
+        <v>7293877</v>
       </c>
       <c r="S134" t="n">
         <v>5</v>
@@ -14015,7 +14015,7 @@
         <v>128819683</v>
       </c>
       <c r="B135" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14109,10 +14109,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128819651</v>
+        <v>128834372</v>
       </c>
       <c r="B136" t="n">
-        <v>80229</v>
+        <v>88777</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14120,21 +14120,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6458</v>
+        <v>4412</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14144,13 +14144,13 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>754220</v>
+        <v>754265</v>
       </c>
       <c r="R136" t="n">
-        <v>7293908</v>
+        <v>7293869</v>
       </c>
       <c r="S136" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -14194,22 +14194,22 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128819669</v>
+        <v>128819651</v>
       </c>
       <c r="B137" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14241,10 +14241,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>753872</v>
+        <v>754220</v>
       </c>
       <c r="R137" t="n">
-        <v>7294169</v>
+        <v>7293908</v>
       </c>
       <c r="S137" t="n">
         <v>3</v>
@@ -14303,10 +14303,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128819645</v>
+        <v>128819669</v>
       </c>
       <c r="B138" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14338,10 +14338,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>754081</v>
+        <v>753872</v>
       </c>
       <c r="R138" t="n">
-        <v>7294036</v>
+        <v>7294169</v>
       </c>
       <c r="S138" t="n">
         <v>3</v>
@@ -14400,10 +14400,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128819640</v>
+        <v>128819645</v>
       </c>
       <c r="B139" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14435,10 +14435,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>754021</v>
+        <v>754081</v>
       </c>
       <c r="R139" t="n">
-        <v>7294099</v>
+        <v>7294036</v>
       </c>
       <c r="S139" t="n">
         <v>3</v>
@@ -14479,7 +14479,6 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -14498,10 +14497,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128834402</v>
+        <v>128819640</v>
       </c>
       <c r="B140" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14533,13 +14532,13 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>753663</v>
+        <v>754021</v>
       </c>
       <c r="R140" t="n">
-        <v>7293971</v>
+        <v>7294099</v>
       </c>
       <c r="S140" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -14577,50 +14576,51 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128834498</v>
+        <v>128834402</v>
       </c>
       <c r="B141" t="n">
-        <v>80264</v>
+        <v>80134</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14630,10 +14630,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>754129</v>
+        <v>753663</v>
       </c>
       <c r="R141" t="n">
-        <v>7294101</v>
+        <v>7293971</v>
       </c>
       <c r="S141" t="n">
         <v>5</v>
@@ -14692,32 +14692,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128834372</v>
+        <v>128834498</v>
       </c>
       <c r="B142" t="n">
-        <v>88772</v>
+        <v>80169</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>4412</v>
+        <v>6463</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14727,10 +14727,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>754265</v>
+        <v>754129</v>
       </c>
       <c r="R142" t="n">
-        <v>7293869</v>
+        <v>7294101</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -14789,32 +14789,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128834489</v>
+        <v>128819667</v>
       </c>
       <c r="B143" t="n">
-        <v>98636</v>
+        <v>80134</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14824,13 +14824,13 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>754044</v>
+        <v>754002</v>
       </c>
       <c r="R143" t="n">
-        <v>7294116</v>
+        <v>7294106</v>
       </c>
       <c r="S143" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -14874,44 +14874,44 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128834379</v>
+        <v>128819643</v>
       </c>
       <c r="B144" t="n">
-        <v>80258</v>
+        <v>80134</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -14921,13 +14921,13 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>753674</v>
+        <v>753951</v>
       </c>
       <c r="R144" t="n">
-        <v>7293973</v>
+        <v>7293999</v>
       </c>
       <c r="S144" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -14971,44 +14971,44 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128834412</v>
+        <v>128834379</v>
       </c>
       <c r="B145" t="n">
-        <v>80229</v>
+        <v>80163</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15018,10 +15018,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>754096</v>
+        <v>753674</v>
       </c>
       <c r="R145" t="n">
-        <v>7293963</v>
+        <v>7293973</v>
       </c>
       <c r="S145" t="n">
         <v>5</v>
@@ -15080,10 +15080,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128819667</v>
+        <v>128834412</v>
       </c>
       <c r="B146" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15115,13 +15115,13 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>754002</v>
+        <v>754096</v>
       </c>
       <c r="R146" t="n">
-        <v>7294106</v>
+        <v>7293963</v>
       </c>
       <c r="S146" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -15165,22 +15165,22 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128819643</v>
+        <v>128819636</v>
       </c>
       <c r="B147" t="n">
-        <v>80229</v>
+        <v>57883</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15188,21 +15188,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>753951</v>
+        <v>754361</v>
       </c>
       <c r="R147" t="n">
-        <v>7293999</v>
+        <v>7293841</v>
       </c>
       <c r="S147" t="n">
         <v>3</v>
@@ -15248,6 +15248,11 @@
       <c r="AA147" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>6 individer</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15274,32 +15279,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128819636</v>
+        <v>128834487</v>
       </c>
       <c r="B148" t="n">
-        <v>57880</v>
+        <v>98643</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15309,13 +15314,13 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>754361</v>
+        <v>754147</v>
       </c>
       <c r="R148" t="n">
-        <v>7293841</v>
+        <v>7294086</v>
       </c>
       <c r="S148" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -15345,11 +15350,6 @@
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>6 individer</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15364,22 +15364,22 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128834487</v>
+        <v>128819682</v>
       </c>
       <c r="B149" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15411,13 +15411,13 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>754147</v>
+        <v>754120</v>
       </c>
       <c r="R149" t="n">
-        <v>7294086</v>
+        <v>7294078</v>
       </c>
       <c r="S149" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -15447,6 +15447,11 @@
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>Riktig förekomst</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15461,22 +15466,22 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128819682</v>
+        <v>128834489</v>
       </c>
       <c r="B150" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15508,13 +15513,13 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>754120</v>
+        <v>754044</v>
       </c>
       <c r="R150" t="n">
-        <v>7294078</v>
+        <v>7294116</v>
       </c>
       <c r="S150" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -15544,11 +15549,6 @@
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>Riktig förekomst</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -15563,44 +15563,44 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128834422</v>
+        <v>128834389</v>
       </c>
       <c r="B151" t="n">
-        <v>80229</v>
+        <v>80038</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15610,10 +15610,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>754355</v>
+        <v>754026</v>
       </c>
       <c r="R151" t="n">
-        <v>7293811</v>
+        <v>7293997</v>
       </c>
       <c r="S151" t="n">
         <v>5</v>
@@ -15672,32 +15672,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128834389</v>
+        <v>128834422</v>
       </c>
       <c r="B152" t="n">
-        <v>80133</v>
+        <v>80134</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15707,10 +15707,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>754026</v>
+        <v>754355</v>
       </c>
       <c r="R152" t="n">
-        <v>7293997</v>
+        <v>7293811</v>
       </c>
       <c r="S152" t="n">
         <v>5</v>
@@ -15772,7 +15772,7 @@
         <v>128834472</v>
       </c>
       <c r="B153" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15874,7 +15874,7 @@
         <v>128834475</v>
       </c>
       <c r="B154" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15973,10 +15973,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128834413</v>
+        <v>128819646</v>
       </c>
       <c r="B155" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16008,13 +16008,13 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>754091</v>
+        <v>754143</v>
       </c>
       <c r="R155" t="n">
-        <v>7293941</v>
+        <v>7294037</v>
       </c>
       <c r="S155" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -16058,22 +16058,22 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128819646</v>
+        <v>128834413</v>
       </c>
       <c r="B156" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16105,13 +16105,13 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>754143</v>
+        <v>754091</v>
       </c>
       <c r="R156" t="n">
-        <v>7294037</v>
+        <v>7293941</v>
       </c>
       <c r="S156" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -16155,44 +16155,44 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128834470</v>
+        <v>128834391</v>
       </c>
       <c r="B157" t="n">
-        <v>98636</v>
+        <v>97514</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16202,10 +16202,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>754249</v>
+        <v>754184</v>
       </c>
       <c r="R157" t="n">
-        <v>7293901</v>
+        <v>7294045</v>
       </c>
       <c r="S157" t="n">
         <v>5</v>
@@ -16264,10 +16264,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128834485</v>
+        <v>128819688</v>
       </c>
       <c r="B158" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16299,13 +16299,13 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>754182</v>
+        <v>754342</v>
       </c>
       <c r="R158" t="n">
-        <v>7294034</v>
+        <v>7293868</v>
       </c>
       <c r="S158" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -16335,11 +16335,6 @@
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -16354,22 +16349,22 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128819692</v>
+        <v>128834470</v>
       </c>
       <c r="B159" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16401,13 +16396,13 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>754049</v>
+        <v>754249</v>
       </c>
       <c r="R159" t="n">
-        <v>7294082</v>
+        <v>7293901</v>
       </c>
       <c r="S159" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -16437,11 +16432,6 @@
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>Stor förekomst</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -16456,12 +16446,12 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
@@ -16471,7 +16461,7 @@
         <v>128819691</v>
       </c>
       <c r="B160" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16570,10 +16560,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128819688</v>
+        <v>128819692</v>
       </c>
       <c r="B161" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16605,10 +16595,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>754342</v>
+        <v>754049</v>
       </c>
       <c r="R161" t="n">
-        <v>7293868</v>
+        <v>7294082</v>
       </c>
       <c r="S161" t="n">
         <v>3</v>
@@ -16641,6 +16631,11 @@
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>Stor förekomst</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -16667,32 +16662,32 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128834391</v>
+        <v>128834485</v>
       </c>
       <c r="B162" t="n">
-        <v>97507</v>
+        <v>98643</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -16702,10 +16697,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>754184</v>
+        <v>754182</v>
       </c>
       <c r="R162" t="n">
-        <v>7294045</v>
+        <v>7294034</v>
       </c>
       <c r="S162" t="n">
         <v>5</v>
@@ -16738,6 +16733,11 @@
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -16767,7 +16767,7 @@
         <v>128834383</v>
       </c>
       <c r="B163" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16864,7 +16864,7 @@
         <v>128834425</v>
       </c>
       <c r="B164" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16961,7 +16961,7 @@
         <v>129001197</v>
       </c>
       <c r="B165" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17067,7 +17067,7 @@
         <v>129001199</v>
       </c>
       <c r="B166" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17170,37 +17170,37 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129001194</v>
+        <v>129001082</v>
       </c>
       <c r="B167" t="n">
-        <v>98636</v>
+        <v>91513</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P167" t="inlineStr">
@@ -17209,10 +17209,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>754411</v>
+        <v>754163</v>
       </c>
       <c r="R167" t="n">
-        <v>7294018</v>
+        <v>7294133</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17239,12 +17239,12 @@
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AC167" t="inlineStr">
@@ -17276,37 +17276,37 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129001082</v>
+        <v>129001194</v>
       </c>
       <c r="B168" t="n">
-        <v>91508</v>
+        <v>98643</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
@@ -17315,10 +17315,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>754163</v>
+        <v>754411</v>
       </c>
       <c r="R168" t="n">
-        <v>7294133</v>
+        <v>7294018</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17345,12 +17345,12 @@
       </c>
       <c r="Y168" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AC168" t="inlineStr">
@@ -17385,7 +17385,7 @@
         <v>129001198</v>
       </c>
       <c r="B169" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
